--- a/BM(최종).xlsx
+++ b/BM(최종).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{107228E5-A3F0-48FB-982B-0C059B8020AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AE2312-B8BF-49B5-88C9-C41F1C1037AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="639">
   <si>
     <t>개수</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2627,6 +2627,85 @@
   </si>
   <si>
     <t>마일리지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>패기 돌발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>패기 소환 횟수 달성 패키지 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>패기 소환 횟수 달성 패키지 2</t>
+  </si>
+  <si>
+    <t>패기 소환 횟수 달성 패키지 3</t>
+  </si>
+  <si>
+    <t>패기 소환 횟수 달성 패키지 4</t>
+  </si>
+  <si>
+    <t>패기 소환 횟수 달성 패키지 5</t>
+  </si>
+  <si>
+    <t>패기 소환 횟수 달성 패키지 6</t>
+  </si>
+  <si>
+    <t>패기 소환 횟수 달성 패키지 7</t>
+  </si>
+  <si>
+    <t>패기 소환 횟수 달성 패키지 8</t>
+  </si>
+  <si>
+    <t>패기 소환 횟수 달성 패키지 9</t>
+  </si>
+  <si>
+    <t>패기 소환 횟수 달성 패키지 10</t>
+  </si>
+  <si>
+    <t>다이아+패기 소환권</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>누적</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소환레벨3</t>
+  </si>
+  <si>
+    <t>소환레벨4</t>
+  </si>
+  <si>
+    <t>소환레벨5</t>
+  </si>
+  <si>
+    <t>소환레벨6</t>
+  </si>
+  <si>
+    <t>소환레벨7</t>
+  </si>
+  <si>
+    <t>소환레벨8</t>
+  </si>
+  <si>
+    <t>소환레벨9</t>
+  </si>
+  <si>
+    <t>소환레벨10</t>
+  </si>
+  <si>
+    <t>다음레벨필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소환레벨2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>패기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2796,7 +2875,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2915,6 +2994,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2955,7 +3046,7 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3293,9 +3384,6 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -3487,6 +3575,69 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="22" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4273,15 +4424,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A1DA42-0C04-487B-9406-B23AFF762709}">
-  <dimension ref="A1:P455"/>
+  <dimension ref="A1:Q467"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" style="12" customWidth="1"/>
     <col min="4" max="4" width="32.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5" style="115" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.125" style="116" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="114" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.125" style="115" customWidth="1"/>
     <col min="7" max="7" width="12.375" style="16" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.125" style="1" customWidth="1"/>
@@ -4289,10 +4440,10 @@
     <col min="11" max="11" width="16.875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.375" style="45" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.875" style="1" customWidth="1"/>
     <col min="18" max="18" width="6.875" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="5.875" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="16384" width="9" style="1"/>
@@ -4311,10 +4462,10 @@
       <c r="D1" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="113" t="s">
+      <c r="E1" s="110" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="114" t="s">
+      <c r="F1" s="186" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="111" t="s">
@@ -4384,7 +4535,7 @@
     <row r="3" spans="1:16">
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
-      <c r="F3" s="117"/>
+      <c r="F3" s="116"/>
       <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:16" s="55" customFormat="1">
@@ -4392,8 +4543,8 @@
         <v>49</v>
       </c>
       <c r="C4" s="57"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="119"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="118"/>
       <c r="G4" s="21"/>
       <c r="L4" s="46"/>
       <c r="N4" s="55">
@@ -4421,7 +4572,7 @@
       <c r="E5" s="112">
         <v>1000</v>
       </c>
-      <c r="F5" s="120">
+      <c r="F5" s="119">
         <v>30</v>
       </c>
       <c r="G5" s="48">
@@ -4451,7 +4602,7 @@
       <c r="E6" s="66">
         <v>4000</v>
       </c>
-      <c r="F6" s="120">
+      <c r="F6" s="119">
         <v>160</v>
       </c>
       <c r="G6" s="48">
@@ -4501,7 +4652,7 @@
       <c r="E7" s="66">
         <v>20000</v>
       </c>
-      <c r="F7" s="120">
+      <c r="F7" s="119">
         <v>800</v>
       </c>
       <c r="G7" s="48">
@@ -4551,7 +4702,7 @@
       <c r="E8" s="66">
         <v>40000</v>
       </c>
-      <c r="F8" s="120">
+      <c r="F8" s="119">
         <v>1600</v>
       </c>
       <c r="G8" s="48">
@@ -4604,7 +4755,7 @@
       <c r="E9" s="66">
         <v>120000</v>
       </c>
-      <c r="F9" s="120">
+      <c r="F9" s="119">
         <v>4800</v>
       </c>
       <c r="G9" s="48">
@@ -4657,7 +4808,7 @@
       <c r="E10" s="66">
         <v>200000</v>
       </c>
-      <c r="F10" s="120">
+      <c r="F10" s="119">
         <v>8000</v>
       </c>
       <c r="G10" s="48">
@@ -4718,7 +4869,7 @@
       <c r="E12" s="112">
         <v>1000</v>
       </c>
-      <c r="F12" s="120">
+      <c r="F12" s="119">
         <v>30</v>
       </c>
       <c r="G12" s="48">
@@ -4758,7 +4909,7 @@
       <c r="E13" s="112">
         <v>4000</v>
       </c>
-      <c r="F13" s="120">
+      <c r="F13" s="119">
         <v>160</v>
       </c>
       <c r="G13" s="48">
@@ -4808,7 +4959,7 @@
       <c r="E14" s="66">
         <v>20000</v>
       </c>
-      <c r="F14" s="120">
+      <c r="F14" s="119">
         <v>800</v>
       </c>
       <c r="G14" s="48">
@@ -4861,7 +5012,7 @@
       <c r="E15" s="66">
         <v>40000</v>
       </c>
-      <c r="F15" s="120">
+      <c r="F15" s="119">
         <v>1600</v>
       </c>
       <c r="G15" s="48">
@@ -4914,7 +5065,7 @@
       <c r="E16" s="66">
         <v>120000</v>
       </c>
-      <c r="F16" s="120">
+      <c r="F16" s="119">
         <v>4800</v>
       </c>
       <c r="G16" s="48">
@@ -4967,7 +5118,7 @@
       <c r="E17" s="66">
         <v>200000</v>
       </c>
-      <c r="F17" s="120">
+      <c r="F17" s="119">
         <v>8000</v>
       </c>
       <c r="G17" s="48">
@@ -5008,7 +5159,7 @@
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="F18" s="121"/>
+      <c r="F18" s="120"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="M18" s="1" t="s">
@@ -5038,7 +5189,7 @@
       <c r="E19" s="112">
         <v>1000</v>
       </c>
-      <c r="F19" s="120">
+      <c r="F19" s="119">
         <v>60</v>
       </c>
       <c r="G19" s="48">
@@ -5075,7 +5226,7 @@
       <c r="E20" s="112">
         <v>12000</v>
       </c>
-      <c r="F20" s="120">
+      <c r="F20" s="119">
         <v>480</v>
       </c>
       <c r="G20" s="48">
@@ -5119,7 +5270,7 @@
       <c r="E21" s="112">
         <v>24000</v>
       </c>
-      <c r="F21" s="120">
+      <c r="F21" s="119">
         <v>960</v>
       </c>
       <c r="G21" s="48">
@@ -5159,7 +5310,7 @@
       <c r="E22" s="112">
         <v>36000</v>
       </c>
-      <c r="F22" s="120">
+      <c r="F22" s="119">
         <v>1440</v>
       </c>
       <c r="G22" s="48">
@@ -5202,7 +5353,7 @@
       <c r="E23" s="112">
         <v>80000</v>
       </c>
-      <c r="F23" s="120">
+      <c r="F23" s="119">
         <v>3200</v>
       </c>
       <c r="G23" s="48">
@@ -5245,7 +5396,7 @@
       <c r="E24" s="112">
         <v>120000</v>
       </c>
-      <c r="F24" s="120">
+      <c r="F24" s="119">
         <v>4800</v>
       </c>
       <c r="G24" s="48">
@@ -5282,10 +5433,10 @@
       <c r="D25" s="54" t="s">
         <v>517</v>
       </c>
-      <c r="E25" s="148">
+      <c r="E25" s="147">
         <v>200000</v>
       </c>
-      <c r="F25" s="120">
+      <c r="F25" s="119">
         <v>8000</v>
       </c>
       <c r="G25" s="48">
@@ -5328,10 +5479,10 @@
         <v>528</v>
       </c>
       <c r="C27" s="75"/>
-      <c r="D27" s="151" t="s">
+      <c r="D27" s="150" t="s">
         <v>526</v>
       </c>
-      <c r="E27" s="122"/>
+      <c r="E27" s="121"/>
       <c r="F27" s="99">
         <v>100</v>
       </c>
@@ -5370,10 +5521,10 @@
         <v>530</v>
       </c>
       <c r="C28" s="75"/>
-      <c r="D28" s="151" t="s">
+      <c r="D28" s="150" t="s">
         <v>526</v>
       </c>
-      <c r="E28" s="122"/>
+      <c r="E28" s="121"/>
       <c r="F28" s="99">
         <v>160</v>
       </c>
@@ -5412,10 +5563,10 @@
         <v>532</v>
       </c>
       <c r="C29" s="75"/>
-      <c r="D29" s="151" t="s">
+      <c r="D29" s="150" t="s">
         <v>526</v>
       </c>
-      <c r="E29" s="122"/>
+      <c r="E29" s="121"/>
       <c r="F29" s="99">
         <v>320</v>
       </c>
@@ -5454,10 +5605,10 @@
         <v>534</v>
       </c>
       <c r="C30" s="75"/>
-      <c r="D30" s="151" t="s">
+      <c r="D30" s="150" t="s">
         <v>526</v>
       </c>
-      <c r="E30" s="122"/>
+      <c r="E30" s="121"/>
       <c r="F30" s="99">
         <v>1000</v>
       </c>
@@ -5496,10 +5647,10 @@
         <v>536</v>
       </c>
       <c r="C31" s="75"/>
-      <c r="D31" s="151" t="s">
+      <c r="D31" s="150" t="s">
         <v>526</v>
       </c>
-      <c r="E31" s="122"/>
+      <c r="E31" s="121"/>
       <c r="F31" s="99">
         <v>1600</v>
       </c>
@@ -5531,7 +5682,7 @@
       </c>
     </row>
     <row r="32" spans="1:16">
-      <c r="F32" s="123">
+      <c r="F32" s="122">
         <f>SUM(F27:F31)</f>
         <v>3180</v>
       </c>
@@ -5556,7 +5707,7 @@
       <c r="D33" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="E33" s="124"/>
+      <c r="E33" s="123"/>
       <c r="F33" s="99">
         <v>100</v>
       </c>
@@ -5598,7 +5749,7 @@
       <c r="D34" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="E34" s="124"/>
+      <c r="E34" s="123"/>
       <c r="F34" s="99">
         <v>160</v>
       </c>
@@ -5640,7 +5791,7 @@
       <c r="D35" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="E35" s="124"/>
+      <c r="E35" s="123"/>
       <c r="F35" s="99">
         <v>320</v>
       </c>
@@ -5682,7 +5833,7 @@
       <c r="D36" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="E36" s="124"/>
+      <c r="E36" s="123"/>
       <c r="F36" s="99">
         <v>1000</v>
       </c>
@@ -5724,7 +5875,7 @@
       <c r="D37" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="E37" s="124"/>
+      <c r="E37" s="123"/>
       <c r="F37" s="99">
         <v>1600</v>
       </c>
@@ -5758,7 +5909,7 @@
     <row r="38" spans="1:13">
       <c r="D38" s="7"/>
       <c r="E38" s="67"/>
-      <c r="F38" s="123">
+      <c r="F38" s="122">
         <f>SUM(F33:F37)</f>
         <v>3180</v>
       </c>
@@ -5774,8 +5925,8 @@
         <v>58</v>
       </c>
       <c r="C39" s="57"/>
-      <c r="E39" s="118"/>
-      <c r="F39" s="119"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="118"/>
       <c r="G39" s="21"/>
       <c r="L39" s="46"/>
     </row>
@@ -5790,7 +5941,7 @@
       <c r="D40" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="E40" s="124"/>
+      <c r="E40" s="123"/>
       <c r="F40" s="99">
         <v>100</v>
       </c>
@@ -5832,7 +5983,7 @@
       <c r="D41" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="E41" s="124"/>
+      <c r="E41" s="123"/>
       <c r="F41" s="99">
         <v>160</v>
       </c>
@@ -5874,7 +6025,7 @@
       <c r="D42" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="E42" s="124"/>
+      <c r="E42" s="123"/>
       <c r="F42" s="99">
         <v>320</v>
       </c>
@@ -5916,7 +6067,7 @@
       <c r="D43" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="E43" s="124"/>
+      <c r="E43" s="123"/>
       <c r="F43" s="99">
         <v>1000</v>
       </c>
@@ -5958,7 +6109,7 @@
       <c r="D44" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="E44" s="124"/>
+      <c r="E44" s="123"/>
       <c r="F44" s="99">
         <v>1600</v>
       </c>
@@ -5990,7 +6141,7 @@
       </c>
     </row>
     <row r="45" spans="1:13">
-      <c r="F45" s="123">
+      <c r="F45" s="122">
         <f>SUM(F40:F44)</f>
         <v>3180</v>
       </c>
@@ -6015,7 +6166,7 @@
       <c r="D46" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="E46" s="124"/>
+      <c r="E46" s="123"/>
       <c r="F46" s="99">
         <v>100</v>
       </c>
@@ -6057,7 +6208,7 @@
       <c r="D47" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="E47" s="124"/>
+      <c r="E47" s="123"/>
       <c r="F47" s="99">
         <v>160</v>
       </c>
@@ -6099,7 +6250,7 @@
       <c r="D48" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="E48" s="124"/>
+      <c r="E48" s="123"/>
       <c r="F48" s="99">
         <v>320</v>
       </c>
@@ -6141,7 +6292,7 @@
       <c r="D49" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="E49" s="124"/>
+      <c r="E49" s="123"/>
       <c r="F49" s="99">
         <v>1000</v>
       </c>
@@ -6183,7 +6334,7 @@
       <c r="D50" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="E50" s="124"/>
+      <c r="E50" s="123"/>
       <c r="F50" s="99">
         <v>1600</v>
       </c>
@@ -6215,7 +6366,7 @@
       </c>
     </row>
     <row r="51" spans="1:13">
-      <c r="F51" s="123">
+      <c r="F51" s="122">
         <f>SUM(F46:F50)</f>
         <v>3180</v>
       </c>
@@ -6237,7 +6388,7 @@
       <c r="D52" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="E52" s="124"/>
+      <c r="E52" s="123"/>
       <c r="F52" s="99">
         <v>100</v>
       </c>
@@ -6279,7 +6430,7 @@
       <c r="D53" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="E53" s="124"/>
+      <c r="E53" s="123"/>
       <c r="F53" s="99">
         <v>160</v>
       </c>
@@ -6321,7 +6472,7 @@
       <c r="D54" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="E54" s="124"/>
+      <c r="E54" s="123"/>
       <c r="F54" s="99">
         <v>320</v>
       </c>
@@ -6363,7 +6514,7 @@
       <c r="D55" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="E55" s="124"/>
+      <c r="E55" s="123"/>
       <c r="F55" s="99">
         <v>1000</v>
       </c>
@@ -6405,7 +6556,7 @@
       <c r="D56" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="E56" s="124"/>
+      <c r="E56" s="123"/>
       <c r="F56" s="99">
         <v>1600</v>
       </c>
@@ -6437,7 +6588,7 @@
       </c>
     </row>
     <row r="57" spans="1:13">
-      <c r="F57" s="123">
+      <c r="F57" s="122">
         <f>SUM(F52:F56)</f>
         <v>3180</v>
       </c>
@@ -6459,7 +6610,7 @@
       <c r="D58" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="E58" s="124"/>
+      <c r="E58" s="123"/>
       <c r="F58" s="99">
         <v>100</v>
       </c>
@@ -6501,7 +6652,7 @@
       <c r="D59" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="E59" s="124"/>
+      <c r="E59" s="123"/>
       <c r="F59" s="99">
         <v>160</v>
       </c>
@@ -6543,7 +6694,7 @@
       <c r="D60" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="E60" s="124"/>
+      <c r="E60" s="123"/>
       <c r="F60" s="99">
         <v>320</v>
       </c>
@@ -6585,7 +6736,7 @@
       <c r="D61" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="E61" s="124"/>
+      <c r="E61" s="123"/>
       <c r="F61" s="99">
         <v>1000</v>
       </c>
@@ -6627,7 +6778,7 @@
       <c r="D62" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="E62" s="124"/>
+      <c r="E62" s="123"/>
       <c r="F62" s="99">
         <v>1600</v>
       </c>
@@ -6659,7 +6810,7 @@
       </c>
     </row>
     <row r="63" spans="1:13">
-      <c r="F63" s="123">
+      <c r="F63" s="122">
         <f>SUM(F58:F62)</f>
         <v>3180</v>
       </c>
@@ -6675,8 +6826,8 @@
         <v>51</v>
       </c>
       <c r="C64" s="57"/>
-      <c r="E64" s="118"/>
-      <c r="F64" s="125"/>
+      <c r="E64" s="117"/>
+      <c r="F64" s="124"/>
       <c r="G64" s="21"/>
       <c r="H64" s="58"/>
       <c r="I64" s="58"/>
@@ -6696,7 +6847,7 @@
       <c r="E65" s="112">
         <v>4000</v>
       </c>
-      <c r="F65" s="120">
+      <c r="F65" s="119">
         <v>100</v>
       </c>
       <c r="G65" s="48">
@@ -6740,7 +6891,7 @@
       <c r="E66" s="112">
         <v>20000</v>
       </c>
-      <c r="F66" s="120">
+      <c r="F66" s="119">
         <v>520</v>
       </c>
       <c r="G66" s="48">
@@ -6784,7 +6935,7 @@
       <c r="E67" s="112">
         <v>40000</v>
       </c>
-      <c r="F67" s="120">
+      <c r="F67" s="119">
         <v>1040</v>
       </c>
       <c r="G67" s="48">
@@ -6828,7 +6979,7 @@
       <c r="E68" s="112">
         <v>120000</v>
       </c>
-      <c r="F68" s="120">
+      <c r="F68" s="119">
         <v>3200</v>
       </c>
       <c r="G68" s="48">
@@ -6872,7 +7023,7 @@
       <c r="E69" s="112">
         <v>200000</v>
       </c>
-      <c r="F69" s="120">
+      <c r="F69" s="119">
         <v>5200</v>
       </c>
       <c r="G69" s="48">
@@ -6903,7 +7054,7 @@
       </c>
     </row>
     <row r="70" spans="1:13">
-      <c r="F70" s="126">
+      <c r="F70" s="125">
         <f>SUM(F65:F69)</f>
         <v>10060</v>
       </c>
@@ -6927,7 +7078,7 @@
       <c r="E71" s="112">
         <v>4000</v>
       </c>
-      <c r="F71" s="120">
+      <c r="F71" s="119">
         <v>100</v>
       </c>
       <c r="G71" s="48">
@@ -6971,7 +7122,7 @@
       <c r="E72" s="112">
         <v>20000</v>
       </c>
-      <c r="F72" s="120">
+      <c r="F72" s="119">
         <v>520</v>
       </c>
       <c r="G72" s="48">
@@ -7015,7 +7166,7 @@
       <c r="E73" s="112">
         <v>40000</v>
       </c>
-      <c r="F73" s="120">
+      <c r="F73" s="119">
         <v>1040</v>
       </c>
       <c r="G73" s="48">
@@ -7059,7 +7210,7 @@
       <c r="E74" s="112">
         <v>120000</v>
       </c>
-      <c r="F74" s="120">
+      <c r="F74" s="119">
         <v>3200</v>
       </c>
       <c r="G74" s="48">
@@ -7103,7 +7254,7 @@
       <c r="E75" s="112">
         <v>200000</v>
       </c>
-      <c r="F75" s="120">
+      <c r="F75" s="119">
         <v>5200</v>
       </c>
       <c r="G75" s="48">
@@ -7134,7 +7285,7 @@
       </c>
     </row>
     <row r="76" spans="1:13">
-      <c r="F76" s="126">
+      <c r="F76" s="125">
         <f>SUM(F71:F75)</f>
         <v>10060</v>
       </c>
@@ -7155,7 +7306,7 @@
       <c r="D77" s="74" t="s">
         <v>542</v>
       </c>
-      <c r="E77" s="124"/>
+      <c r="E77" s="123"/>
       <c r="F77" s="99">
         <v>100</v>
       </c>
@@ -7197,7 +7348,7 @@
       <c r="D78" s="74" t="s">
         <v>542</v>
       </c>
-      <c r="E78" s="124"/>
+      <c r="E78" s="123"/>
       <c r="F78" s="99">
         <v>160</v>
       </c>
@@ -7239,7 +7390,7 @@
       <c r="D79" s="74" t="s">
         <v>542</v>
       </c>
-      <c r="E79" s="124"/>
+      <c r="E79" s="123"/>
       <c r="F79" s="99">
         <v>320</v>
       </c>
@@ -7281,7 +7432,7 @@
       <c r="D80" s="74" t="s">
         <v>542</v>
       </c>
-      <c r="E80" s="124"/>
+      <c r="E80" s="123"/>
       <c r="F80" s="99">
         <v>1000</v>
       </c>
@@ -7323,7 +7474,7 @@
       <c r="D81" s="74" t="s">
         <v>542</v>
       </c>
-      <c r="E81" s="124"/>
+      <c r="E81" s="123"/>
       <c r="F81" s="99">
         <v>1600</v>
       </c>
@@ -7355,7 +7506,7 @@
       </c>
     </row>
     <row r="82" spans="1:13">
-      <c r="F82" s="123">
+      <c r="F82" s="122">
         <f>SUM(F77:F81)</f>
         <v>3180</v>
       </c>
@@ -7371,8 +7522,8 @@
         <v>50</v>
       </c>
       <c r="C83" s="57"/>
-      <c r="E83" s="118"/>
-      <c r="F83" s="119" t="s">
+      <c r="E83" s="117"/>
+      <c r="F83" s="118" t="s">
         <v>14</v>
       </c>
       <c r="G83" s="21"/>
@@ -7389,10 +7540,10 @@
         <v>549</v>
       </c>
       <c r="C84" s="75"/>
-      <c r="D84" s="152" t="s">
+      <c r="D84" s="151" t="s">
         <v>548</v>
       </c>
-      <c r="E84" s="124"/>
+      <c r="E84" s="123"/>
       <c r="F84" s="99">
         <v>100</v>
       </c>
@@ -7431,10 +7582,10 @@
         <v>550</v>
       </c>
       <c r="C85" s="75"/>
-      <c r="D85" s="152" t="s">
+      <c r="D85" s="151" t="s">
         <v>548</v>
       </c>
-      <c r="E85" s="124"/>
+      <c r="E85" s="123"/>
       <c r="F85" s="99">
         <v>160</v>
       </c>
@@ -7473,10 +7624,10 @@
         <v>551</v>
       </c>
       <c r="C86" s="75"/>
-      <c r="D86" s="152" t="s">
+      <c r="D86" s="151" t="s">
         <v>548</v>
       </c>
-      <c r="E86" s="124"/>
+      <c r="E86" s="123"/>
       <c r="F86" s="99">
         <v>320</v>
       </c>
@@ -7515,10 +7666,10 @@
         <v>552</v>
       </c>
       <c r="C87" s="75"/>
-      <c r="D87" s="152" t="s">
+      <c r="D87" s="151" t="s">
         <v>548</v>
       </c>
-      <c r="E87" s="124"/>
+      <c r="E87" s="123"/>
       <c r="F87" s="99">
         <v>1000</v>
       </c>
@@ -7557,10 +7708,10 @@
         <v>553</v>
       </c>
       <c r="C88" s="75"/>
-      <c r="D88" s="152" t="s">
+      <c r="D88" s="151" t="s">
         <v>548</v>
       </c>
-      <c r="E88" s="124"/>
+      <c r="E88" s="123"/>
       <c r="F88" s="99">
         <v>1600</v>
       </c>
@@ -7596,7 +7747,7 @@
       <c r="C89" s="11"/>
       <c r="D89" s="7"/>
       <c r="E89" s="67"/>
-      <c r="F89" s="123">
+      <c r="F89" s="122">
         <f>SUM(F84:F88)</f>
         <v>3180</v>
       </c>
@@ -7618,7 +7769,7 @@
       <c r="D90" s="74" t="s">
         <v>559</v>
       </c>
-      <c r="E90" s="124"/>
+      <c r="E90" s="123"/>
       <c r="F90" s="99">
         <v>100</v>
       </c>
@@ -7660,7 +7811,7 @@
       <c r="D91" s="74" t="s">
         <v>559</v>
       </c>
-      <c r="E91" s="124"/>
+      <c r="E91" s="123"/>
       <c r="F91" s="99">
         <v>160</v>
       </c>
@@ -7702,7 +7853,7 @@
       <c r="D92" s="74" t="s">
         <v>559</v>
       </c>
-      <c r="E92" s="124"/>
+      <c r="E92" s="123"/>
       <c r="F92" s="99">
         <v>320</v>
       </c>
@@ -7744,7 +7895,7 @@
       <c r="D93" s="74" t="s">
         <v>559</v>
       </c>
-      <c r="E93" s="124"/>
+      <c r="E93" s="123"/>
       <c r="F93" s="99">
         <v>1000</v>
       </c>
@@ -7786,7 +7937,7 @@
       <c r="D94" s="74" t="s">
         <v>559</v>
       </c>
-      <c r="E94" s="124"/>
+      <c r="E94" s="123"/>
       <c r="F94" s="99">
         <v>1600</v>
       </c>
@@ -7821,8 +7972,8 @@
       <c r="B95" s="11"/>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
-      <c r="E95" s="127"/>
-      <c r="F95" s="123">
+      <c r="E95" s="126"/>
+      <c r="F95" s="122">
         <f>SUM(F90:F94)</f>
         <v>3180</v>
       </c>
@@ -7841,10 +7992,10 @@
         <v>560</v>
       </c>
       <c r="C96" s="75"/>
-      <c r="D96" s="152" t="s">
+      <c r="D96" s="151" t="s">
         <v>565</v>
       </c>
-      <c r="E96" s="124"/>
+      <c r="E96" s="123"/>
       <c r="F96" s="99">
         <v>100</v>
       </c>
@@ -7883,10 +8034,10 @@
         <v>561</v>
       </c>
       <c r="C97" s="75"/>
-      <c r="D97" s="152" t="s">
+      <c r="D97" s="151" t="s">
         <v>565</v>
       </c>
-      <c r="E97" s="124"/>
+      <c r="E97" s="123"/>
       <c r="F97" s="99">
         <v>160</v>
       </c>
@@ -7925,10 +8076,10 @@
         <v>562</v>
       </c>
       <c r="C98" s="75"/>
-      <c r="D98" s="152" t="s">
+      <c r="D98" s="151" t="s">
         <v>565</v>
       </c>
-      <c r="E98" s="124"/>
+      <c r="E98" s="123"/>
       <c r="F98" s="99">
         <v>320</v>
       </c>
@@ -7967,10 +8118,10 @@
         <v>563</v>
       </c>
       <c r="C99" s="75"/>
-      <c r="D99" s="152" t="s">
+      <c r="D99" s="151" t="s">
         <v>565</v>
       </c>
-      <c r="E99" s="124"/>
+      <c r="E99" s="123"/>
       <c r="F99" s="99">
         <v>1000</v>
       </c>
@@ -8009,10 +8160,10 @@
         <v>564</v>
       </c>
       <c r="C100" s="75"/>
-      <c r="D100" s="152" t="s">
+      <c r="D100" s="151" t="s">
         <v>565</v>
       </c>
-      <c r="E100" s="124"/>
+      <c r="E100" s="123"/>
       <c r="F100" s="99">
         <v>1600</v>
       </c>
@@ -8044,7 +8195,7 @@
       </c>
     </row>
     <row r="101" spans="1:13">
-      <c r="F101" s="123">
+      <c r="F101" s="122">
         <f>SUM(F96:F100)</f>
         <v>3180</v>
       </c>
@@ -8060,8 +8211,8 @@
         <v>52</v>
       </c>
       <c r="C102" s="57"/>
-      <c r="E102" s="118"/>
-      <c r="F102" s="119"/>
+      <c r="E102" s="117"/>
+      <c r="F102" s="118"/>
       <c r="G102" s="21"/>
       <c r="L102" s="46"/>
     </row>
@@ -8076,10 +8227,10 @@
       <c r="D103" s="77" t="s">
         <v>461</v>
       </c>
-      <c r="E103" s="128">
+      <c r="E103" s="127">
         <v>4000</v>
       </c>
-      <c r="F103" s="129">
+      <c r="F103" s="128">
         <v>80</v>
       </c>
       <c r="G103" s="32">
@@ -8120,10 +8271,10 @@
       <c r="D104" s="77" t="s">
         <v>461</v>
       </c>
-      <c r="E104" s="128">
+      <c r="E104" s="127">
         <v>20000</v>
       </c>
-      <c r="F104" s="129">
+      <c r="F104" s="128">
         <v>400</v>
       </c>
       <c r="G104" s="32">
@@ -8164,10 +8315,10 @@
       <c r="D105" s="77" t="s">
         <v>461</v>
       </c>
-      <c r="E105" s="128">
+      <c r="E105" s="127">
         <v>40000</v>
       </c>
-      <c r="F105" s="129">
+      <c r="F105" s="128">
         <v>800</v>
       </c>
       <c r="G105" s="32">
@@ -8208,10 +8359,10 @@
       <c r="D106" s="77" t="s">
         <v>461</v>
       </c>
-      <c r="E106" s="128">
+      <c r="E106" s="127">
         <v>120000</v>
       </c>
-      <c r="F106" s="129">
+      <c r="F106" s="128">
         <v>2400</v>
       </c>
       <c r="G106" s="32">
@@ -8252,10 +8403,10 @@
       <c r="D107" s="77" t="s">
         <v>461</v>
       </c>
-      <c r="E107" s="128">
+      <c r="E107" s="127">
         <v>200000</v>
       </c>
-      <c r="F107" s="129">
+      <c r="F107" s="128">
         <v>4000</v>
       </c>
       <c r="G107" s="32">
@@ -8288,7 +8439,7 @@
     <row r="108" spans="1:13">
       <c r="B108" s="23"/>
       <c r="C108" s="10"/>
-      <c r="F108" s="117"/>
+      <c r="F108" s="116"/>
       <c r="G108" s="27"/>
     </row>
     <row r="109" spans="1:13">
@@ -8299,10 +8450,10 @@
         <v>566</v>
       </c>
       <c r="C109" s="75"/>
-      <c r="D109" s="152" t="s">
+      <c r="D109" s="151" t="s">
         <v>571</v>
       </c>
-      <c r="E109" s="124"/>
+      <c r="E109" s="123"/>
       <c r="F109" s="99">
         <v>100</v>
       </c>
@@ -8338,10 +8489,10 @@
         <v>567</v>
       </c>
       <c r="C110" s="75"/>
-      <c r="D110" s="152" t="s">
+      <c r="D110" s="151" t="s">
         <v>571</v>
       </c>
-      <c r="E110" s="124"/>
+      <c r="E110" s="123"/>
       <c r="F110" s="99">
         <v>160</v>
       </c>
@@ -8377,10 +8528,10 @@
         <v>568</v>
       </c>
       <c r="C111" s="75"/>
-      <c r="D111" s="152" t="s">
+      <c r="D111" s="151" t="s">
         <v>571</v>
       </c>
-      <c r="E111" s="124"/>
+      <c r="E111" s="123"/>
       <c r="F111" s="99">
         <v>320</v>
       </c>
@@ -8416,10 +8567,10 @@
         <v>569</v>
       </c>
       <c r="C112" s="75"/>
-      <c r="D112" s="152" t="s">
+      <c r="D112" s="151" t="s">
         <v>571</v>
       </c>
-      <c r="E112" s="124"/>
+      <c r="E112" s="123"/>
       <c r="F112" s="99">
         <v>1000</v>
       </c>
@@ -8455,10 +8606,10 @@
         <v>570</v>
       </c>
       <c r="C113" s="75"/>
-      <c r="D113" s="152" t="s">
+      <c r="D113" s="151" t="s">
         <v>571</v>
       </c>
-      <c r="E113" s="124"/>
+      <c r="E113" s="123"/>
       <c r="F113" s="99">
         <v>1600</v>
       </c>
@@ -8487,7 +8638,7 @@
       </c>
     </row>
     <row r="114" spans="1:13">
-      <c r="F114" s="123">
+      <c r="F114" s="122">
         <f>SUM(F109:F113)</f>
         <v>3180</v>
       </c>
@@ -8503,8 +8654,8 @@
         <v>122</v>
       </c>
       <c r="C115" s="57"/>
-      <c r="E115" s="118"/>
-      <c r="F115" s="119"/>
+      <c r="E115" s="117"/>
+      <c r="F115" s="118"/>
       <c r="G115" s="21"/>
       <c r="L115" s="46"/>
     </row>
@@ -8519,10 +8670,10 @@
       <c r="D116" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="E116" s="130">
+      <c r="E116" s="129">
         <v>500</v>
       </c>
-      <c r="F116" s="130"/>
+      <c r="F116" s="129"/>
       <c r="G116" s="80"/>
       <c r="H116" s="78"/>
       <c r="I116" s="78"/>
@@ -8543,10 +8694,10 @@
       <c r="D117" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="E117" s="130">
+      <c r="E117" s="129">
         <v>5000</v>
       </c>
-      <c r="F117" s="130"/>
+      <c r="F117" s="129"/>
       <c r="G117" s="80">
         <f>E117</f>
         <v>5000</v>
@@ -8585,10 +8736,10 @@
       <c r="D118" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="E118" s="130">
+      <c r="E118" s="129">
         <v>9000</v>
       </c>
-      <c r="F118" s="130"/>
+      <c r="F118" s="129"/>
       <c r="G118" s="80">
         <f>E118</f>
         <v>9000</v>
@@ -8627,10 +8778,10 @@
       <c r="D119" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="E119" s="130">
+      <c r="E119" s="129">
         <v>17000</v>
       </c>
-      <c r="F119" s="130"/>
+      <c r="F119" s="129"/>
       <c r="G119" s="80">
         <f>E119</f>
         <v>17000</v>
@@ -8669,10 +8820,10 @@
       <c r="D120" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="E120" s="130">
+      <c r="E120" s="129">
         <v>60000</v>
       </c>
-      <c r="F120" s="130"/>
+      <c r="F120" s="129"/>
       <c r="G120" s="80">
         <f>E120</f>
         <v>60000</v>
@@ -8711,10 +8862,10 @@
       <c r="D121" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="E121" s="130">
+      <c r="E121" s="129">
         <v>125000</v>
       </c>
-      <c r="F121" s="130"/>
+      <c r="F121" s="129"/>
       <c r="G121" s="80">
         <f>E121</f>
         <v>125000</v>
@@ -8744,13 +8895,13 @@
     </row>
     <row r="122" spans="1:13">
       <c r="B122" s="12"/>
-      <c r="E122" s="161" t="s">
+      <c r="E122" s="160" t="s">
         <v>601</v>
       </c>
-      <c r="F122" s="117"/>
+      <c r="F122" s="116"/>
       <c r="G122" s="17"/>
       <c r="H122" s="9"/>
-      <c r="I122" s="153"/>
+      <c r="I122" s="152"/>
       <c r="J122" s="6"/>
       <c r="K122" s="6"/>
     </row>
@@ -8758,33 +8909,33 @@
       <c r="A123" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B123" s="154" t="s">
+      <c r="B123" s="153" t="s">
         <v>600</v>
       </c>
-      <c r="C123" s="154"/>
-      <c r="D123" s="155" t="s">
+      <c r="C123" s="153"/>
+      <c r="D123" s="154" t="s">
         <v>601</v>
       </c>
-      <c r="E123" s="156">
+      <c r="E123" s="155">
         <v>110</v>
       </c>
-      <c r="F123" s="156"/>
-      <c r="G123" s="157">
+      <c r="F123" s="155"/>
+      <c r="G123" s="156">
         <f t="shared" ref="G123:G127" si="40">E123*100</f>
         <v>11000</v>
       </c>
-      <c r="H123" s="158">
+      <c r="H123" s="157">
         <v>1100</v>
       </c>
-      <c r="I123" s="159">
+      <c r="I123" s="158">
         <f>H123/10</f>
         <v>110</v>
       </c>
-      <c r="J123" s="160">
+      <c r="J123" s="159">
         <f>H123/G123</f>
         <v>0.1</v>
       </c>
-      <c r="K123" s="160">
+      <c r="K123" s="159">
         <f>G123/H123</f>
         <v>10</v>
       </c>
@@ -8797,33 +8948,33 @@
       <c r="A124" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B124" s="154" t="s">
+      <c r="B124" s="153" t="s">
         <v>602</v>
       </c>
-      <c r="C124" s="154"/>
-      <c r="D124" s="155" t="s">
+      <c r="C124" s="153"/>
+      <c r="D124" s="154" t="s">
         <v>601</v>
       </c>
-      <c r="E124" s="156">
+      <c r="E124" s="155">
         <v>660</v>
       </c>
-      <c r="F124" s="156"/>
-      <c r="G124" s="157">
+      <c r="F124" s="155"/>
+      <c r="G124" s="156">
         <f t="shared" si="40"/>
         <v>66000</v>
       </c>
-      <c r="H124" s="158">
+      <c r="H124" s="157">
         <v>6600</v>
       </c>
-      <c r="I124" s="159">
+      <c r="I124" s="158">
         <f t="shared" ref="I124:I128" si="41">H124/10</f>
         <v>660</v>
       </c>
-      <c r="J124" s="160">
+      <c r="J124" s="159">
         <f t="shared" ref="J124:J126" si="42">H124/G124</f>
         <v>0.1</v>
       </c>
-      <c r="K124" s="160">
+      <c r="K124" s="159">
         <f t="shared" ref="K124:K126" si="43">G124/H124</f>
         <v>10</v>
       </c>
@@ -8836,33 +8987,33 @@
       <c r="A125" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B125" s="154" t="s">
+      <c r="B125" s="153" t="s">
         <v>603</v>
       </c>
-      <c r="C125" s="154"/>
-      <c r="D125" s="155" t="s">
+      <c r="C125" s="153"/>
+      <c r="D125" s="154" t="s">
         <v>601</v>
       </c>
-      <c r="E125" s="156">
+      <c r="E125" s="155">
         <v>1100</v>
       </c>
-      <c r="F125" s="156"/>
-      <c r="G125" s="157">
+      <c r="F125" s="155"/>
+      <c r="G125" s="156">
         <f t="shared" si="40"/>
         <v>110000</v>
       </c>
-      <c r="H125" s="158">
+      <c r="H125" s="157">
         <v>11000</v>
       </c>
-      <c r="I125" s="159">
+      <c r="I125" s="158">
         <f t="shared" si="41"/>
         <v>1100</v>
       </c>
-      <c r="J125" s="160">
+      <c r="J125" s="159">
         <f t="shared" si="42"/>
         <v>0.1</v>
       </c>
-      <c r="K125" s="160">
+      <c r="K125" s="159">
         <f t="shared" si="43"/>
         <v>10</v>
       </c>
@@ -8875,33 +9026,33 @@
       <c r="A126" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B126" s="154" t="s">
+      <c r="B126" s="153" t="s">
         <v>604</v>
       </c>
-      <c r="C126" s="154"/>
-      <c r="D126" s="155" t="s">
+      <c r="C126" s="153"/>
+      <c r="D126" s="154" t="s">
         <v>601</v>
       </c>
-      <c r="E126" s="156">
+      <c r="E126" s="155">
         <v>3300</v>
       </c>
-      <c r="F126" s="156"/>
-      <c r="G126" s="157">
+      <c r="F126" s="155"/>
+      <c r="G126" s="156">
         <f t="shared" si="40"/>
         <v>330000</v>
       </c>
-      <c r="H126" s="158">
+      <c r="H126" s="157">
         <v>33000</v>
       </c>
-      <c r="I126" s="159">
+      <c r="I126" s="158">
         <f t="shared" si="41"/>
         <v>3300</v>
       </c>
-      <c r="J126" s="160">
+      <c r="J126" s="159">
         <f t="shared" si="42"/>
         <v>0.1</v>
       </c>
-      <c r="K126" s="160">
+      <c r="K126" s="159">
         <f t="shared" si="43"/>
         <v>10</v>
       </c>
@@ -8914,33 +9065,33 @@
       <c r="A127" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B127" s="154" t="s">
+      <c r="B127" s="153" t="s">
         <v>605</v>
       </c>
-      <c r="C127" s="154"/>
-      <c r="D127" s="155" t="s">
+      <c r="C127" s="153"/>
+      <c r="D127" s="154" t="s">
         <v>601</v>
       </c>
-      <c r="E127" s="156">
+      <c r="E127" s="155">
         <v>5500</v>
       </c>
-      <c r="F127" s="156"/>
-      <c r="G127" s="157">
+      <c r="F127" s="155"/>
+      <c r="G127" s="156">
         <f t="shared" si="40"/>
         <v>550000</v>
       </c>
-      <c r="H127" s="158">
+      <c r="H127" s="157">
         <v>55000</v>
       </c>
-      <c r="I127" s="159">
+      <c r="I127" s="158">
         <f t="shared" si="41"/>
         <v>5500</v>
       </c>
-      <c r="J127" s="160">
+      <c r="J127" s="159">
         <f t="shared" ref="J127:J128" si="45">H127/G127</f>
         <v>0.1</v>
       </c>
-      <c r="K127" s="160">
+      <c r="K127" s="159">
         <f t="shared" ref="K127:K128" si="46">G127/H127</f>
         <v>10</v>
       </c>
@@ -8953,33 +9104,33 @@
       <c r="A128" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B128" s="154" t="s">
+      <c r="B128" s="153" t="s">
         <v>606</v>
       </c>
-      <c r="C128" s="154"/>
-      <c r="D128" s="155" t="s">
+      <c r="C128" s="153"/>
+      <c r="D128" s="154" t="s">
         <v>601</v>
       </c>
-      <c r="E128" s="156">
+      <c r="E128" s="155">
         <v>11000</v>
       </c>
-      <c r="F128" s="156"/>
-      <c r="G128" s="157">
+      <c r="F128" s="155"/>
+      <c r="G128" s="156">
         <f>E128*100</f>
         <v>1100000</v>
       </c>
-      <c r="H128" s="158">
+      <c r="H128" s="157">
         <v>110000</v>
       </c>
-      <c r="I128" s="159">
+      <c r="I128" s="158">
         <f t="shared" si="41"/>
         <v>11000</v>
       </c>
-      <c r="J128" s="160">
+      <c r="J128" s="159">
         <f t="shared" si="45"/>
         <v>0.1</v>
       </c>
-      <c r="K128" s="160">
+      <c r="K128" s="159">
         <f t="shared" si="46"/>
         <v>10</v>
       </c>
@@ -8999,8 +9150,8 @@
         <v>79</v>
       </c>
       <c r="C130" s="57"/>
-      <c r="E130" s="118"/>
-      <c r="F130" s="119"/>
+      <c r="E130" s="117"/>
+      <c r="F130" s="118"/>
       <c r="G130" s="21"/>
       <c r="L130" s="46"/>
     </row>
@@ -9015,10 +9166,10 @@
       <c r="D131" s="28" t="s">
         <v>359</v>
       </c>
-      <c r="E131" s="148">
+      <c r="E131" s="147">
         <v>1000</v>
       </c>
-      <c r="F131" s="120"/>
+      <c r="F131" s="119"/>
       <c r="G131" s="48">
         <f>F131+E131</f>
         <v>1000</v>
@@ -9039,10 +9190,10 @@
       <c r="D132" s="60" t="s">
         <v>459</v>
       </c>
-      <c r="E132" s="131">
+      <c r="E132" s="130">
         <v>3000</v>
       </c>
-      <c r="F132" s="137">
+      <c r="F132" s="136">
         <v>90</v>
       </c>
       <c r="G132" s="61">
@@ -9083,10 +9234,10 @@
       <c r="D133" s="60" t="s">
         <v>459</v>
       </c>
-      <c r="E133" s="131">
+      <c r="E133" s="130">
         <v>10000</v>
       </c>
-      <c r="F133" s="137">
+      <c r="F133" s="136">
         <v>400</v>
       </c>
       <c r="G133" s="61">
@@ -9127,10 +9278,10 @@
       <c r="D134" s="60" t="s">
         <v>459</v>
       </c>
-      <c r="E134" s="131">
+      <c r="E134" s="130">
         <v>18000</v>
       </c>
-      <c r="F134" s="137">
+      <c r="F134" s="136">
         <v>720</v>
       </c>
       <c r="G134" s="61">
@@ -9171,10 +9322,10 @@
       <c r="D135" s="28" t="s">
         <v>460</v>
       </c>
-      <c r="E135" s="148">
+      <c r="E135" s="147">
         <v>3000</v>
       </c>
-      <c r="F135" s="129">
+      <c r="F135" s="128">
         <v>60</v>
       </c>
       <c r="G135" s="48">
@@ -9215,10 +9366,10 @@
       <c r="D136" s="28" t="s">
         <v>460</v>
       </c>
-      <c r="E136" s="148">
+      <c r="E136" s="147">
         <v>11000</v>
       </c>
-      <c r="F136" s="129">
+      <c r="F136" s="128">
         <v>260</v>
       </c>
       <c r="G136" s="48">
@@ -9259,10 +9410,10 @@
       <c r="D137" s="28" t="s">
         <v>460</v>
       </c>
-      <c r="E137" s="148">
+      <c r="E137" s="147">
         <v>18000</v>
       </c>
-      <c r="F137" s="129">
+      <c r="F137" s="128">
         <v>480</v>
       </c>
       <c r="G137" s="48">
@@ -9303,10 +9454,10 @@
       <c r="D138" s="60" t="s">
         <v>461</v>
       </c>
-      <c r="E138" s="131">
+      <c r="E138" s="130">
         <v>2000</v>
       </c>
-      <c r="F138" s="137">
+      <c r="F138" s="136">
         <v>50</v>
       </c>
       <c r="G138" s="61">
@@ -9347,10 +9498,10 @@
       <c r="D139" s="60" t="s">
         <v>461</v>
       </c>
-      <c r="E139" s="131">
+      <c r="E139" s="130">
         <v>10000</v>
       </c>
-      <c r="F139" s="137">
+      <c r="F139" s="136">
         <v>200</v>
       </c>
       <c r="G139" s="61">
@@ -9391,10 +9542,10 @@
       <c r="D140" s="60" t="s">
         <v>461</v>
       </c>
-      <c r="E140" s="131">
+      <c r="E140" s="130">
         <v>18000</v>
       </c>
-      <c r="F140" s="137">
+      <c r="F140" s="136">
         <v>360</v>
       </c>
       <c r="G140" s="61">
@@ -9435,10 +9586,10 @@
       <c r="D141" s="28" t="s">
         <v>462</v>
       </c>
-      <c r="E141" s="148">
+      <c r="E141" s="147">
         <v>2000</v>
       </c>
-      <c r="F141" s="129">
+      <c r="F141" s="128">
         <v>25000</v>
       </c>
       <c r="G141" s="48">
@@ -9479,10 +9630,10 @@
       <c r="D142" s="28" t="s">
         <v>462</v>
       </c>
-      <c r="E142" s="148">
+      <c r="E142" s="147">
         <v>10000</v>
       </c>
-      <c r="F142" s="129">
+      <c r="F142" s="128">
         <v>125000</v>
       </c>
       <c r="G142" s="48">
@@ -9523,10 +9674,10 @@
       <c r="D143" s="28" t="s">
         <v>462</v>
       </c>
-      <c r="E143" s="148">
+      <c r="E143" s="147">
         <v>20000</v>
       </c>
-      <c r="F143" s="129">
+      <c r="F143" s="128">
         <v>250000</v>
       </c>
       <c r="G143" s="48">
@@ -9567,10 +9718,10 @@
       <c r="D144" s="60" t="s">
         <v>463</v>
       </c>
-      <c r="E144" s="131">
+      <c r="E144" s="130">
         <v>2000</v>
       </c>
-      <c r="F144" s="134">
+      <c r="F144" s="133">
         <v>35000</v>
       </c>
       <c r="G144" s="61">
@@ -9611,10 +9762,10 @@
       <c r="D145" s="60" t="s">
         <v>463</v>
       </c>
-      <c r="E145" s="131">
+      <c r="E145" s="130">
         <v>10000</v>
       </c>
-      <c r="F145" s="134">
+      <c r="F145" s="133">
         <v>170000</v>
       </c>
       <c r="G145" s="61">
@@ -9655,10 +9806,10 @@
       <c r="D146" s="60" t="s">
         <v>463</v>
       </c>
-      <c r="E146" s="131">
+      <c r="E146" s="130">
         <v>20000</v>
       </c>
-      <c r="F146" s="134">
+      <c r="F146" s="133">
         <v>350000</v>
       </c>
       <c r="G146" s="61">
@@ -9699,8 +9850,8 @@
       <c r="D147" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="E147" s="132"/>
-      <c r="F147" s="120">
+      <c r="E147" s="131"/>
+      <c r="F147" s="119">
         <v>1</v>
       </c>
       <c r="G147" s="48">
@@ -9741,8 +9892,8 @@
       <c r="D148" s="64" t="s">
         <v>360</v>
       </c>
-      <c r="E148" s="133"/>
-      <c r="F148" s="134">
+      <c r="E148" s="132"/>
+      <c r="F148" s="133">
         <v>1</v>
       </c>
       <c r="G148" s="61">
@@ -9797,8 +9948,8 @@
       <c r="D150" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="E150" s="135"/>
-      <c r="F150" s="136">
+      <c r="E150" s="134"/>
+      <c r="F150" s="135">
         <v>500</v>
       </c>
       <c r="G150" s="92">
@@ -9836,8 +9987,8 @@
       <c r="D151" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="E151" s="135"/>
-      <c r="F151" s="136">
+      <c r="E151" s="134"/>
+      <c r="F151" s="135">
         <v>1000</v>
       </c>
       <c r="G151" s="92">
@@ -9875,8 +10026,8 @@
       <c r="D152" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="E152" s="135"/>
-      <c r="F152" s="136">
+      <c r="E152" s="134"/>
+      <c r="F152" s="135">
         <v>500</v>
       </c>
       <c r="G152" s="92">
@@ -9914,8 +10065,8 @@
       <c r="D153" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="E153" s="135"/>
-      <c r="F153" s="136">
+      <c r="E153" s="134"/>
+      <c r="F153" s="135">
         <v>1000</v>
       </c>
       <c r="G153" s="92">
@@ -9953,10 +10104,10 @@
       <c r="D155" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="E155" s="148">
+      <c r="E155" s="147">
         <v>3000</v>
       </c>
-      <c r="F155" s="120"/>
+      <c r="F155" s="119"/>
       <c r="G155" s="48"/>
       <c r="H155" s="28"/>
       <c r="I155" s="28"/>
@@ -9974,10 +10125,10 @@
       <c r="D156" s="60" t="s">
         <v>459</v>
       </c>
-      <c r="E156" s="131">
+      <c r="E156" s="130">
         <v>30000</v>
       </c>
-      <c r="F156" s="137">
+      <c r="F156" s="136">
         <v>900</v>
       </c>
       <c r="G156" s="61">
@@ -10018,10 +10169,10 @@
       <c r="D157" s="60" t="s">
         <v>459</v>
       </c>
-      <c r="E157" s="131">
+      <c r="E157" s="130">
         <v>60000</v>
       </c>
-      <c r="F157" s="137">
+      <c r="F157" s="136">
         <v>2400</v>
       </c>
       <c r="G157" s="61">
@@ -10062,10 +10213,10 @@
       <c r="D158" s="60" t="s">
         <v>459</v>
       </c>
-      <c r="E158" s="131">
+      <c r="E158" s="130">
         <v>90000</v>
       </c>
-      <c r="F158" s="137">
+      <c r="F158" s="136">
         <v>3600</v>
       </c>
       <c r="G158" s="61">
@@ -10106,10 +10257,10 @@
       <c r="D159" s="28" t="s">
         <v>460</v>
       </c>
-      <c r="E159" s="148">
+      <c r="E159" s="147">
         <v>24000</v>
       </c>
-      <c r="F159" s="129">
+      <c r="F159" s="128">
         <v>600</v>
       </c>
       <c r="G159" s="48">
@@ -10150,10 +10301,10 @@
       <c r="D160" s="28" t="s">
         <v>460</v>
       </c>
-      <c r="E160" s="148">
+      <c r="E160" s="147">
         <v>60000</v>
       </c>
-      <c r="F160" s="129">
+      <c r="F160" s="128">
         <v>1600</v>
       </c>
       <c r="G160" s="48">
@@ -10194,10 +10345,10 @@
       <c r="D161" s="28" t="s">
         <v>460</v>
       </c>
-      <c r="E161" s="148">
+      <c r="E161" s="147">
         <v>90000</v>
       </c>
-      <c r="F161" s="129">
+      <c r="F161" s="128">
         <v>2400</v>
       </c>
       <c r="G161" s="48">
@@ -10238,10 +10389,10 @@
       <c r="D162" s="60" t="s">
         <v>461</v>
       </c>
-      <c r="E162" s="131">
+      <c r="E162" s="130">
         <v>20000</v>
       </c>
-      <c r="F162" s="137">
+      <c r="F162" s="136">
         <v>500</v>
       </c>
       <c r="G162" s="61">
@@ -10282,10 +10433,10 @@
       <c r="D163" s="60" t="s">
         <v>461</v>
       </c>
-      <c r="E163" s="131">
+      <c r="E163" s="130">
         <v>60000</v>
       </c>
-      <c r="F163" s="137">
+      <c r="F163" s="136">
         <v>1200</v>
       </c>
       <c r="G163" s="61">
@@ -10326,10 +10477,10 @@
       <c r="D164" s="60" t="s">
         <v>461</v>
       </c>
-      <c r="E164" s="131">
+      <c r="E164" s="130">
         <v>90000</v>
       </c>
-      <c r="F164" s="137">
+      <c r="F164" s="136">
         <v>1800</v>
       </c>
       <c r="G164" s="61">
@@ -10370,10 +10521,10 @@
       <c r="D165" s="28" t="s">
         <v>462</v>
       </c>
-      <c r="E165" s="148">
+      <c r="E165" s="147">
         <v>20000</v>
       </c>
-      <c r="F165" s="129">
+      <c r="F165" s="128">
         <v>250000</v>
       </c>
       <c r="G165" s="48">
@@ -10414,10 +10565,10 @@
       <c r="D166" s="28" t="s">
         <v>462</v>
       </c>
-      <c r="E166" s="148">
+      <c r="E166" s="147">
         <v>45000</v>
       </c>
-      <c r="F166" s="129">
+      <c r="F166" s="128">
         <v>800000</v>
       </c>
       <c r="G166" s="48">
@@ -10458,10 +10609,10 @@
       <c r="D167" s="28" t="s">
         <v>462</v>
       </c>
-      <c r="E167" s="148">
+      <c r="E167" s="147">
         <v>70000</v>
       </c>
-      <c r="F167" s="129">
+      <c r="F167" s="128">
         <v>1350000</v>
       </c>
       <c r="G167" s="48">
@@ -10502,10 +10653,10 @@
       <c r="D168" s="60" t="s">
         <v>463</v>
       </c>
-      <c r="E168" s="131">
+      <c r="E168" s="130">
         <v>20000</v>
       </c>
-      <c r="F168" s="137">
+      <c r="F168" s="136">
         <v>340000</v>
       </c>
       <c r="G168" s="61">
@@ -10546,14 +10697,14 @@
       <c r="D169" s="60" t="s">
         <v>463</v>
       </c>
-      <c r="E169" s="131">
+      <c r="E169" s="130">
         <v>45000</v>
       </c>
-      <c r="F169" s="137">
+      <c r="F169" s="136">
         <v>1100000</v>
       </c>
       <c r="G169" s="61">
-        <f t="shared" ref="G168:G170" si="77">0.25*F169+E169</f>
+        <f t="shared" ref="G169:G170" si="77">0.25*F169+E169</f>
         <v>320000</v>
       </c>
       <c r="H169" s="62">
@@ -10590,10 +10741,10 @@
       <c r="D170" s="60" t="s">
         <v>463</v>
       </c>
-      <c r="E170" s="131">
+      <c r="E170" s="130">
         <v>70000</v>
       </c>
-      <c r="F170" s="137">
+      <c r="F170" s="136">
         <v>1800000</v>
       </c>
       <c r="G170" s="61">
@@ -10634,8 +10785,8 @@
       <c r="D171" s="54" t="s">
         <v>363</v>
       </c>
-      <c r="E171" s="132"/>
-      <c r="F171" s="120">
+      <c r="E171" s="131"/>
+      <c r="F171" s="119">
         <v>2</v>
       </c>
       <c r="G171" s="48">
@@ -10676,8 +10827,8 @@
       <c r="D172" s="54" t="s">
         <v>363</v>
       </c>
-      <c r="E172" s="132"/>
-      <c r="F172" s="120">
+      <c r="E172" s="131"/>
+      <c r="F172" s="119">
         <v>3</v>
       </c>
       <c r="G172" s="48">
@@ -10718,8 +10869,8 @@
       <c r="D173" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="E173" s="131"/>
-      <c r="F173" s="130">
+      <c r="E173" s="130"/>
+      <c r="F173" s="129">
         <v>100000</v>
       </c>
       <c r="G173" s="80">
@@ -10760,8 +10911,8 @@
       <c r="D174" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="E174" s="131"/>
-      <c r="F174" s="130">
+      <c r="E174" s="130"/>
+      <c r="F174" s="129">
         <v>300000</v>
       </c>
       <c r="G174" s="80">
@@ -10802,8 +10953,8 @@
       <c r="D175" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="E175" s="131"/>
-      <c r="F175" s="130">
+      <c r="E175" s="130"/>
+      <c r="F175" s="129">
         <v>500000</v>
       </c>
       <c r="G175" s="80">
@@ -10844,8 +10995,8 @@
       <c r="D176" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="E176" s="131"/>
-      <c r="F176" s="130">
+      <c r="E176" s="130"/>
+      <c r="F176" s="129">
         <v>1000000</v>
       </c>
       <c r="G176" s="80">
@@ -10886,8 +11037,8 @@
       <c r="D177" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E177" s="129"/>
-      <c r="F177" s="120">
+      <c r="E177" s="128"/>
+      <c r="F177" s="119">
         <v>1000</v>
       </c>
       <c r="G177" s="48">
@@ -10928,8 +11079,8 @@
       <c r="D178" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E178" s="129"/>
-      <c r="F178" s="120">
+      <c r="E178" s="128"/>
+      <c r="F178" s="119">
         <v>3000</v>
       </c>
       <c r="G178" s="48">
@@ -10970,8 +11121,8 @@
       <c r="D179" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="E179" s="137"/>
-      <c r="F179" s="134">
+      <c r="E179" s="136"/>
+      <c r="F179" s="133">
         <v>1000</v>
       </c>
       <c r="G179" s="61">
@@ -11012,8 +11163,8 @@
       <c r="D180" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="E180" s="137"/>
-      <c r="F180" s="134">
+      <c r="E180" s="136"/>
+      <c r="F180" s="133">
         <v>3000</v>
       </c>
       <c r="G180" s="61">
@@ -11055,8 +11206,8 @@
         <v>82</v>
       </c>
       <c r="C182" s="57"/>
-      <c r="E182" s="118"/>
-      <c r="F182" s="119"/>
+      <c r="E182" s="117"/>
+      <c r="F182" s="118"/>
       <c r="G182" s="21"/>
       <c r="L182" s="46"/>
     </row>
@@ -11071,10 +11222,10 @@
       <c r="D183" s="78" t="s">
         <v>107</v>
       </c>
-      <c r="E183" s="131">
+      <c r="E183" s="130">
         <v>2800</v>
       </c>
-      <c r="F183" s="130"/>
+      <c r="F183" s="129"/>
       <c r="G183" s="80">
         <f>E183*25</f>
         <v>70000</v>
@@ -11110,10 +11261,10 @@
       <c r="D184" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="E184" s="131">
+      <c r="E184" s="130">
         <v>4000</v>
       </c>
-      <c r="F184" s="130"/>
+      <c r="F184" s="129"/>
       <c r="G184" s="80">
         <f t="shared" ref="G184:G202" si="84">E184*25</f>
         <v>100000</v>
@@ -11149,10 +11300,10 @@
       <c r="D185" s="78" t="s">
         <v>109</v>
       </c>
-      <c r="E185" s="131">
+      <c r="E185" s="130">
         <v>5600</v>
       </c>
-      <c r="F185" s="130"/>
+      <c r="F185" s="129"/>
       <c r="G185" s="80">
         <f t="shared" si="84"/>
         <v>140000</v>
@@ -11188,10 +11339,10 @@
       <c r="D186" s="78" t="s">
         <v>110</v>
       </c>
-      <c r="E186" s="131">
+      <c r="E186" s="130">
         <v>11200</v>
       </c>
-      <c r="F186" s="130"/>
+      <c r="F186" s="129"/>
       <c r="G186" s="80">
         <f t="shared" si="84"/>
         <v>280000</v>
@@ -11227,10 +11378,10 @@
       <c r="D187" s="78" t="s">
         <v>111</v>
       </c>
-      <c r="E187" s="131">
+      <c r="E187" s="130">
         <v>17000</v>
       </c>
-      <c r="F187" s="130"/>
+      <c r="F187" s="129"/>
       <c r="G187" s="80">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11266,10 +11417,10 @@
       <c r="D188" s="78" t="s">
         <v>112</v>
       </c>
-      <c r="E188" s="131">
+      <c r="E188" s="130">
         <v>17000</v>
       </c>
-      <c r="F188" s="130"/>
+      <c r="F188" s="129"/>
       <c r="G188" s="80">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11305,10 +11456,10 @@
       <c r="D189" s="78" t="s">
         <v>113</v>
       </c>
-      <c r="E189" s="131">
+      <c r="E189" s="130">
         <v>17000</v>
       </c>
-      <c r="F189" s="130"/>
+      <c r="F189" s="129"/>
       <c r="G189" s="80">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11344,10 +11495,10 @@
       <c r="D190" s="78" t="s">
         <v>114</v>
       </c>
-      <c r="E190" s="131">
+      <c r="E190" s="130">
         <v>17000</v>
       </c>
-      <c r="F190" s="130"/>
+      <c r="F190" s="129"/>
       <c r="G190" s="80">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11383,10 +11534,10 @@
       <c r="D191" s="78" t="s">
         <v>365</v>
       </c>
-      <c r="E191" s="131">
+      <c r="E191" s="130">
         <v>17000</v>
       </c>
-      <c r="F191" s="130"/>
+      <c r="F191" s="129"/>
       <c r="G191" s="80">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11422,10 +11573,10 @@
       <c r="D192" s="78" t="s">
         <v>366</v>
       </c>
-      <c r="E192" s="131">
+      <c r="E192" s="130">
         <v>17000</v>
       </c>
-      <c r="F192" s="130"/>
+      <c r="F192" s="129"/>
       <c r="G192" s="80">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11461,10 +11612,10 @@
       <c r="D193" s="90" t="s">
         <v>394</v>
       </c>
-      <c r="E193" s="135">
+      <c r="E193" s="134">
         <v>17000</v>
       </c>
-      <c r="F193" s="136"/>
+      <c r="F193" s="135"/>
       <c r="G193" s="92">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11497,10 +11648,10 @@
       <c r="D194" s="90" t="s">
         <v>396</v>
       </c>
-      <c r="E194" s="135">
+      <c r="E194" s="134">
         <v>17000</v>
       </c>
-      <c r="F194" s="136"/>
+      <c r="F194" s="135"/>
       <c r="G194" s="92">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11533,10 +11684,10 @@
       <c r="D195" s="90" t="s">
         <v>398</v>
       </c>
-      <c r="E195" s="135">
+      <c r="E195" s="134">
         <v>17000</v>
       </c>
-      <c r="F195" s="136"/>
+      <c r="F195" s="135"/>
       <c r="G195" s="92">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11569,10 +11720,10 @@
       <c r="D196" s="90" t="s">
         <v>400</v>
       </c>
-      <c r="E196" s="135">
+      <c r="E196" s="134">
         <v>17000</v>
       </c>
-      <c r="F196" s="136"/>
+      <c r="F196" s="135"/>
       <c r="G196" s="92">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11605,10 +11756,10 @@
       <c r="D197" s="90" t="s">
         <v>402</v>
       </c>
-      <c r="E197" s="135">
+      <c r="E197" s="134">
         <v>17000</v>
       </c>
-      <c r="F197" s="136"/>
+      <c r="F197" s="135"/>
       <c r="G197" s="92">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11641,10 +11792,10 @@
       <c r="D198" s="90" t="s">
         <v>404</v>
       </c>
-      <c r="E198" s="135">
+      <c r="E198" s="134">
         <v>17000</v>
       </c>
-      <c r="F198" s="136"/>
+      <c r="F198" s="135"/>
       <c r="G198" s="92">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11677,10 +11828,10 @@
       <c r="D199" s="90" t="s">
         <v>406</v>
       </c>
-      <c r="E199" s="135">
+      <c r="E199" s="134">
         <v>17000</v>
       </c>
-      <c r="F199" s="136"/>
+      <c r="F199" s="135"/>
       <c r="G199" s="92">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11713,10 +11864,10 @@
       <c r="D200" s="90" t="s">
         <v>408</v>
       </c>
-      <c r="E200" s="135">
+      <c r="E200" s="134">
         <v>17000</v>
       </c>
-      <c r="F200" s="136"/>
+      <c r="F200" s="135"/>
       <c r="G200" s="92">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11749,10 +11900,10 @@
       <c r="D201" s="90" t="s">
         <v>410</v>
       </c>
-      <c r="E201" s="135">
+      <c r="E201" s="134">
         <v>17000</v>
       </c>
-      <c r="F201" s="136"/>
+      <c r="F201" s="135"/>
       <c r="G201" s="92">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11785,10 +11936,10 @@
       <c r="D202" s="90" t="s">
         <v>412</v>
       </c>
-      <c r="E202" s="135">
+      <c r="E202" s="134">
         <v>17000</v>
       </c>
-      <c r="F202" s="136"/>
+      <c r="F202" s="135"/>
       <c r="G202" s="92">
         <f t="shared" si="84"/>
         <v>425000</v>
@@ -11832,10 +11983,10 @@
       <c r="D204" s="78" t="s">
         <v>93</v>
       </c>
-      <c r="E204" s="131">
+      <c r="E204" s="130">
         <v>2800</v>
       </c>
-      <c r="F204" s="130"/>
+      <c r="F204" s="129"/>
       <c r="G204" s="80">
         <f>E204*25</f>
         <v>70000</v>
@@ -11871,10 +12022,10 @@
       <c r="D205" s="78" t="s">
         <v>92</v>
       </c>
-      <c r="E205" s="131">
+      <c r="E205" s="130">
         <v>4000</v>
       </c>
-      <c r="F205" s="130"/>
+      <c r="F205" s="129"/>
       <c r="G205" s="80">
         <f t="shared" ref="G205:G223" si="91">E205*25</f>
         <v>100000</v>
@@ -11910,10 +12061,10 @@
       <c r="D206" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="E206" s="131">
+      <c r="E206" s="130">
         <v>5600</v>
       </c>
-      <c r="F206" s="130"/>
+      <c r="F206" s="129"/>
       <c r="G206" s="80">
         <f t="shared" si="91"/>
         <v>140000</v>
@@ -11949,10 +12100,10 @@
       <c r="D207" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="E207" s="131">
+      <c r="E207" s="130">
         <v>11200</v>
       </c>
-      <c r="F207" s="130"/>
+      <c r="F207" s="129"/>
       <c r="G207" s="80">
         <f t="shared" si="91"/>
         <v>280000</v>
@@ -11988,10 +12139,10 @@
       <c r="D208" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="E208" s="131">
+      <c r="E208" s="130">
         <v>17000</v>
       </c>
-      <c r="F208" s="130"/>
+      <c r="F208" s="129"/>
       <c r="G208" s="80">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12027,10 +12178,10 @@
       <c r="D209" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="E209" s="131">
+      <c r="E209" s="130">
         <v>17000</v>
       </c>
-      <c r="F209" s="130"/>
+      <c r="F209" s="129"/>
       <c r="G209" s="80">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12066,10 +12217,10 @@
       <c r="D210" s="78" t="s">
         <v>98</v>
       </c>
-      <c r="E210" s="131">
+      <c r="E210" s="130">
         <v>17000</v>
       </c>
-      <c r="F210" s="130"/>
+      <c r="F210" s="129"/>
       <c r="G210" s="80">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12105,10 +12256,10 @@
       <c r="D211" s="78" t="s">
         <v>393</v>
       </c>
-      <c r="E211" s="131">
+      <c r="E211" s="130">
         <v>17000</v>
       </c>
-      <c r="F211" s="130"/>
+      <c r="F211" s="129"/>
       <c r="G211" s="80">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12144,10 +12295,10 @@
       <c r="D212" s="78" t="s">
         <v>389</v>
       </c>
-      <c r="E212" s="131">
+      <c r="E212" s="130">
         <v>17000</v>
       </c>
-      <c r="F212" s="130"/>
+      <c r="F212" s="129"/>
       <c r="G212" s="80">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12183,10 +12334,10 @@
       <c r="D213" s="78" t="s">
         <v>391</v>
       </c>
-      <c r="E213" s="131">
+      <c r="E213" s="130">
         <v>17000</v>
       </c>
-      <c r="F213" s="130"/>
+      <c r="F213" s="129"/>
       <c r="G213" s="80">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12222,10 +12373,10 @@
       <c r="D214" s="90" t="s">
         <v>413</v>
       </c>
-      <c r="E214" s="135">
+      <c r="E214" s="134">
         <v>17000</v>
       </c>
-      <c r="F214" s="136"/>
+      <c r="F214" s="135"/>
       <c r="G214" s="92">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12258,10 +12409,10 @@
       <c r="D215" s="90" t="s">
         <v>415</v>
       </c>
-      <c r="E215" s="135">
+      <c r="E215" s="134">
         <v>17000</v>
       </c>
-      <c r="F215" s="136"/>
+      <c r="F215" s="135"/>
       <c r="G215" s="92">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12294,10 +12445,10 @@
       <c r="D216" s="90" t="s">
         <v>417</v>
       </c>
-      <c r="E216" s="135">
+      <c r="E216" s="134">
         <v>17000</v>
       </c>
-      <c r="F216" s="136"/>
+      <c r="F216" s="135"/>
       <c r="G216" s="92">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12330,10 +12481,10 @@
       <c r="D217" s="90" t="s">
         <v>419</v>
       </c>
-      <c r="E217" s="135">
+      <c r="E217" s="134">
         <v>17000</v>
       </c>
-      <c r="F217" s="136"/>
+      <c r="F217" s="135"/>
       <c r="G217" s="92">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12366,10 +12517,10 @@
       <c r="D218" s="90" t="s">
         <v>421</v>
       </c>
-      <c r="E218" s="135">
+      <c r="E218" s="134">
         <v>17000</v>
       </c>
-      <c r="F218" s="136"/>
+      <c r="F218" s="135"/>
       <c r="G218" s="92">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12402,10 +12553,10 @@
       <c r="D219" s="90" t="s">
         <v>423</v>
       </c>
-      <c r="E219" s="135">
+      <c r="E219" s="134">
         <v>17000</v>
       </c>
-      <c r="F219" s="136"/>
+      <c r="F219" s="135"/>
       <c r="G219" s="92">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12438,10 +12589,10 @@
       <c r="D220" s="90" t="s">
         <v>425</v>
       </c>
-      <c r="E220" s="135">
+      <c r="E220" s="134">
         <v>17000</v>
       </c>
-      <c r="F220" s="136"/>
+      <c r="F220" s="135"/>
       <c r="G220" s="92">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12474,10 +12625,10 @@
       <c r="D221" s="90" t="s">
         <v>427</v>
       </c>
-      <c r="E221" s="135">
+      <c r="E221" s="134">
         <v>17000</v>
       </c>
-      <c r="F221" s="136"/>
+      <c r="F221" s="135"/>
       <c r="G221" s="92">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12510,10 +12661,10 @@
       <c r="D222" s="90" t="s">
         <v>429</v>
       </c>
-      <c r="E222" s="135">
+      <c r="E222" s="134">
         <v>17000</v>
       </c>
-      <c r="F222" s="136"/>
+      <c r="F222" s="135"/>
       <c r="G222" s="92">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12546,10 +12697,10 @@
       <c r="D223" s="90" t="s">
         <v>431</v>
       </c>
-      <c r="E223" s="135">
+      <c r="E223" s="134">
         <v>17000</v>
       </c>
-      <c r="F223" s="136"/>
+      <c r="F223" s="135"/>
       <c r="G223" s="92">
         <f t="shared" si="91"/>
         <v>425000</v>
@@ -12595,10 +12746,10 @@
       <c r="D225" s="78" t="s">
         <v>434</v>
       </c>
-      <c r="E225" s="131">
+      <c r="E225" s="130">
         <v>2800</v>
       </c>
-      <c r="F225" s="130"/>
+      <c r="F225" s="129"/>
       <c r="G225" s="80">
         <f>E225*25</f>
         <v>70000</v>
@@ -12637,10 +12788,10 @@
       <c r="D226" s="78" t="s">
         <v>434</v>
       </c>
-      <c r="E226" s="131">
+      <c r="E226" s="130">
         <v>4000</v>
       </c>
-      <c r="F226" s="130"/>
+      <c r="F226" s="129"/>
       <c r="G226" s="80">
         <f t="shared" ref="G226:G239" si="97">E226*25</f>
         <v>100000</v>
@@ -12679,10 +12830,10 @@
       <c r="D227" s="78" t="s">
         <v>433</v>
       </c>
-      <c r="E227" s="131">
+      <c r="E227" s="130">
         <v>5600</v>
       </c>
-      <c r="F227" s="130"/>
+      <c r="F227" s="129"/>
       <c r="G227" s="80">
         <f t="shared" si="97"/>
         <v>140000</v>
@@ -12721,10 +12872,10 @@
       <c r="D228" s="78" t="s">
         <v>433</v>
       </c>
-      <c r="E228" s="131">
+      <c r="E228" s="130">
         <v>11200</v>
       </c>
-      <c r="F228" s="130"/>
+      <c r="F228" s="129"/>
       <c r="G228" s="80">
         <f t="shared" si="97"/>
         <v>280000</v>
@@ -12763,10 +12914,10 @@
       <c r="D229" s="78" t="s">
         <v>433</v>
       </c>
-      <c r="E229" s="131">
+      <c r="E229" s="130">
         <v>17000</v>
       </c>
-      <c r="F229" s="130"/>
+      <c r="F229" s="129"/>
       <c r="G229" s="80">
         <f t="shared" si="97"/>
         <v>425000</v>
@@ -12805,10 +12956,10 @@
       <c r="D230" s="78" t="s">
         <v>433</v>
       </c>
-      <c r="E230" s="131">
+      <c r="E230" s="130">
         <v>17000</v>
       </c>
-      <c r="F230" s="130"/>
+      <c r="F230" s="129"/>
       <c r="G230" s="80">
         <f t="shared" si="97"/>
         <v>425000</v>
@@ -12847,10 +12998,10 @@
       <c r="D231" s="78" t="s">
         <v>433</v>
       </c>
-      <c r="E231" s="131">
+      <c r="E231" s="130">
         <v>17000</v>
       </c>
-      <c r="F231" s="130"/>
+      <c r="F231" s="129"/>
       <c r="G231" s="80">
         <f t="shared" si="97"/>
         <v>425000</v>
@@ -12889,10 +13040,10 @@
       <c r="D232" s="78" t="s">
         <v>433</v>
       </c>
-      <c r="E232" s="131">
+      <c r="E232" s="130">
         <v>17000</v>
       </c>
-      <c r="F232" s="130"/>
+      <c r="F232" s="129"/>
       <c r="G232" s="80">
         <f t="shared" si="97"/>
         <v>425000</v>
@@ -12931,10 +13082,10 @@
       <c r="D233" s="78" t="s">
         <v>433</v>
       </c>
-      <c r="E233" s="131">
+      <c r="E233" s="130">
         <v>17000</v>
       </c>
-      <c r="F233" s="130"/>
+      <c r="F233" s="129"/>
       <c r="G233" s="80">
         <f t="shared" si="97"/>
         <v>425000</v>
@@ -12973,10 +13124,10 @@
       <c r="D234" s="78" t="s">
         <v>433</v>
       </c>
-      <c r="E234" s="131">
+      <c r="E234" s="130">
         <v>17000</v>
       </c>
-      <c r="F234" s="130"/>
+      <c r="F234" s="129"/>
       <c r="G234" s="80">
         <f t="shared" si="97"/>
         <v>425000</v>
@@ -13015,10 +13166,10 @@
       <c r="D235" s="78" t="s">
         <v>433</v>
       </c>
-      <c r="E235" s="131">
+      <c r="E235" s="130">
         <v>17000</v>
       </c>
-      <c r="F235" s="130"/>
+      <c r="F235" s="129"/>
       <c r="G235" s="80">
         <f t="shared" si="97"/>
         <v>425000</v>
@@ -13057,10 +13208,10 @@
       <c r="D236" s="78" t="s">
         <v>433</v>
       </c>
-      <c r="E236" s="131">
+      <c r="E236" s="130">
         <v>17000</v>
       </c>
-      <c r="F236" s="130"/>
+      <c r="F236" s="129"/>
       <c r="G236" s="80">
         <f t="shared" si="97"/>
         <v>425000</v>
@@ -13099,10 +13250,10 @@
       <c r="D237" s="78" t="s">
         <v>433</v>
       </c>
-      <c r="E237" s="131">
+      <c r="E237" s="130">
         <v>17000</v>
       </c>
-      <c r="F237" s="130"/>
+      <c r="F237" s="129"/>
       <c r="G237" s="80">
         <f t="shared" si="97"/>
         <v>425000</v>
@@ -13141,10 +13292,10 @@
       <c r="D238" s="78" t="s">
         <v>433</v>
       </c>
-      <c r="E238" s="131">
+      <c r="E238" s="130">
         <v>17000</v>
       </c>
-      <c r="F238" s="130"/>
+      <c r="F238" s="129"/>
       <c r="G238" s="80">
         <f t="shared" si="97"/>
         <v>425000</v>
@@ -13183,10 +13334,10 @@
       <c r="D239" s="78" t="s">
         <v>433</v>
       </c>
-      <c r="E239" s="131">
+      <c r="E239" s="130">
         <v>17000</v>
       </c>
-      <c r="F239" s="130"/>
+      <c r="F239" s="129"/>
       <c r="G239" s="80">
         <f t="shared" si="97"/>
         <v>425000</v>
@@ -13213,7 +13364,7 @@
     </row>
     <row r="240" spans="1:12">
       <c r="B240" s="12"/>
-      <c r="F240" s="117"/>
+      <c r="F240" s="116"/>
       <c r="G240" s="17"/>
       <c r="H240" s="9"/>
       <c r="I240" s="9"/>
@@ -13233,10 +13384,10 @@
       <c r="D241" s="78" t="s">
         <v>440</v>
       </c>
-      <c r="E241" s="131">
+      <c r="E241" s="130">
         <v>2800</v>
       </c>
-      <c r="F241" s="130"/>
+      <c r="F241" s="129"/>
       <c r="G241" s="80">
         <f>E241*25</f>
         <v>70000</v>
@@ -13274,10 +13425,10 @@
       <c r="D242" s="78" t="s">
         <v>440</v>
       </c>
-      <c r="E242" s="131">
+      <c r="E242" s="130">
         <v>4000</v>
       </c>
-      <c r="F242" s="130"/>
+      <c r="F242" s="129"/>
       <c r="G242" s="80">
         <f t="shared" ref="G242:G250" si="102">E242*25</f>
         <v>100000</v>
@@ -13315,10 +13466,10 @@
       <c r="D243" s="78" t="s">
         <v>440</v>
       </c>
-      <c r="E243" s="131">
+      <c r="E243" s="130">
         <v>5600</v>
       </c>
-      <c r="F243" s="130"/>
+      <c r="F243" s="129"/>
       <c r="G243" s="80">
         <f t="shared" si="102"/>
         <v>140000</v>
@@ -13356,10 +13507,10 @@
       <c r="D244" s="78" t="s">
         <v>440</v>
       </c>
-      <c r="E244" s="131">
+      <c r="E244" s="130">
         <v>11200</v>
       </c>
-      <c r="F244" s="130"/>
+      <c r="F244" s="129"/>
       <c r="G244" s="80">
         <f t="shared" si="102"/>
         <v>280000</v>
@@ -13397,10 +13548,10 @@
       <c r="D245" s="78" t="s">
         <v>440</v>
       </c>
-      <c r="E245" s="131">
+      <c r="E245" s="130">
         <v>17000</v>
       </c>
-      <c r="F245" s="130"/>
+      <c r="F245" s="129"/>
       <c r="G245" s="80">
         <f t="shared" si="102"/>
         <v>425000</v>
@@ -13438,10 +13589,10 @@
       <c r="D246" s="78" t="s">
         <v>440</v>
       </c>
-      <c r="E246" s="131">
+      <c r="E246" s="130">
         <v>17000</v>
       </c>
-      <c r="F246" s="130"/>
+      <c r="F246" s="129"/>
       <c r="G246" s="80">
         <f t="shared" si="102"/>
         <v>425000</v>
@@ -13479,10 +13630,10 @@
       <c r="D247" s="78" t="s">
         <v>440</v>
       </c>
-      <c r="E247" s="131">
+      <c r="E247" s="130">
         <v>17000</v>
       </c>
-      <c r="F247" s="130"/>
+      <c r="F247" s="129"/>
       <c r="G247" s="80">
         <f t="shared" si="102"/>
         <v>425000</v>
@@ -13520,10 +13671,10 @@
       <c r="D248" s="78" t="s">
         <v>440</v>
       </c>
-      <c r="E248" s="131">
+      <c r="E248" s="130">
         <v>17000</v>
       </c>
-      <c r="F248" s="130"/>
+      <c r="F248" s="129"/>
       <c r="G248" s="80">
         <f t="shared" si="102"/>
         <v>425000</v>
@@ -13561,10 +13712,10 @@
       <c r="D249" s="78" t="s">
         <v>440</v>
       </c>
-      <c r="E249" s="131">
+      <c r="E249" s="130">
         <v>17000</v>
       </c>
-      <c r="F249" s="130"/>
+      <c r="F249" s="129"/>
       <c r="G249" s="80">
         <f t="shared" si="102"/>
         <v>425000</v>
@@ -13602,10 +13753,10 @@
       <c r="D250" s="78" t="s">
         <v>440</v>
       </c>
-      <c r="E250" s="131">
+      <c r="E250" s="130">
         <v>17000</v>
       </c>
-      <c r="F250" s="130"/>
+      <c r="F250" s="129"/>
       <c r="G250" s="80">
         <f t="shared" si="102"/>
         <v>425000</v>
@@ -13642,8 +13793,8 @@
         <v>609</v>
       </c>
       <c r="C252" s="57"/>
-      <c r="E252" s="118"/>
-      <c r="F252" s="119"/>
+      <c r="E252" s="117"/>
+      <c r="F252" s="118"/>
       <c r="G252" s="21"/>
       <c r="L252" s="46"/>
     </row>
@@ -13654,11 +13805,11 @@
       <c r="B253" s="28" t="s">
         <v>447</v>
       </c>
-      <c r="D253" s="177" t="s">
+      <c r="D253" s="176" t="s">
         <v>443</v>
       </c>
-      <c r="E253" s="138"/>
-      <c r="F253" s="120">
+      <c r="E253" s="137"/>
+      <c r="F253" s="119">
         <v>1000000</v>
       </c>
       <c r="G253" s="48">
@@ -13689,8 +13840,8 @@
       <c r="B254" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D254" s="177"/>
-      <c r="F254" s="117"/>
+      <c r="D254" s="176"/>
+      <c r="F254" s="116"/>
       <c r="G254" s="17"/>
       <c r="H254" s="9"/>
       <c r="I254" s="9"/>
@@ -13698,8 +13849,8 @@
       <c r="K254" s="6"/>
     </row>
     <row r="255" spans="1:12">
-      <c r="D255" s="177"/>
-      <c r="F255" s="117"/>
+      <c r="D255" s="176"/>
+      <c r="F255" s="116"/>
       <c r="G255" s="17"/>
       <c r="H255" s="9"/>
       <c r="I255" s="9"/>
@@ -13716,11 +13867,11 @@
       <c r="B257" s="28" t="s">
         <v>444</v>
       </c>
-      <c r="D257" s="177" t="s">
+      <c r="D257" s="176" t="s">
         <v>501</v>
       </c>
-      <c r="E257" s="138"/>
-      <c r="F257" s="120">
+      <c r="E257" s="137"/>
+      <c r="F257" s="119">
         <v>360000</v>
       </c>
       <c r="G257" s="48">
@@ -13751,16 +13902,16 @@
       <c r="B258" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="D258" s="177"/>
-      <c r="E258" s="138"/>
+      <c r="D258" s="176"/>
+      <c r="E258" s="137"/>
     </row>
     <row r="259" spans="1:13">
-      <c r="D259" s="177"/>
-      <c r="E259" s="138"/>
+      <c r="D259" s="176"/>
+      <c r="E259" s="137"/>
     </row>
     <row r="260" spans="1:13" ht="13.5" customHeight="1">
-      <c r="D260" s="177"/>
-      <c r="E260" s="138"/>
+      <c r="D260" s="176"/>
+      <c r="E260" s="137"/>
     </row>
     <row r="261" spans="1:13">
       <c r="D261" s="51"/>
@@ -13772,11 +13923,11 @@
       <c r="B262" s="28" t="s">
         <v>445</v>
       </c>
-      <c r="D262" s="177" t="s">
+      <c r="D262" s="176" t="s">
         <v>442</v>
       </c>
-      <c r="E262" s="138"/>
-      <c r="F262" s="120">
+      <c r="E262" s="137"/>
+      <c r="F262" s="119">
         <v>400000</v>
       </c>
       <c r="G262" s="48">
@@ -13807,24 +13958,24 @@
       <c r="B263" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="D263" s="177"/>
-      <c r="E263" s="138"/>
+      <c r="D263" s="176"/>
+      <c r="E263" s="137"/>
     </row>
     <row r="264" spans="1:13">
-      <c r="D264" s="177"/>
-      <c r="E264" s="138"/>
+      <c r="D264" s="176"/>
+      <c r="E264" s="137"/>
     </row>
     <row r="265" spans="1:13">
-      <c r="D265" s="177"/>
-      <c r="E265" s="138"/>
+      <c r="D265" s="176"/>
+      <c r="E265" s="137"/>
     </row>
     <row r="267" spans="1:13" s="55" customFormat="1">
       <c r="B267" s="56" t="s">
         <v>106</v>
       </c>
       <c r="C267" s="57"/>
-      <c r="E267" s="118"/>
-      <c r="F267" s="119"/>
+      <c r="E267" s="117"/>
+      <c r="F267" s="118"/>
       <c r="G267" s="21"/>
       <c r="L267" s="46"/>
     </row>
@@ -13834,43 +13985,43 @@
       </c>
       <c r="C268" s="10"/>
       <c r="D268" s="25"/>
-      <c r="E268" s="139"/>
-      <c r="F268" s="117"/>
+      <c r="E268" s="138"/>
+      <c r="F268" s="116"/>
       <c r="G268" s="17"/>
     </row>
     <row r="269" spans="1:13">
       <c r="A269" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B269" s="164" t="s">
+      <c r="B269" s="163" t="s">
         <v>133</v>
       </c>
-      <c r="C269" s="165" t="s">
+      <c r="C269" s="164" t="s">
         <v>154</v>
       </c>
-      <c r="D269" s="175" t="s">
+      <c r="D269" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="E269" s="176">
+      <c r="E269" s="175">
         <v>80000</v>
       </c>
-      <c r="F269" s="176"/>
-      <c r="G269" s="173">
+      <c r="F269" s="175"/>
+      <c r="G269" s="172">
         <f t="shared" ref="G269:G288" si="104">E269</f>
         <v>80000</v>
       </c>
-      <c r="H269" s="168">
+      <c r="H269" s="167">
         <v>5500</v>
       </c>
-      <c r="I269" s="169">
+      <c r="I269" s="168">
         <f t="shared" ref="I269:I288" si="105">H269/10</f>
         <v>550</v>
       </c>
-      <c r="J269" s="174">
+      <c r="J269" s="173">
         <f t="shared" ref="J269:J288" si="106">H269/G269</f>
         <v>6.8750000000000006E-2</v>
       </c>
-      <c r="K269" s="174">
+      <c r="K269" s="173">
         <f t="shared" ref="K269:K288" si="107">G269/H269</f>
         <v>14.545454545454545</v>
       </c>
@@ -13895,10 +14046,10 @@
       <c r="D270" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E270" s="130">
+      <c r="E270" s="129">
         <v>160000</v>
       </c>
-      <c r="F270" s="130"/>
+      <c r="F270" s="129"/>
       <c r="G270" s="80">
         <f t="shared" si="104"/>
         <v>160000</v>
@@ -13939,10 +14090,10 @@
       <c r="D271" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E271" s="130">
+      <c r="E271" s="129">
         <v>480000</v>
       </c>
-      <c r="F271" s="130"/>
+      <c r="F271" s="129"/>
       <c r="G271" s="80">
         <f t="shared" si="104"/>
         <v>480000</v>
@@ -13983,10 +14134,10 @@
       <c r="D272" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E272" s="130">
+      <c r="E272" s="129">
         <v>800000</v>
       </c>
-      <c r="F272" s="130"/>
+      <c r="F272" s="129"/>
       <c r="G272" s="80">
         <f t="shared" si="104"/>
         <v>800000</v>
@@ -14027,10 +14178,10 @@
       <c r="D273" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E273" s="130">
+      <c r="E273" s="129">
         <v>80000</v>
       </c>
-      <c r="F273" s="130"/>
+      <c r="F273" s="129"/>
       <c r="G273" s="80">
         <f t="shared" si="104"/>
         <v>80000</v>
@@ -14071,10 +14222,10 @@
       <c r="D274" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E274" s="130">
+      <c r="E274" s="129">
         <v>160000</v>
       </c>
-      <c r="F274" s="130"/>
+      <c r="F274" s="129"/>
       <c r="G274" s="80">
         <f t="shared" si="104"/>
         <v>160000</v>
@@ -14115,10 +14266,10 @@
       <c r="D275" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E275" s="130">
+      <c r="E275" s="129">
         <v>480000</v>
       </c>
-      <c r="F275" s="130"/>
+      <c r="F275" s="129"/>
       <c r="G275" s="80">
         <f t="shared" si="104"/>
         <v>480000</v>
@@ -14159,10 +14310,10 @@
       <c r="D276" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E276" s="130">
+      <c r="E276" s="129">
         <v>800000</v>
       </c>
-      <c r="F276" s="130"/>
+      <c r="F276" s="129"/>
       <c r="G276" s="80">
         <f t="shared" si="104"/>
         <v>800000</v>
@@ -14203,10 +14354,10 @@
       <c r="D277" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E277" s="130">
+      <c r="E277" s="129">
         <v>1600000</v>
       </c>
-      <c r="F277" s="130"/>
+      <c r="F277" s="129"/>
       <c r="G277" s="80">
         <f t="shared" si="104"/>
         <v>1600000</v>
@@ -14247,10 +14398,10 @@
       <c r="D278" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E278" s="130">
+      <c r="E278" s="129">
         <v>160000</v>
       </c>
-      <c r="F278" s="130"/>
+      <c r="F278" s="129"/>
       <c r="G278" s="80">
         <f t="shared" si="104"/>
         <v>160000</v>
@@ -14291,10 +14442,10 @@
       <c r="D279" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E279" s="130">
+      <c r="E279" s="129">
         <v>480000</v>
       </c>
-      <c r="F279" s="130"/>
+      <c r="F279" s="129"/>
       <c r="G279" s="80">
         <f t="shared" si="104"/>
         <v>480000</v>
@@ -14335,10 +14486,10 @@
       <c r="D280" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E280" s="130">
+      <c r="E280" s="129">
         <v>800000</v>
       </c>
-      <c r="F280" s="130"/>
+      <c r="F280" s="129"/>
       <c r="G280" s="80">
         <f t="shared" si="104"/>
         <v>800000</v>
@@ -14379,10 +14530,10 @@
       <c r="D281" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E281" s="130">
+      <c r="E281" s="129">
         <v>1600000</v>
       </c>
-      <c r="F281" s="130"/>
+      <c r="F281" s="129"/>
       <c r="G281" s="80">
         <f t="shared" si="104"/>
         <v>1600000</v>
@@ -14423,10 +14574,10 @@
       <c r="D282" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E282" s="130">
+      <c r="E282" s="129">
         <v>160000</v>
       </c>
-      <c r="F282" s="130"/>
+      <c r="F282" s="129"/>
       <c r="G282" s="80">
         <f t="shared" si="104"/>
         <v>160000</v>
@@ -14467,10 +14618,10 @@
       <c r="D283" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E283" s="130">
+      <c r="E283" s="129">
         <v>480000</v>
       </c>
-      <c r="F283" s="130"/>
+      <c r="F283" s="129"/>
       <c r="G283" s="80">
         <f t="shared" si="104"/>
         <v>480000</v>
@@ -14511,10 +14662,10 @@
       <c r="D284" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E284" s="130">
+      <c r="E284" s="129">
         <v>800000</v>
       </c>
-      <c r="F284" s="130"/>
+      <c r="F284" s="129"/>
       <c r="G284" s="80">
         <f t="shared" si="104"/>
         <v>800000</v>
@@ -14555,10 +14706,10 @@
       <c r="D285" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E285" s="130">
+      <c r="E285" s="129">
         <v>1600000</v>
       </c>
-      <c r="F285" s="130"/>
+      <c r="F285" s="129"/>
       <c r="G285" s="80">
         <f t="shared" si="104"/>
         <v>1600000</v>
@@ -14599,10 +14750,10 @@
       <c r="D286" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E286" s="130">
+      <c r="E286" s="129">
         <v>160000</v>
       </c>
-      <c r="F286" s="130"/>
+      <c r="F286" s="129"/>
       <c r="G286" s="80">
         <f t="shared" si="104"/>
         <v>160000</v>
@@ -14643,10 +14794,10 @@
       <c r="D287" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E287" s="130">
+      <c r="E287" s="129">
         <v>480000</v>
       </c>
-      <c r="F287" s="130"/>
+      <c r="F287" s="129"/>
       <c r="G287" s="80">
         <f t="shared" si="104"/>
         <v>480000</v>
@@ -14687,10 +14838,10 @@
       <c r="D288" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="E288" s="130">
+      <c r="E288" s="129">
         <v>800000</v>
       </c>
-      <c r="F288" s="130"/>
+      <c r="F288" s="129"/>
       <c r="G288" s="80">
         <f t="shared" si="104"/>
         <v>800000</v>
@@ -14723,43 +14874,43 @@
         <v>246</v>
       </c>
       <c r="D290" s="25"/>
-      <c r="E290" s="139"/>
+      <c r="E290" s="138"/>
     </row>
     <row r="291" spans="1:13">
       <c r="A291" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B291" s="164" t="s">
+      <c r="B291" s="163" t="s">
         <v>174</v>
       </c>
-      <c r="C291" s="165" t="s">
+      <c r="C291" s="164" t="s">
         <v>320</v>
       </c>
-      <c r="D291" s="172" t="s">
+      <c r="D291" s="171" t="s">
         <v>516</v>
       </c>
-      <c r="E291" s="166">
+      <c r="E291" s="165">
         <v>4800</v>
       </c>
-      <c r="F291" s="166">
+      <c r="F291" s="165">
         <v>190</v>
       </c>
-      <c r="G291" s="173">
+      <c r="G291" s="172">
         <f>F291*100+E291</f>
         <v>23800</v>
       </c>
-      <c r="H291" s="168">
+      <c r="H291" s="167">
         <v>1100</v>
       </c>
-      <c r="I291" s="169">
+      <c r="I291" s="168">
         <f t="shared" ref="I291:I307" si="113">H291/10</f>
         <v>110</v>
       </c>
-      <c r="J291" s="174">
+      <c r="J291" s="173">
         <f t="shared" ref="J291:J298" si="114">H291/G291</f>
         <v>4.6218487394957986E-2</v>
       </c>
-      <c r="K291" s="174">
+      <c r="K291" s="173">
         <f t="shared" ref="K291:K298" si="115">G291/H291</f>
         <v>21.636363636363637</v>
       </c>
@@ -14784,10 +14935,10 @@
       <c r="D292" s="69" t="s">
         <v>516</v>
       </c>
-      <c r="E292" s="148">
+      <c r="E292" s="147">
         <v>14000</v>
       </c>
-      <c r="F292" s="129">
+      <c r="F292" s="128">
         <v>580</v>
       </c>
       <c r="G292" s="48">
@@ -14830,10 +14981,10 @@
       <c r="D293" s="69" t="s">
         <v>516</v>
       </c>
-      <c r="E293" s="148">
+      <c r="E293" s="147">
         <v>24000</v>
       </c>
-      <c r="F293" s="129">
+      <c r="F293" s="128">
         <v>960</v>
       </c>
       <c r="G293" s="48">
@@ -14876,10 +15027,10 @@
       <c r="D294" s="69" t="s">
         <v>516</v>
       </c>
-      <c r="E294" s="148">
+      <c r="E294" s="147">
         <v>41000</v>
       </c>
-      <c r="F294" s="129">
+      <c r="F294" s="128">
         <v>2000</v>
       </c>
       <c r="G294" s="48">
@@ -14922,10 +15073,10 @@
       <c r="D295" s="69" t="s">
         <v>516</v>
       </c>
-      <c r="E295" s="148">
+      <c r="E295" s="147">
         <v>140000</v>
       </c>
-      <c r="F295" s="129">
+      <c r="F295" s="128">
         <v>5800</v>
       </c>
       <c r="G295" s="48">
@@ -14968,10 +15119,10 @@
       <c r="D296" s="69" t="s">
         <v>516</v>
       </c>
-      <c r="E296" s="148">
+      <c r="E296" s="147">
         <v>240000</v>
       </c>
-      <c r="F296" s="129">
+      <c r="F296" s="128">
         <v>9600</v>
       </c>
       <c r="G296" s="48">
@@ -15014,10 +15165,10 @@
       <c r="D297" s="69" t="s">
         <v>516</v>
       </c>
-      <c r="E297" s="148">
+      <c r="E297" s="147">
         <v>240000</v>
       </c>
-      <c r="F297" s="129">
+      <c r="F297" s="128">
         <v>9600</v>
       </c>
       <c r="G297" s="48">
@@ -15060,10 +15211,10 @@
       <c r="D298" s="69" t="s">
         <v>516</v>
       </c>
-      <c r="E298" s="148">
+      <c r="E298" s="147">
         <v>400000</v>
       </c>
-      <c r="F298" s="129">
+      <c r="F298" s="128">
         <v>20000</v>
       </c>
       <c r="G298" s="48">
@@ -15095,8 +15246,8 @@
     </row>
     <row r="299" spans="1:13">
       <c r="D299" s="26"/>
-      <c r="E299" s="140"/>
-      <c r="F299" s="141">
+      <c r="E299" s="139"/>
+      <c r="F299" s="140">
         <f>SUM(F291:F298)</f>
         <v>48730</v>
       </c>
@@ -15117,37 +15268,37 @@
       <c r="A300" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B300" s="164" t="s">
+      <c r="B300" s="163" t="s">
         <v>493</v>
       </c>
-      <c r="C300" s="165" t="s">
+      <c r="C300" s="164" t="s">
         <v>320</v>
       </c>
-      <c r="D300" s="172" t="s">
+      <c r="D300" s="171" t="s">
         <v>520</v>
       </c>
-      <c r="E300" s="166">
+      <c r="E300" s="165">
         <v>4800</v>
       </c>
-      <c r="F300" s="166">
+      <c r="F300" s="165">
         <v>190</v>
       </c>
-      <c r="G300" s="173">
+      <c r="G300" s="172">
         <f>F300*100+E300</f>
         <v>23800</v>
       </c>
-      <c r="H300" s="168">
+      <c r="H300" s="167">
         <v>1100</v>
       </c>
-      <c r="I300" s="169">
+      <c r="I300" s="168">
         <f t="shared" si="113"/>
         <v>110</v>
       </c>
-      <c r="J300" s="174">
+      <c r="J300" s="173">
         <f t="shared" ref="J300:J307" si="119">H300/G300</f>
         <v>4.6218487394957986E-2</v>
       </c>
-      <c r="K300" s="174">
+      <c r="K300" s="173">
         <f t="shared" ref="K300:K307" si="120">G300/H300</f>
         <v>21.636363636363637</v>
       </c>
@@ -15172,10 +15323,10 @@
       <c r="D301" s="69" t="s">
         <v>520</v>
       </c>
-      <c r="E301" s="148">
+      <c r="E301" s="147">
         <v>14000</v>
       </c>
-      <c r="F301" s="129">
+      <c r="F301" s="128">
         <v>580</v>
       </c>
       <c r="G301" s="48">
@@ -15218,10 +15369,10 @@
       <c r="D302" s="69" t="s">
         <v>520</v>
       </c>
-      <c r="E302" s="148">
+      <c r="E302" s="147">
         <v>24000</v>
       </c>
-      <c r="F302" s="129">
+      <c r="F302" s="128">
         <v>960</v>
       </c>
       <c r="G302" s="48">
@@ -15264,10 +15415,10 @@
       <c r="D303" s="69" t="s">
         <v>520</v>
       </c>
-      <c r="E303" s="148">
+      <c r="E303" s="147">
         <v>41000</v>
       </c>
-      <c r="F303" s="129">
+      <c r="F303" s="128">
         <v>2000</v>
       </c>
       <c r="G303" s="48">
@@ -15310,10 +15461,10 @@
       <c r="D304" s="69" t="s">
         <v>520</v>
       </c>
-      <c r="E304" s="148">
+      <c r="E304" s="147">
         <v>140000</v>
       </c>
-      <c r="F304" s="129">
+      <c r="F304" s="128">
         <v>5800</v>
       </c>
       <c r="G304" s="48">
@@ -15356,10 +15507,10 @@
       <c r="D305" s="69" t="s">
         <v>520</v>
       </c>
-      <c r="E305" s="148">
+      <c r="E305" s="147">
         <v>240000</v>
       </c>
-      <c r="F305" s="129">
+      <c r="F305" s="128">
         <v>9600</v>
       </c>
       <c r="G305" s="48">
@@ -15402,10 +15553,10 @@
       <c r="D306" s="69" t="s">
         <v>520</v>
       </c>
-      <c r="E306" s="148">
+      <c r="E306" s="147">
         <v>240000</v>
       </c>
-      <c r="F306" s="129">
+      <c r="F306" s="128">
         <v>9600</v>
       </c>
       <c r="G306" s="48">
@@ -15448,10 +15599,10 @@
       <c r="D307" s="69" t="s">
         <v>520</v>
       </c>
-      <c r="E307" s="148">
+      <c r="E307" s="147">
         <v>400000</v>
       </c>
-      <c r="F307" s="129">
+      <c r="F307" s="128">
         <v>20000</v>
       </c>
       <c r="G307" s="48">
@@ -15484,7 +15635,7 @@
     <row r="308" spans="1:13">
       <c r="D308" s="8"/>
       <c r="E308" s="67"/>
-      <c r="F308" s="141">
+      <c r="F308" s="140">
         <f>SUM(F300:F307)</f>
         <v>48730</v>
       </c>
@@ -15506,8 +15657,8 @@
         <v>315</v>
       </c>
       <c r="D309" s="26"/>
-      <c r="E309" s="140"/>
-      <c r="F309" s="142"/>
+      <c r="E309" s="139"/>
+      <c r="F309" s="141"/>
       <c r="G309" s="24"/>
       <c r="H309" s="25"/>
       <c r="I309" s="25"/>
@@ -15519,37 +15670,37 @@
       <c r="A310" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B310" s="164" t="s">
+      <c r="B310" s="163" t="s">
         <v>182</v>
       </c>
-      <c r="C310" s="165" t="s">
+      <c r="C310" s="164" t="s">
         <v>320</v>
       </c>
-      <c r="D310" s="172" t="s">
+      <c r="D310" s="171" t="s">
         <v>518</v>
       </c>
-      <c r="E310" s="166">
+      <c r="E310" s="165">
         <v>4500</v>
       </c>
-      <c r="F310" s="166">
+      <c r="F310" s="165">
         <v>130</v>
       </c>
-      <c r="G310" s="167">
+      <c r="G310" s="166">
         <f>F310*150+E310</f>
         <v>24000</v>
       </c>
-      <c r="H310" s="168">
+      <c r="H310" s="167">
         <v>1100</v>
       </c>
-      <c r="I310" s="169">
+      <c r="I310" s="168">
         <f t="shared" ref="I310:I326" si="124">H310/10</f>
         <v>110</v>
       </c>
-      <c r="J310" s="170">
+      <c r="J310" s="169">
         <f t="shared" ref="J310:J317" si="125">H310/G310</f>
         <v>4.583333333333333E-2</v>
       </c>
-      <c r="K310" s="170">
+      <c r="K310" s="169">
         <f t="shared" ref="K310:K317" si="126">G310/H310</f>
         <v>21.818181818181817</v>
       </c>
@@ -15574,10 +15725,10 @@
       <c r="D311" s="69" t="s">
         <v>518</v>
       </c>
-      <c r="E311" s="148">
+      <c r="E311" s="147">
         <v>12000</v>
       </c>
-      <c r="F311" s="129">
+      <c r="F311" s="128">
         <v>400</v>
       </c>
       <c r="G311" s="32">
@@ -15620,10 +15771,10 @@
       <c r="D312" s="69" t="s">
         <v>518</v>
       </c>
-      <c r="E312" s="148">
+      <c r="E312" s="147">
         <v>23000</v>
       </c>
-      <c r="F312" s="129">
+      <c r="F312" s="128">
         <v>650</v>
       </c>
       <c r="G312" s="32">
@@ -15666,10 +15817,10 @@
       <c r="D313" s="69" t="s">
         <v>518</v>
       </c>
-      <c r="E313" s="148">
+      <c r="E313" s="147">
         <v>45000</v>
       </c>
-      <c r="F313" s="129">
+      <c r="F313" s="128">
         <v>1300</v>
       </c>
       <c r="G313" s="32">
@@ -15712,10 +15863,10 @@
       <c r="D314" s="69" t="s">
         <v>518</v>
       </c>
-      <c r="E314" s="148">
+      <c r="E314" s="147">
         <v>150000</v>
       </c>
-      <c r="F314" s="129">
+      <c r="F314" s="128">
         <v>3800</v>
       </c>
       <c r="G314" s="32">
@@ -15758,10 +15909,10 @@
       <c r="D315" s="69" t="s">
         <v>518</v>
       </c>
-      <c r="E315" s="148">
+      <c r="E315" s="147">
         <v>210000</v>
       </c>
-      <c r="F315" s="129">
+      <c r="F315" s="128">
         <v>6600</v>
       </c>
       <c r="G315" s="32">
@@ -15804,10 +15955,10 @@
       <c r="D316" s="69" t="s">
         <v>518</v>
       </c>
-      <c r="E316" s="148">
+      <c r="E316" s="147">
         <v>210000</v>
       </c>
-      <c r="F316" s="129">
+      <c r="F316" s="128">
         <v>6600</v>
       </c>
       <c r="G316" s="32">
@@ -15850,10 +16001,10 @@
       <c r="D317" s="69" t="s">
         <v>518</v>
       </c>
-      <c r="E317" s="148">
+      <c r="E317" s="147">
         <v>450000</v>
       </c>
-      <c r="F317" s="129">
+      <c r="F317" s="128">
         <v>13000</v>
       </c>
       <c r="G317" s="32">
@@ -15885,47 +16036,47 @@
     </row>
     <row r="318" spans="1:13">
       <c r="D318" s="26"/>
-      <c r="E318" s="140"/>
+      <c r="E318" s="139"/>
     </row>
     <row r="319" spans="1:13">
       <c r="A319" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B319" s="164" t="s">
+      <c r="B319" s="163" t="s">
         <v>190</v>
       </c>
-      <c r="C319" s="165" t="s">
+      <c r="C319" s="164" t="s">
         <v>320</v>
       </c>
-      <c r="D319" s="165" t="s">
+      <c r="D319" s="164" t="s">
         <v>519</v>
       </c>
-      <c r="E319" s="166">
+      <c r="E319" s="165">
         <v>4500</v>
       </c>
-      <c r="F319" s="166">
+      <c r="F319" s="165">
         <v>130</v>
       </c>
-      <c r="G319" s="167">
+      <c r="G319" s="166">
         <f>F319*150+E319</f>
         <v>24000</v>
       </c>
-      <c r="H319" s="168">
+      <c r="H319" s="167">
         <v>1100</v>
       </c>
-      <c r="I319" s="169">
+      <c r="I319" s="168">
         <f t="shared" si="124"/>
         <v>110</v>
       </c>
-      <c r="J319" s="170">
+      <c r="J319" s="169">
         <f t="shared" ref="J319:J326" si="129">H319/G319</f>
         <v>4.583333333333333E-2</v>
       </c>
-      <c r="K319" s="170">
+      <c r="K319" s="169">
         <f t="shared" ref="K319:K326" si="130">G319/H319</f>
         <v>21.818181818181817</v>
       </c>
-      <c r="L319" s="171">
+      <c r="L319" s="170">
         <f t="shared" ref="L319:L326" si="131">K319/K$2</f>
         <v>10.298181818181817</v>
       </c>
@@ -15946,10 +16097,10 @@
       <c r="D320" s="44" t="s">
         <v>519</v>
       </c>
-      <c r="E320" s="148">
+      <c r="E320" s="147">
         <v>12000</v>
       </c>
-      <c r="F320" s="129">
+      <c r="F320" s="128">
         <v>400</v>
       </c>
       <c r="G320" s="32">
@@ -15992,10 +16143,10 @@
       <c r="D321" s="44" t="s">
         <v>519</v>
       </c>
-      <c r="E321" s="148">
+      <c r="E321" s="147">
         <v>23000</v>
       </c>
-      <c r="F321" s="129">
+      <c r="F321" s="128">
         <v>650</v>
       </c>
       <c r="G321" s="32">
@@ -16038,10 +16189,10 @@
       <c r="D322" s="44" t="s">
         <v>519</v>
       </c>
-      <c r="E322" s="148">
+      <c r="E322" s="147">
         <v>45000</v>
       </c>
-      <c r="F322" s="129">
+      <c r="F322" s="128">
         <v>1300</v>
       </c>
       <c r="G322" s="32">
@@ -16084,10 +16235,10 @@
       <c r="D323" s="44" t="s">
         <v>519</v>
       </c>
-      <c r="E323" s="148">
+      <c r="E323" s="147">
         <v>150000</v>
       </c>
-      <c r="F323" s="129">
+      <c r="F323" s="128">
         <v>3800</v>
       </c>
       <c r="G323" s="32">
@@ -16130,10 +16281,10 @@
       <c r="D324" s="44" t="s">
         <v>519</v>
       </c>
-      <c r="E324" s="148">
+      <c r="E324" s="147">
         <v>210000</v>
       </c>
-      <c r="F324" s="129">
+      <c r="F324" s="128">
         <v>6600</v>
       </c>
       <c r="G324" s="32">
@@ -16176,10 +16327,10 @@
       <c r="D325" s="44" t="s">
         <v>519</v>
       </c>
-      <c r="E325" s="148">
+      <c r="E325" s="147">
         <v>210000</v>
       </c>
-      <c r="F325" s="129">
+      <c r="F325" s="128">
         <v>6600</v>
       </c>
       <c r="G325" s="32">
@@ -16222,10 +16373,10 @@
       <c r="D326" s="44" t="s">
         <v>519</v>
       </c>
-      <c r="E326" s="148">
+      <c r="E326" s="147">
         <v>450000</v>
       </c>
-      <c r="F326" s="129">
+      <c r="F326" s="128">
         <v>13000</v>
       </c>
       <c r="G326" s="32">
@@ -16271,8 +16422,8 @@
       <c r="D328" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="E328" s="135"/>
-      <c r="F328" s="143">
+      <c r="E328" s="134"/>
+      <c r="F328" s="142">
         <v>1000</v>
       </c>
       <c r="G328" s="97">
@@ -16309,8 +16460,8 @@
       <c r="D329" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="E329" s="135"/>
-      <c r="F329" s="143">
+      <c r="E329" s="134"/>
+      <c r="F329" s="142">
         <v>3000</v>
       </c>
       <c r="G329" s="97">
@@ -16347,8 +16498,8 @@
       <c r="D330" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="E330" s="135"/>
-      <c r="F330" s="143">
+      <c r="E330" s="134"/>
+      <c r="F330" s="142">
         <v>5600</v>
       </c>
       <c r="G330" s="97">
@@ -16385,8 +16536,8 @@
       <c r="D331" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="E331" s="135"/>
-      <c r="F331" s="143">
+      <c r="E331" s="134"/>
+      <c r="F331" s="142">
         <v>16000</v>
       </c>
       <c r="G331" s="97">
@@ -16423,8 +16574,8 @@
       <c r="D332" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="E332" s="135"/>
-      <c r="F332" s="143">
+      <c r="E332" s="134"/>
+      <c r="F332" s="142">
         <v>16000</v>
       </c>
       <c r="G332" s="97">
@@ -16449,7 +16600,7 @@
       </c>
     </row>
     <row r="333" spans="1:13">
-      <c r="F333" s="117"/>
+      <c r="F333" s="116"/>
       <c r="G333" s="17"/>
     </row>
     <row r="334" spans="1:13">
@@ -16465,8 +16616,8 @@
       <c r="D334" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="E334" s="135"/>
-      <c r="F334" s="143">
+      <c r="E334" s="134"/>
+      <c r="F334" s="142">
         <v>1600</v>
       </c>
       <c r="G334" s="97">
@@ -16503,8 +16654,8 @@
       <c r="D335" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="E335" s="135"/>
-      <c r="F335" s="143">
+      <c r="E335" s="134"/>
+      <c r="F335" s="142">
         <v>4800</v>
       </c>
       <c r="G335" s="97">
@@ -16541,8 +16692,8 @@
       <c r="D336" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="E336" s="135"/>
-      <c r="F336" s="143">
+      <c r="E336" s="134"/>
+      <c r="F336" s="142">
         <v>8000</v>
       </c>
       <c r="G336" s="97">
@@ -16579,8 +16730,8 @@
       <c r="D337" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="E337" s="135"/>
-      <c r="F337" s="143">
+      <c r="E337" s="134"/>
+      <c r="F337" s="142">
         <v>16000</v>
       </c>
       <c r="G337" s="97">
@@ -16617,8 +16768,8 @@
       <c r="D338" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="E338" s="135"/>
-      <c r="F338" s="143">
+      <c r="E338" s="134"/>
+      <c r="F338" s="142">
         <v>16000</v>
       </c>
       <c r="G338" s="97">
@@ -16656,8 +16807,8 @@
         <v>328</v>
       </c>
       <c r="D340" s="90"/>
-      <c r="E340" s="135"/>
-      <c r="F340" s="136"/>
+      <c r="E340" s="134"/>
+      <c r="F340" s="135"/>
       <c r="G340" s="92"/>
       <c r="H340" s="90"/>
       <c r="I340" s="90"/>
@@ -16675,8 +16826,8 @@
         <v>329</v>
       </c>
       <c r="D341" s="91"/>
-      <c r="E341" s="135"/>
-      <c r="F341" s="136"/>
+      <c r="E341" s="134"/>
+      <c r="F341" s="135"/>
       <c r="G341" s="92"/>
       <c r="H341" s="90"/>
       <c r="I341" s="90"/>
@@ -16694,8 +16845,8 @@
         <v>330</v>
       </c>
       <c r="D342" s="91"/>
-      <c r="E342" s="135"/>
-      <c r="F342" s="136"/>
+      <c r="E342" s="134"/>
+      <c r="F342" s="135"/>
       <c r="G342" s="92"/>
       <c r="H342" s="90"/>
       <c r="I342" s="90"/>
@@ -16713,8 +16864,8 @@
         <v>331</v>
       </c>
       <c r="D343" s="90"/>
-      <c r="E343" s="135"/>
-      <c r="F343" s="136"/>
+      <c r="E343" s="134"/>
+      <c r="F343" s="135"/>
       <c r="G343" s="92"/>
       <c r="H343" s="90"/>
       <c r="I343" s="90"/>
@@ -16732,8 +16883,8 @@
         <v>332</v>
       </c>
       <c r="D344" s="90"/>
-      <c r="E344" s="135"/>
-      <c r="F344" s="136"/>
+      <c r="E344" s="134"/>
+      <c r="F344" s="135"/>
       <c r="G344" s="92"/>
       <c r="H344" s="90"/>
       <c r="I344" s="90"/>
@@ -16751,8 +16902,8 @@
         <v>328</v>
       </c>
       <c r="D346" s="90"/>
-      <c r="E346" s="135"/>
-      <c r="F346" s="136"/>
+      <c r="E346" s="134"/>
+      <c r="F346" s="135"/>
       <c r="G346" s="92"/>
       <c r="H346" s="90"/>
       <c r="I346" s="90"/>
@@ -16770,8 +16921,8 @@
         <v>329</v>
       </c>
       <c r="D347" s="90"/>
-      <c r="E347" s="135"/>
-      <c r="F347" s="136"/>
+      <c r="E347" s="134"/>
+      <c r="F347" s="135"/>
       <c r="G347" s="92"/>
       <c r="H347" s="90"/>
       <c r="I347" s="90"/>
@@ -16789,8 +16940,8 @@
         <v>330</v>
       </c>
       <c r="D348" s="91"/>
-      <c r="E348" s="135"/>
-      <c r="F348" s="136"/>
+      <c r="E348" s="134"/>
+      <c r="F348" s="135"/>
       <c r="G348" s="92"/>
       <c r="H348" s="90"/>
       <c r="I348" s="90"/>
@@ -16808,8 +16959,8 @@
         <v>331</v>
       </c>
       <c r="D349" s="91"/>
-      <c r="E349" s="135"/>
-      <c r="F349" s="136"/>
+      <c r="E349" s="134"/>
+      <c r="F349" s="135"/>
       <c r="G349" s="92"/>
       <c r="H349" s="90"/>
       <c r="I349" s="90"/>
@@ -16827,8 +16978,8 @@
         <v>332</v>
       </c>
       <c r="D350" s="91"/>
-      <c r="E350" s="135"/>
-      <c r="F350" s="136"/>
+      <c r="E350" s="134"/>
+      <c r="F350" s="135"/>
       <c r="G350" s="92"/>
       <c r="H350" s="90"/>
       <c r="I350" s="90"/>
@@ -16849,8 +17000,8 @@
         <v>328</v>
       </c>
       <c r="D352" s="90"/>
-      <c r="E352" s="135"/>
-      <c r="F352" s="136"/>
+      <c r="E352" s="134"/>
+      <c r="F352" s="135"/>
       <c r="G352" s="92"/>
       <c r="H352" s="90"/>
       <c r="I352" s="90"/>
@@ -16868,8 +17019,8 @@
         <v>329</v>
       </c>
       <c r="D353" s="91"/>
-      <c r="E353" s="135"/>
-      <c r="F353" s="136"/>
+      <c r="E353" s="134"/>
+      <c r="F353" s="135"/>
       <c r="G353" s="92"/>
       <c r="H353" s="90"/>
       <c r="I353" s="90"/>
@@ -16887,8 +17038,8 @@
         <v>330</v>
       </c>
       <c r="D354" s="91"/>
-      <c r="E354" s="135"/>
-      <c r="F354" s="136"/>
+      <c r="E354" s="134"/>
+      <c r="F354" s="135"/>
       <c r="G354" s="92"/>
       <c r="H354" s="90"/>
       <c r="I354" s="90"/>
@@ -16906,8 +17057,8 @@
         <v>331</v>
       </c>
       <c r="D355" s="91"/>
-      <c r="E355" s="135"/>
-      <c r="F355" s="136"/>
+      <c r="E355" s="134"/>
+      <c r="F355" s="135"/>
       <c r="G355" s="92"/>
       <c r="H355" s="90"/>
       <c r="I355" s="90"/>
@@ -16925,8 +17076,8 @@
         <v>332</v>
       </c>
       <c r="D356" s="91"/>
-      <c r="E356" s="135"/>
-      <c r="F356" s="136"/>
+      <c r="E356" s="134"/>
+      <c r="F356" s="135"/>
       <c r="G356" s="92"/>
       <c r="H356" s="90"/>
       <c r="I356" s="90"/>
@@ -16947,8 +17098,8 @@
         <v>328</v>
       </c>
       <c r="D358" s="90"/>
-      <c r="E358" s="135"/>
-      <c r="F358" s="136"/>
+      <c r="E358" s="134"/>
+      <c r="F358" s="135"/>
       <c r="G358" s="92"/>
       <c r="H358" s="90"/>
       <c r="I358" s="90"/>
@@ -16966,8 +17117,8 @@
         <v>329</v>
       </c>
       <c r="D359" s="91"/>
-      <c r="E359" s="135"/>
-      <c r="F359" s="136"/>
+      <c r="E359" s="134"/>
+      <c r="F359" s="135"/>
       <c r="G359" s="92"/>
       <c r="H359" s="90"/>
       <c r="I359" s="90"/>
@@ -16985,8 +17136,8 @@
         <v>330</v>
       </c>
       <c r="D360" s="91"/>
-      <c r="E360" s="135"/>
-      <c r="F360" s="136"/>
+      <c r="E360" s="134"/>
+      <c r="F360" s="135"/>
       <c r="G360" s="92"/>
       <c r="H360" s="90"/>
       <c r="I360" s="90"/>
@@ -17004,8 +17155,8 @@
         <v>331</v>
       </c>
       <c r="D361" s="91"/>
-      <c r="E361" s="135"/>
-      <c r="F361" s="136"/>
+      <c r="E361" s="134"/>
+      <c r="F361" s="135"/>
       <c r="G361" s="92"/>
       <c r="H361" s="90"/>
       <c r="I361" s="90"/>
@@ -17023,8 +17174,8 @@
         <v>332</v>
       </c>
       <c r="D362" s="91"/>
-      <c r="E362" s="135"/>
-      <c r="F362" s="136"/>
+      <c r="E362" s="134"/>
+      <c r="F362" s="135"/>
       <c r="G362" s="92"/>
       <c r="H362" s="90"/>
       <c r="I362" s="90"/>
@@ -17039,7 +17190,7 @@
         <v>247</v>
       </c>
       <c r="D364" s="26"/>
-      <c r="E364" s="140"/>
+      <c r="E364" s="139"/>
     </row>
     <row r="365" spans="1:13">
       <c r="A365" s="1" t="s">
@@ -17054,10 +17205,10 @@
       <c r="D365" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="E365" s="148">
+      <c r="E365" s="147">
         <v>14000</v>
       </c>
-      <c r="F365" s="129">
+      <c r="F365" s="128">
         <v>290</v>
       </c>
       <c r="G365" s="32">
@@ -17100,10 +17251,10 @@
       <c r="D366" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="E366" s="148">
+      <c r="E366" s="147">
         <v>20000</v>
       </c>
-      <c r="F366" s="129">
+      <c r="F366" s="128">
         <v>500</v>
       </c>
       <c r="G366" s="32">
@@ -17146,10 +17297,10 @@
       <c r="D367" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="E367" s="148">
+      <c r="E367" s="147">
         <v>40000</v>
       </c>
-      <c r="F367" s="129">
+      <c r="F367" s="128">
         <v>1000</v>
       </c>
       <c r="G367" s="32">
@@ -17192,10 +17343,10 @@
       <c r="D368" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="E368" s="148">
+      <c r="E368" s="147">
         <v>120000</v>
       </c>
-      <c r="F368" s="129">
+      <c r="F368" s="128">
         <v>3000</v>
       </c>
       <c r="G368" s="32">
@@ -17238,10 +17389,10 @@
       <c r="D369" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="E369" s="148">
+      <c r="E369" s="147">
         <v>240000</v>
       </c>
-      <c r="F369" s="129">
+      <c r="F369" s="128">
         <v>4800</v>
       </c>
       <c r="G369" s="32">
@@ -17284,10 +17435,10 @@
       <c r="D370" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="E370" s="148">
+      <c r="E370" s="147">
         <v>40000</v>
       </c>
-      <c r="F370" s="129">
+      <c r="F370" s="128">
         <v>1000</v>
       </c>
       <c r="G370" s="32">
@@ -17330,10 +17481,10 @@
       <c r="D371" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="E371" s="148">
+      <c r="E371" s="147">
         <v>120000</v>
       </c>
-      <c r="F371" s="129">
+      <c r="F371" s="128">
         <v>3000</v>
       </c>
       <c r="G371" s="32">
@@ -17376,10 +17527,10 @@
       <c r="D372" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="E372" s="148">
+      <c r="E372" s="147">
         <v>240000</v>
       </c>
-      <c r="F372" s="129">
+      <c r="F372" s="128">
         <v>4800</v>
       </c>
       <c r="G372" s="32">
@@ -17422,10 +17573,10 @@
       <c r="D373" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="E373" s="148">
+      <c r="E373" s="147">
         <v>120000</v>
       </c>
-      <c r="F373" s="129">
+      <c r="F373" s="128">
         <v>3000</v>
       </c>
       <c r="G373" s="32">
@@ -17468,10 +17619,10 @@
       <c r="D374" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="E374" s="148">
+      <c r="E374" s="147">
         <v>240000</v>
       </c>
-      <c r="F374" s="129">
+      <c r="F374" s="128">
         <v>4800</v>
       </c>
       <c r="G374" s="32">
@@ -17502,10 +17653,10 @@
       </c>
     </row>
     <row r="375" spans="1:14">
-      <c r="E375" s="144" t="s">
+      <c r="E375" s="143" t="s">
         <v>509</v>
       </c>
-      <c r="F375" s="114" t="s">
+      <c r="F375" s="113" t="s">
         <v>11</v>
       </c>
     </row>
@@ -17522,10 +17673,10 @@
       <c r="D376" s="28" t="s">
         <v>508</v>
       </c>
-      <c r="E376" s="129">
+      <c r="E376" s="128">
         <v>70</v>
       </c>
-      <c r="F376" s="150">
+      <c r="F376" s="149">
         <v>33000</v>
       </c>
       <c r="G376" s="29">
@@ -17570,10 +17721,10 @@
       <c r="D377" s="28" t="s">
         <v>502</v>
       </c>
-      <c r="E377" s="129">
+      <c r="E377" s="128">
         <v>57</v>
       </c>
-      <c r="F377" s="150">
+      <c r="F377" s="149">
         <v>57000</v>
       </c>
       <c r="G377" s="29">
@@ -17618,10 +17769,10 @@
       <c r="D378" s="28" t="s">
         <v>503</v>
       </c>
-      <c r="E378" s="129">
+      <c r="E378" s="128">
         <v>77</v>
       </c>
-      <c r="F378" s="150">
+      <c r="F378" s="149">
         <v>110000</v>
       </c>
       <c r="G378" s="29">
@@ -17666,10 +17817,10 @@
       <c r="D379" s="28" t="s">
         <v>504</v>
       </c>
-      <c r="E379" s="129">
+      <c r="E379" s="128">
         <v>137</v>
       </c>
-      <c r="F379" s="150">
+      <c r="F379" s="149">
         <v>340000</v>
       </c>
       <c r="G379" s="29">
@@ -17714,10 +17865,10 @@
       <c r="D380" s="28" t="s">
         <v>505</v>
       </c>
-      <c r="E380" s="129">
+      <c r="E380" s="128">
         <v>110</v>
       </c>
-      <c r="F380" s="150">
+      <c r="F380" s="149">
         <v>300000</v>
       </c>
       <c r="G380" s="29">
@@ -17762,10 +17913,10 @@
       <c r="D381" s="28" t="s">
         <v>506</v>
       </c>
-      <c r="E381" s="129">
+      <c r="E381" s="128">
         <v>29</v>
       </c>
-      <c r="F381" s="150">
+      <c r="F381" s="149">
         <v>60000</v>
       </c>
       <c r="G381" s="32">
@@ -17810,10 +17961,10 @@
       <c r="D382" s="28" t="s">
         <v>505</v>
       </c>
-      <c r="E382" s="129">
+      <c r="E382" s="128">
         <v>50</v>
       </c>
-      <c r="F382" s="150">
+      <c r="F382" s="149">
         <v>480000</v>
       </c>
       <c r="G382" s="32">
@@ -17858,10 +18009,10 @@
       <c r="D383" s="28" t="s">
         <v>507</v>
       </c>
-      <c r="E383" s="129">
+      <c r="E383" s="128">
         <v>84</v>
       </c>
-      <c r="F383" s="150">
+      <c r="F383" s="149">
         <v>260000</v>
       </c>
       <c r="G383" s="32">
@@ -17906,10 +18057,10 @@
       <c r="D384" s="28" t="s">
         <v>506</v>
       </c>
-      <c r="E384" s="129">
+      <c r="E384" s="128">
         <v>30</v>
       </c>
-      <c r="F384" s="150">
+      <c r="F384" s="149">
         <v>50000</v>
       </c>
       <c r="G384" s="35">
@@ -17954,10 +18105,10 @@
       <c r="D385" s="28" t="s">
         <v>504</v>
       </c>
-      <c r="E385" s="129">
+      <c r="E385" s="128">
         <v>160</v>
       </c>
-      <c r="F385" s="150">
+      <c r="F385" s="149">
         <v>160000</v>
       </c>
       <c r="G385" s="35">
@@ -18002,10 +18153,10 @@
       <c r="D386" s="28" t="s">
         <v>505</v>
       </c>
-      <c r="E386" s="129">
+      <c r="E386" s="128">
         <v>110</v>
       </c>
-      <c r="F386" s="150">
+      <c r="F386" s="149">
         <v>300000</v>
       </c>
       <c r="G386" s="35">
@@ -18050,10 +18201,10 @@
       <c r="D387" s="28" t="s">
         <v>503</v>
       </c>
-      <c r="E387" s="129">
+      <c r="E387" s="128">
         <v>85</v>
       </c>
-      <c r="F387" s="150">
+      <c r="F387" s="149">
         <v>75000</v>
       </c>
       <c r="G387" s="38">
@@ -18098,10 +18249,10 @@
       <c r="D388" s="28" t="s">
         <v>507</v>
       </c>
-      <c r="E388" s="129">
+      <c r="E388" s="128">
         <v>50</v>
       </c>
-      <c r="F388" s="150">
+      <c r="F388" s="149">
         <v>160000</v>
       </c>
       <c r="G388" s="38">
@@ -18146,10 +18297,10 @@
       <c r="D389" s="28" t="s">
         <v>505</v>
       </c>
-      <c r="E389" s="129">
+      <c r="E389" s="128">
         <v>110</v>
       </c>
-      <c r="F389" s="150">
+      <c r="F389" s="149">
         <v>300000</v>
       </c>
       <c r="G389" s="38">
@@ -18194,10 +18345,10 @@
       <c r="D390" s="28" t="s">
         <v>504</v>
       </c>
-      <c r="E390" s="129">
+      <c r="E390" s="128">
         <v>160</v>
       </c>
-      <c r="F390" s="150">
+      <c r="F390" s="149">
         <v>160000</v>
       </c>
       <c r="G390" s="41">
@@ -18242,10 +18393,10 @@
       <c r="D391" s="28" t="s">
         <v>503</v>
       </c>
-      <c r="E391" s="129">
+      <c r="E391" s="128">
         <v>270</v>
       </c>
-      <c r="F391" s="150">
+      <c r="F391" s="149">
         <v>140000</v>
       </c>
       <c r="G391" s="41">
@@ -18290,10 +18441,10 @@
       <c r="D392" s="28" t="s">
         <v>505</v>
       </c>
-      <c r="E392" s="129">
+      <c r="E392" s="128">
         <v>110</v>
       </c>
-      <c r="F392" s="150">
+      <c r="F392" s="149">
         <v>300000</v>
       </c>
       <c r="G392" s="41">
@@ -18338,10 +18489,10 @@
       <c r="D393" s="28" t="s">
         <v>506</v>
       </c>
-      <c r="E393" s="129">
+      <c r="E393" s="128">
         <v>89</v>
       </c>
-      <c r="F393" s="150">
+      <c r="F393" s="149">
         <v>160000</v>
       </c>
       <c r="G393" s="32">
@@ -18374,13 +18525,13 @@
       </c>
     </row>
     <row r="394" spans="1:14">
-      <c r="F394" s="145"/>
+      <c r="F394" s="144"/>
     </row>
     <row r="395" spans="1:14">
       <c r="B395" s="22" t="s">
         <v>248</v>
       </c>
-      <c r="F395" s="145" t="s">
+      <c r="F395" s="144" t="s">
         <v>511</v>
       </c>
     </row>
@@ -18397,10 +18548,10 @@
       <c r="D396" s="28" t="s">
         <v>610</v>
       </c>
-      <c r="E396" s="148">
+      <c r="E396" s="147">
         <v>24000</v>
       </c>
-      <c r="F396" s="129">
+      <c r="F396" s="128">
         <v>2744056000</v>
       </c>
       <c r="G396" s="32">
@@ -18445,10 +18596,10 @@
       <c r="D397" s="28" t="s">
         <v>611</v>
       </c>
-      <c r="E397" s="148">
+      <c r="E397" s="147">
         <v>24000</v>
       </c>
-      <c r="F397" s="129">
+      <c r="F397" s="128">
         <v>18341848000</v>
       </c>
       <c r="G397" s="32">
@@ -18493,10 +18644,10 @@
       <c r="D398" s="28" t="s">
         <v>611</v>
       </c>
-      <c r="E398" s="148">
+      <c r="E398" s="147">
         <v>48000</v>
       </c>
-      <c r="F398" s="129">
+      <c r="F398" s="128">
         <v>47804344000</v>
       </c>
       <c r="G398" s="32">
@@ -18541,10 +18692,10 @@
       <c r="D399" s="28" t="s">
         <v>611</v>
       </c>
-      <c r="E399" s="148">
+      <c r="E399" s="147">
         <v>48000</v>
       </c>
-      <c r="F399" s="129">
+      <c r="F399" s="128">
         <v>79740101000</v>
       </c>
       <c r="G399" s="32">
@@ -18589,10 +18740,10 @@
       <c r="D400" s="28" t="s">
         <v>611</v>
       </c>
-      <c r="E400" s="148">
+      <c r="E400" s="147">
         <v>48000</v>
       </c>
-      <c r="F400" s="129">
+      <c r="F400" s="128">
         <v>129783016999.99998</v>
       </c>
       <c r="G400" s="32">
@@ -18637,10 +18788,10 @@
       <c r="D401" s="28" t="s">
         <v>611</v>
       </c>
-      <c r="E401" s="148">
+      <c r="E401" s="147">
         <v>48000</v>
       </c>
-      <c r="F401" s="129">
+      <c r="F401" s="128">
         <v>164535042000</v>
       </c>
       <c r="G401" s="32">
@@ -18685,10 +18836,10 @@
       <c r="D402" s="28" t="s">
         <v>611</v>
       </c>
-      <c r="E402" s="148">
+      <c r="E402" s="147">
         <v>100000</v>
       </c>
-      <c r="F402" s="129">
+      <c r="F402" s="128">
         <v>190188355000</v>
       </c>
       <c r="G402" s="32">
@@ -18733,10 +18884,10 @@
       <c r="D403" s="28" t="s">
         <v>611</v>
       </c>
-      <c r="E403" s="148">
+      <c r="E403" s="147">
         <v>100000</v>
       </c>
-      <c r="F403" s="129">
+      <c r="F403" s="128">
         <v>201543692000</v>
       </c>
       <c r="G403" s="32">
@@ -18781,10 +18932,10 @@
       <c r="D404" s="28" t="s">
         <v>611</v>
       </c>
-      <c r="E404" s="148">
+      <c r="E404" s="147">
         <v>100000</v>
       </c>
-      <c r="F404" s="129">
+      <c r="F404" s="128">
         <v>257869052000</v>
       </c>
       <c r="G404" s="32">
@@ -18829,10 +18980,10 @@
       <c r="D405" s="28" t="s">
         <v>611</v>
       </c>
-      <c r="E405" s="148">
+      <c r="E405" s="147">
         <v>100000</v>
       </c>
-      <c r="F405" s="129">
+      <c r="F405" s="128">
         <v>321126764000</v>
       </c>
       <c r="G405" s="32">
@@ -18864,6 +19015,12 @@
         <v>607</v>
       </c>
     </row>
+    <row r="406" spans="1:14">
+      <c r="H406" s="13">
+        <f>SUM(H396:H405)</f>
+        <v>143000</v>
+      </c>
+    </row>
     <row r="407" spans="1:14">
       <c r="A407" s="1" t="s">
         <v>74</v>
@@ -18877,10 +19034,10 @@
       <c r="D407" s="28" t="s">
         <v>612</v>
       </c>
-      <c r="E407" s="149">
+      <c r="E407" s="148">
         <v>14000</v>
       </c>
-      <c r="F407" s="120">
+      <c r="F407" s="119">
         <v>2</v>
       </c>
       <c r="G407" s="48">
@@ -18923,10 +19080,10 @@
       <c r="D408" s="28" t="s">
         <v>612</v>
       </c>
-      <c r="E408" s="149">
+      <c r="E408" s="148">
         <v>24000</v>
       </c>
-      <c r="F408" s="120">
+      <c r="F408" s="119">
         <v>3</v>
       </c>
       <c r="G408" s="48">
@@ -18969,10 +19126,10 @@
       <c r="D409" s="28" t="s">
         <v>612</v>
       </c>
-      <c r="E409" s="149">
+      <c r="E409" s="148">
         <v>48000</v>
       </c>
-      <c r="F409" s="120">
+      <c r="F409" s="119">
         <v>4</v>
       </c>
       <c r="G409" s="48">
@@ -19015,10 +19172,10 @@
       <c r="D410" s="28" t="s">
         <v>612</v>
       </c>
-      <c r="E410" s="148">
+      <c r="E410" s="147">
         <v>150000</v>
       </c>
-      <c r="F410" s="120">
+      <c r="F410" s="119">
         <v>10</v>
       </c>
       <c r="G410" s="48">
@@ -19061,10 +19218,10 @@
       <c r="D411" s="28" t="s">
         <v>612</v>
       </c>
-      <c r="E411" s="148">
+      <c r="E411" s="147">
         <v>200000</v>
       </c>
-      <c r="F411" s="120">
+      <c r="F411" s="119">
         <v>15</v>
       </c>
       <c r="G411" s="48">
@@ -19107,10 +19264,10 @@
       <c r="D412" s="28" t="s">
         <v>612</v>
       </c>
-      <c r="E412" s="148">
+      <c r="E412" s="147">
         <v>200000</v>
       </c>
-      <c r="F412" s="120">
+      <c r="F412" s="119">
         <v>15</v>
       </c>
       <c r="G412" s="48">
@@ -19153,10 +19310,10 @@
       <c r="D413" s="28" t="s">
         <v>612</v>
       </c>
-      <c r="E413" s="148">
+      <c r="E413" s="147">
         <v>200000</v>
       </c>
-      <c r="F413" s="120">
+      <c r="F413" s="119">
         <v>15</v>
       </c>
       <c r="G413" s="48">
@@ -19199,10 +19356,10 @@
       <c r="D414" s="28" t="s">
         <v>612</v>
       </c>
-      <c r="E414" s="148">
+      <c r="E414" s="147">
         <v>200000</v>
       </c>
-      <c r="F414" s="120">
+      <c r="F414" s="119">
         <v>15</v>
       </c>
       <c r="G414" s="48">
@@ -19245,10 +19402,10 @@
       <c r="D415" s="28" t="s">
         <v>612</v>
       </c>
-      <c r="E415" s="148">
+      <c r="E415" s="147">
         <v>200000</v>
       </c>
-      <c r="F415" s="120">
+      <c r="F415" s="119">
         <v>15</v>
       </c>
       <c r="G415" s="48">
@@ -19278,6 +19435,12 @@
         <v>607</v>
       </c>
     </row>
+    <row r="416" spans="1:14">
+      <c r="H416" s="13">
+        <f>SUM(H407:H415)</f>
+        <v>327800</v>
+      </c>
+    </row>
     <row r="417" spans="1:12">
       <c r="A417" s="1" t="s">
         <v>74</v>
@@ -19291,20 +19454,20 @@
       <c r="D417" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E417" s="136">
+      <c r="E417" s="135">
         <v>14000</v>
       </c>
-      <c r="F417" s="136">
+      <c r="F417" s="135">
         <v>4</v>
       </c>
       <c r="G417" s="92">
         <f>10000*F417+E417</f>
         <v>54000</v>
       </c>
-      <c r="H417" s="146">
+      <c r="H417" s="145">
         <v>11000</v>
       </c>
-      <c r="I417" s="147">
+      <c r="I417" s="146">
         <f t="shared" si="145"/>
         <v>1100</v>
       </c>
@@ -19334,20 +19497,20 @@
       <c r="D418" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E418" s="136">
+      <c r="E418" s="135">
         <v>28000</v>
       </c>
-      <c r="F418" s="136">
+      <c r="F418" s="135">
         <v>8</v>
       </c>
       <c r="G418" s="92">
         <f t="shared" ref="G418:G435" si="159">10000*F418+E418</f>
         <v>108000</v>
       </c>
-      <c r="H418" s="146">
+      <c r="H418" s="145">
         <v>22000</v>
       </c>
-      <c r="I418" s="147">
+      <c r="I418" s="146">
         <f t="shared" si="145"/>
         <v>2200</v>
       </c>
@@ -19377,20 +19540,20 @@
       <c r="D419" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E419" s="135">
+      <c r="E419" s="134">
         <v>42000</v>
       </c>
-      <c r="F419" s="136">
+      <c r="F419" s="135">
         <v>12</v>
       </c>
       <c r="G419" s="92">
         <f t="shared" si="159"/>
         <v>162000</v>
       </c>
-      <c r="H419" s="146">
+      <c r="H419" s="145">
         <v>33000</v>
       </c>
-      <c r="I419" s="147">
+      <c r="I419" s="146">
         <f t="shared" si="145"/>
         <v>3300</v>
       </c>
@@ -19420,20 +19583,20 @@
       <c r="D420" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E420" s="135">
+      <c r="E420" s="134">
         <v>70000</v>
       </c>
-      <c r="F420" s="136">
+      <c r="F420" s="135">
         <v>20</v>
       </c>
       <c r="G420" s="92">
         <f t="shared" si="159"/>
         <v>270000</v>
       </c>
-      <c r="H420" s="146">
+      <c r="H420" s="145">
         <v>55000</v>
       </c>
-      <c r="I420" s="147">
+      <c r="I420" s="146">
         <f t="shared" si="145"/>
         <v>5500</v>
       </c>
@@ -19463,20 +19626,20 @@
       <c r="D421" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E421" s="135">
+      <c r="E421" s="134">
         <v>140000</v>
       </c>
-      <c r="F421" s="136">
+      <c r="F421" s="135">
         <v>40</v>
       </c>
       <c r="G421" s="92">
         <f t="shared" si="159"/>
         <v>540000</v>
       </c>
-      <c r="H421" s="146">
+      <c r="H421" s="145">
         <v>110000</v>
       </c>
-      <c r="I421" s="147">
+      <c r="I421" s="146">
         <f t="shared" si="145"/>
         <v>11000</v>
       </c>
@@ -19506,20 +19669,20 @@
       <c r="D422" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E422" s="136">
+      <c r="E422" s="135">
         <v>14000</v>
       </c>
-      <c r="F422" s="136">
+      <c r="F422" s="135">
         <v>4</v>
       </c>
       <c r="G422" s="92">
         <f t="shared" si="159"/>
         <v>54000</v>
       </c>
-      <c r="H422" s="146">
+      <c r="H422" s="145">
         <v>11000</v>
       </c>
-      <c r="I422" s="147">
+      <c r="I422" s="146">
         <f t="shared" si="145"/>
         <v>1100</v>
       </c>
@@ -19549,20 +19712,20 @@
       <c r="D423" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E423" s="136">
+      <c r="E423" s="135">
         <v>28000</v>
       </c>
-      <c r="F423" s="136">
+      <c r="F423" s="135">
         <v>8</v>
       </c>
       <c r="G423" s="92">
         <f t="shared" si="159"/>
         <v>108000</v>
       </c>
-      <c r="H423" s="146">
+      <c r="H423" s="145">
         <v>22000</v>
       </c>
-      <c r="I423" s="147">
+      <c r="I423" s="146">
         <f t="shared" si="145"/>
         <v>2200</v>
       </c>
@@ -19592,20 +19755,20 @@
       <c r="D424" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E424" s="135">
+      <c r="E424" s="134">
         <v>42000</v>
       </c>
-      <c r="F424" s="136">
+      <c r="F424" s="135">
         <v>12</v>
       </c>
       <c r="G424" s="92">
         <f t="shared" si="159"/>
         <v>162000</v>
       </c>
-      <c r="H424" s="146">
+      <c r="H424" s="145">
         <v>33000</v>
       </c>
-      <c r="I424" s="147">
+      <c r="I424" s="146">
         <f t="shared" si="145"/>
         <v>3300</v>
       </c>
@@ -19635,20 +19798,20 @@
       <c r="D425" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E425" s="135">
+      <c r="E425" s="134">
         <v>70000</v>
       </c>
-      <c r="F425" s="136">
+      <c r="F425" s="135">
         <v>20</v>
       </c>
       <c r="G425" s="92">
         <f t="shared" si="159"/>
         <v>270000</v>
       </c>
-      <c r="H425" s="146">
+      <c r="H425" s="145">
         <v>55000</v>
       </c>
-      <c r="I425" s="147">
+      <c r="I425" s="146">
         <f t="shared" si="145"/>
         <v>5500</v>
       </c>
@@ -19678,20 +19841,20 @@
       <c r="D426" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E426" s="135">
+      <c r="E426" s="134">
         <v>140000</v>
       </c>
-      <c r="F426" s="136">
+      <c r="F426" s="135">
         <v>40</v>
       </c>
       <c r="G426" s="92">
         <f t="shared" si="159"/>
         <v>540000</v>
       </c>
-      <c r="H426" s="146">
+      <c r="H426" s="145">
         <v>110000</v>
       </c>
-      <c r="I426" s="147">
+      <c r="I426" s="146">
         <f t="shared" si="145"/>
         <v>11000</v>
       </c>
@@ -19721,20 +19884,20 @@
       <c r="D427" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E427" s="136">
+      <c r="E427" s="135">
         <v>14000</v>
       </c>
-      <c r="F427" s="136">
+      <c r="F427" s="135">
         <v>4</v>
       </c>
       <c r="G427" s="92">
         <f t="shared" si="159"/>
         <v>54000</v>
       </c>
-      <c r="H427" s="146">
+      <c r="H427" s="145">
         <v>11000</v>
       </c>
-      <c r="I427" s="147">
+      <c r="I427" s="146">
         <f t="shared" si="145"/>
         <v>1100</v>
       </c>
@@ -19764,20 +19927,20 @@
       <c r="D428" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E428" s="136">
+      <c r="E428" s="135">
         <v>28000</v>
       </c>
-      <c r="F428" s="136">
+      <c r="F428" s="135">
         <v>8</v>
       </c>
       <c r="G428" s="92">
         <f t="shared" si="159"/>
         <v>108000</v>
       </c>
-      <c r="H428" s="146">
+      <c r="H428" s="145">
         <v>22000</v>
       </c>
-      <c r="I428" s="147">
+      <c r="I428" s="146">
         <f t="shared" si="145"/>
         <v>2200</v>
       </c>
@@ -19807,20 +19970,20 @@
       <c r="D429" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E429" s="135">
+      <c r="E429" s="134">
         <v>42000</v>
       </c>
-      <c r="F429" s="136">
+      <c r="F429" s="135">
         <v>12</v>
       </c>
       <c r="G429" s="92">
         <f t="shared" si="159"/>
         <v>162000</v>
       </c>
-      <c r="H429" s="146">
+      <c r="H429" s="145">
         <v>33000</v>
       </c>
-      <c r="I429" s="147">
+      <c r="I429" s="146">
         <f t="shared" si="145"/>
         <v>3300</v>
       </c>
@@ -19850,20 +20013,20 @@
       <c r="D430" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E430" s="135">
+      <c r="E430" s="134">
         <v>70000</v>
       </c>
-      <c r="F430" s="136">
+      <c r="F430" s="135">
         <v>20</v>
       </c>
       <c r="G430" s="92">
         <f t="shared" si="159"/>
         <v>270000</v>
       </c>
-      <c r="H430" s="146">
+      <c r="H430" s="145">
         <v>55000</v>
       </c>
-      <c r="I430" s="147">
+      <c r="I430" s="146">
         <f t="shared" si="145"/>
         <v>5500</v>
       </c>
@@ -19893,20 +20056,20 @@
       <c r="D431" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E431" s="135">
+      <c r="E431" s="134">
         <v>140000</v>
       </c>
-      <c r="F431" s="136">
+      <c r="F431" s="135">
         <v>40</v>
       </c>
       <c r="G431" s="92">
         <f t="shared" si="159"/>
         <v>540000</v>
       </c>
-      <c r="H431" s="146">
+      <c r="H431" s="145">
         <v>110000</v>
       </c>
-      <c r="I431" s="147">
+      <c r="I431" s="146">
         <f t="shared" si="145"/>
         <v>11000</v>
       </c>
@@ -19936,20 +20099,20 @@
       <c r="D432" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E432" s="136">
+      <c r="E432" s="135">
         <v>14000</v>
       </c>
-      <c r="F432" s="136">
+      <c r="F432" s="135">
         <v>4</v>
       </c>
       <c r="G432" s="92">
         <f t="shared" si="159"/>
         <v>54000</v>
       </c>
-      <c r="H432" s="146">
+      <c r="H432" s="145">
         <v>11000</v>
       </c>
-      <c r="I432" s="147">
+      <c r="I432" s="146">
         <f t="shared" si="145"/>
         <v>1100</v>
       </c>
@@ -19966,7 +20129,7 @@
         <v>2.3170909090909091</v>
       </c>
     </row>
-    <row r="433" spans="1:12">
+    <row r="433" spans="1:17">
       <c r="A433" s="1" t="s">
         <v>74</v>
       </c>
@@ -19979,20 +20142,20 @@
       <c r="D433" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E433" s="136">
+      <c r="E433" s="135">
         <v>28000</v>
       </c>
-      <c r="F433" s="136">
+      <c r="F433" s="135">
         <v>8</v>
       </c>
       <c r="G433" s="92">
         <f t="shared" si="159"/>
         <v>108000</v>
       </c>
-      <c r="H433" s="146">
+      <c r="H433" s="145">
         <v>22000</v>
       </c>
-      <c r="I433" s="147">
+      <c r="I433" s="146">
         <f t="shared" si="145"/>
         <v>2200</v>
       </c>
@@ -20009,7 +20172,7 @@
         <v>2.3170909090909091</v>
       </c>
     </row>
-    <row r="434" spans="1:12">
+    <row r="434" spans="1:17">
       <c r="A434" s="1" t="s">
         <v>74</v>
       </c>
@@ -20022,20 +20185,20 @@
       <c r="D434" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E434" s="135">
+      <c r="E434" s="134">
         <v>42000</v>
       </c>
-      <c r="F434" s="136">
+      <c r="F434" s="135">
         <v>12</v>
       </c>
       <c r="G434" s="92">
         <f t="shared" si="159"/>
         <v>162000</v>
       </c>
-      <c r="H434" s="146">
+      <c r="H434" s="145">
         <v>33000</v>
       </c>
-      <c r="I434" s="147">
+      <c r="I434" s="146">
         <f t="shared" si="145"/>
         <v>3300</v>
       </c>
@@ -20051,8 +20214,12 @@
         <f t="shared" si="160"/>
         <v>2.3170909090909091</v>
       </c>
-    </row>
-    <row r="435" spans="1:12">
+      <c r="Q434" s="1">
+        <f>1000*600</f>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="435" spans="1:17">
       <c r="A435" s="1" t="s">
         <v>74</v>
       </c>
@@ -20065,20 +20232,20 @@
       <c r="D435" s="90" t="s">
         <v>449</v>
       </c>
-      <c r="E435" s="135">
+      <c r="E435" s="134">
         <v>70000</v>
       </c>
-      <c r="F435" s="136">
+      <c r="F435" s="135">
         <v>20</v>
       </c>
       <c r="G435" s="92">
         <f t="shared" si="159"/>
         <v>270000</v>
       </c>
-      <c r="H435" s="146">
+      <c r="H435" s="145">
         <v>55000</v>
       </c>
-      <c r="I435" s="147">
+      <c r="I435" s="146">
         <f t="shared" si="145"/>
         <v>5500</v>
       </c>
@@ -20095,169 +20262,782 @@
         <v>2.3170909090909091</v>
       </c>
     </row>
-    <row r="437" spans="1:12" s="55" customFormat="1">
-      <c r="B437" s="56" t="s">
+    <row r="436" spans="1:17">
+      <c r="B436" s="177"/>
+      <c r="C436" s="178"/>
+      <c r="D436" s="177"/>
+      <c r="E436" s="182"/>
+      <c r="F436" s="116"/>
+      <c r="G436" s="17"/>
+      <c r="H436" s="183"/>
+      <c r="I436" s="184"/>
+      <c r="J436" s="180"/>
+      <c r="K436" s="180"/>
+      <c r="L436" s="181"/>
+    </row>
+    <row r="437" spans="1:17">
+      <c r="B437" s="22" t="s">
+        <v>615</v>
+      </c>
+      <c r="D437" s="26"/>
+      <c r="E437" s="139"/>
+      <c r="F437" s="141"/>
+      <c r="G437" s="24"/>
+      <c r="H437" s="25"/>
+      <c r="I437" s="25"/>
+      <c r="J437" s="25"/>
+      <c r="K437" s="25"/>
+      <c r="L437" s="89"/>
+      <c r="N437" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="O437" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="P437" s="1" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="438" spans="1:17">
+      <c r="A438" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B438" s="28" t="s">
+        <v>616</v>
+      </c>
+      <c r="C438" s="191">
+        <v>200</v>
+      </c>
+      <c r="D438" s="69" t="s">
+        <v>626</v>
+      </c>
+      <c r="E438" s="147">
+        <v>10000</v>
+      </c>
+      <c r="F438" s="128">
+        <v>120</v>
+      </c>
+      <c r="G438" s="32">
+        <f>E438+(F438*600)</f>
+        <v>82000</v>
+      </c>
+      <c r="H438" s="49">
+        <v>5500</v>
+      </c>
+      <c r="I438" s="100">
+        <f t="shared" ref="I438:I445" si="161">H438/10</f>
+        <v>550</v>
+      </c>
+      <c r="J438" s="34">
+        <f t="shared" ref="J438:J445" si="162">H438/G438</f>
+        <v>6.7073170731707321E-2</v>
+      </c>
+      <c r="K438" s="34">
+        <f t="shared" ref="K438:K445" si="163">G438/H438</f>
+        <v>14.909090909090908</v>
+      </c>
+      <c r="L438" s="88">
+        <f t="shared" ref="L438:L445" si="164">K438/K$2</f>
+        <v>7.0370909090909084</v>
+      </c>
+      <c r="M438" s="185"/>
+      <c r="N438" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="O438" s="44">
+        <v>200</v>
+      </c>
+      <c r="P438" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="439" spans="1:17">
+      <c r="A439" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B439" s="28" t="s">
+        <v>617</v>
+      </c>
+      <c r="C439" s="191">
+        <v>1000</v>
+      </c>
+      <c r="D439" s="69" t="s">
+        <v>626</v>
+      </c>
+      <c r="E439" s="192">
+        <v>20000</v>
+      </c>
+      <c r="F439" s="193">
+        <v>240</v>
+      </c>
+      <c r="G439" s="194">
+        <f t="shared" ref="G439:G447" si="165">E439+(F439*600)</f>
+        <v>164000</v>
+      </c>
+      <c r="H439" s="195">
+        <v>11000</v>
+      </c>
+      <c r="I439" s="196">
+        <f t="shared" si="161"/>
+        <v>1100</v>
+      </c>
+      <c r="J439" s="34">
+        <f t="shared" si="162"/>
+        <v>6.7073170731707321E-2</v>
+      </c>
+      <c r="K439" s="34">
+        <f t="shared" si="163"/>
+        <v>14.909090909090908</v>
+      </c>
+      <c r="L439" s="88">
+        <f t="shared" si="164"/>
+        <v>7.0370909090909084</v>
+      </c>
+      <c r="N439" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="O439" s="44">
+        <v>300</v>
+      </c>
+      <c r="P439" s="1">
+        <f>O438+O439</f>
+        <v>500</v>
+      </c>
+      <c r="Q439" s="1">
+        <f>P439*600</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="440" spans="1:17">
+      <c r="A440" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B440" s="28" t="s">
+        <v>618</v>
+      </c>
+      <c r="C440" s="191">
+        <v>2000</v>
+      </c>
+      <c r="D440" s="69" t="s">
+        <v>626</v>
+      </c>
+      <c r="E440" s="192">
+        <v>30000</v>
+      </c>
+      <c r="F440" s="193">
+        <v>500</v>
+      </c>
+      <c r="G440" s="194">
+        <f t="shared" si="165"/>
+        <v>330000</v>
+      </c>
+      <c r="H440" s="195">
+        <v>22000</v>
+      </c>
+      <c r="I440" s="196">
+        <f t="shared" si="161"/>
+        <v>2200</v>
+      </c>
+      <c r="J440" s="34">
+        <f t="shared" si="162"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="K440" s="34">
+        <f t="shared" si="163"/>
+        <v>15</v>
+      </c>
+      <c r="L440" s="88">
+        <f t="shared" si="164"/>
+        <v>7.0799999999999992</v>
+      </c>
+      <c r="N440" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="O440" s="44">
+        <v>500</v>
+      </c>
+      <c r="P440" s="1">
+        <f>P439+O440</f>
+        <v>1000</v>
+      </c>
+      <c r="Q440" s="1">
+        <f t="shared" ref="Q440:Q447" si="166">P440*600</f>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="441" spans="1:17">
+      <c r="A441" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B441" s="28" t="s">
+        <v>619</v>
+      </c>
+      <c r="C441" s="191">
+        <v>3000</v>
+      </c>
+      <c r="D441" s="69" t="s">
+        <v>626</v>
+      </c>
+      <c r="E441" s="192">
+        <v>45000</v>
+      </c>
+      <c r="F441" s="193">
+        <v>750</v>
+      </c>
+      <c r="G441" s="194">
+        <f t="shared" si="165"/>
+        <v>495000</v>
+      </c>
+      <c r="H441" s="195">
+        <v>33000</v>
+      </c>
+      <c r="I441" s="196">
+        <f t="shared" si="161"/>
+        <v>3300</v>
+      </c>
+      <c r="J441" s="34">
+        <f t="shared" si="162"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="K441" s="34">
+        <f t="shared" si="163"/>
+        <v>15</v>
+      </c>
+      <c r="L441" s="88">
+        <f t="shared" si="164"/>
+        <v>7.0799999999999992</v>
+      </c>
+      <c r="N441" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="O441" s="44">
+        <v>700</v>
+      </c>
+      <c r="P441" s="1">
+        <f t="shared" ref="P441:P447" si="167">P440+O441</f>
+        <v>1700</v>
+      </c>
+      <c r="Q441" s="1">
+        <f t="shared" si="166"/>
+        <v>1020000</v>
+      </c>
+    </row>
+    <row r="442" spans="1:17">
+      <c r="A442" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B442" s="28" t="s">
+        <v>620</v>
+      </c>
+      <c r="C442" s="191">
+        <v>4000</v>
+      </c>
+      <c r="D442" s="69" t="s">
+        <v>626</v>
+      </c>
+      <c r="E442" s="147">
+        <v>20000</v>
+      </c>
+      <c r="F442" s="128">
+        <v>240</v>
+      </c>
+      <c r="G442" s="32">
+        <f t="shared" si="165"/>
+        <v>164000</v>
+      </c>
+      <c r="H442" s="49">
+        <v>11000</v>
+      </c>
+      <c r="I442" s="100">
+        <f t="shared" si="161"/>
+        <v>1100</v>
+      </c>
+      <c r="J442" s="34">
+        <f t="shared" si="162"/>
+        <v>6.7073170731707321E-2</v>
+      </c>
+      <c r="K442" s="34">
+        <f t="shared" si="163"/>
+        <v>14.909090909090908</v>
+      </c>
+      <c r="L442" s="88">
+        <f t="shared" si="164"/>
+        <v>7.0370909090909084</v>
+      </c>
+      <c r="N442" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="O442" s="44">
+        <v>900</v>
+      </c>
+      <c r="P442" s="1">
+        <f t="shared" si="167"/>
+        <v>2600</v>
+      </c>
+      <c r="Q442" s="1">
+        <f t="shared" si="166"/>
+        <v>1560000</v>
+      </c>
+    </row>
+    <row r="443" spans="1:17">
+      <c r="A443" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B443" s="28" t="s">
+        <v>621</v>
+      </c>
+      <c r="C443" s="191">
+        <v>5000</v>
+      </c>
+      <c r="D443" s="69" t="s">
+        <v>626</v>
+      </c>
+      <c r="E443" s="147">
+        <v>30000</v>
+      </c>
+      <c r="F443" s="128">
+        <v>500</v>
+      </c>
+      <c r="G443" s="32">
+        <f t="shared" si="165"/>
+        <v>330000</v>
+      </c>
+      <c r="H443" s="49">
+        <v>22000</v>
+      </c>
+      <c r="I443" s="100">
+        <f t="shared" si="161"/>
+        <v>2200</v>
+      </c>
+      <c r="J443" s="34">
+        <f t="shared" si="162"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="K443" s="34">
+        <f t="shared" si="163"/>
+        <v>15</v>
+      </c>
+      <c r="L443" s="88">
+        <f t="shared" si="164"/>
+        <v>7.0799999999999992</v>
+      </c>
+      <c r="N443" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="O443" s="44">
+        <v>1100</v>
+      </c>
+      <c r="P443" s="1">
+        <f t="shared" si="167"/>
+        <v>3700</v>
+      </c>
+      <c r="Q443" s="1">
+        <f t="shared" si="166"/>
+        <v>2220000</v>
+      </c>
+    </row>
+    <row r="444" spans="1:17">
+      <c r="A444" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B444" s="28" t="s">
+        <v>622</v>
+      </c>
+      <c r="C444" s="191">
+        <v>6000</v>
+      </c>
+      <c r="D444" s="69" t="s">
+        <v>626</v>
+      </c>
+      <c r="E444" s="147">
+        <v>45000</v>
+      </c>
+      <c r="F444" s="128">
+        <v>750</v>
+      </c>
+      <c r="G444" s="32">
+        <f t="shared" si="165"/>
+        <v>495000</v>
+      </c>
+      <c r="H444" s="49">
+        <v>33000</v>
+      </c>
+      <c r="I444" s="100">
+        <f t="shared" si="161"/>
+        <v>3300</v>
+      </c>
+      <c r="J444" s="34">
+        <f t="shared" si="162"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="K444" s="34">
+        <f t="shared" si="163"/>
+        <v>15</v>
+      </c>
+      <c r="L444" s="88">
+        <f t="shared" si="164"/>
+        <v>7.0799999999999992</v>
+      </c>
+      <c r="N444" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="O444" s="44">
+        <v>1400</v>
+      </c>
+      <c r="P444" s="1">
+        <f t="shared" si="167"/>
+        <v>5100</v>
+      </c>
+      <c r="Q444" s="1">
+        <f t="shared" si="166"/>
+        <v>3060000</v>
+      </c>
+    </row>
+    <row r="445" spans="1:17">
+      <c r="A445" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B445" s="28" t="s">
+        <v>623</v>
+      </c>
+      <c r="C445" s="191">
+        <v>7000</v>
+      </c>
+      <c r="D445" s="69" t="s">
+        <v>626</v>
+      </c>
+      <c r="E445" s="192">
+        <v>20000</v>
+      </c>
+      <c r="F445" s="193">
+        <v>240</v>
+      </c>
+      <c r="G445" s="194">
+        <f t="shared" si="165"/>
+        <v>164000</v>
+      </c>
+      <c r="H445" s="195">
+        <v>11000</v>
+      </c>
+      <c r="I445" s="196">
+        <f t="shared" si="161"/>
+        <v>1100</v>
+      </c>
+      <c r="J445" s="34">
+        <f t="shared" si="162"/>
+        <v>6.7073170731707321E-2</v>
+      </c>
+      <c r="K445" s="34">
+        <f t="shared" si="163"/>
+        <v>14.909090909090908</v>
+      </c>
+      <c r="L445" s="88">
+        <f t="shared" si="164"/>
+        <v>7.0370909090909084</v>
+      </c>
+      <c r="N445" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="O445" s="44">
+        <v>1700</v>
+      </c>
+      <c r="P445" s="1">
+        <f t="shared" si="167"/>
+        <v>6800</v>
+      </c>
+      <c r="Q445" s="1">
+        <f t="shared" si="166"/>
+        <v>4080000</v>
+      </c>
+    </row>
+    <row r="446" spans="1:17">
+      <c r="A446" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B446" s="28" t="s">
+        <v>624</v>
+      </c>
+      <c r="C446" s="191">
+        <v>8000</v>
+      </c>
+      <c r="D446" s="69" t="s">
+        <v>626</v>
+      </c>
+      <c r="E446" s="192">
+        <v>30000</v>
+      </c>
+      <c r="F446" s="193">
+        <v>500</v>
+      </c>
+      <c r="G446" s="194">
+        <f t="shared" si="165"/>
+        <v>330000</v>
+      </c>
+      <c r="H446" s="195">
+        <v>22000</v>
+      </c>
+      <c r="I446" s="196">
+        <f t="shared" ref="I446:I447" si="168">H446/10</f>
+        <v>2200</v>
+      </c>
+      <c r="J446" s="34">
+        <f t="shared" ref="J446:J447" si="169">H446/G446</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="K446" s="34">
+        <f t="shared" ref="K446:K447" si="170">G446/H446</f>
+        <v>15</v>
+      </c>
+      <c r="L446" s="88">
+        <f t="shared" ref="L446:L447" si="171">K446/K$2</f>
+        <v>7.0799999999999992</v>
+      </c>
+      <c r="N446" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="O446" s="44">
+        <v>2000</v>
+      </c>
+      <c r="P446" s="1">
+        <f t="shared" si="167"/>
+        <v>8800</v>
+      </c>
+      <c r="Q446" s="1">
+        <f t="shared" si="166"/>
+        <v>5280000</v>
+      </c>
+    </row>
+    <row r="447" spans="1:17">
+      <c r="A447" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B447" s="28" t="s">
+        <v>625</v>
+      </c>
+      <c r="C447" s="191">
+        <v>9000</v>
+      </c>
+      <c r="D447" s="69" t="s">
+        <v>626</v>
+      </c>
+      <c r="E447" s="192">
+        <v>45000</v>
+      </c>
+      <c r="F447" s="193">
+        <v>750</v>
+      </c>
+      <c r="G447" s="194">
+        <f t="shared" si="165"/>
+        <v>495000</v>
+      </c>
+      <c r="H447" s="195">
+        <v>33000</v>
+      </c>
+      <c r="I447" s="196">
+        <f t="shared" si="168"/>
+        <v>3300</v>
+      </c>
+      <c r="J447" s="34">
+        <f t="shared" si="169"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="K447" s="34">
+        <f t="shared" si="170"/>
+        <v>15</v>
+      </c>
+      <c r="L447" s="88">
+        <f t="shared" si="171"/>
+        <v>7.0799999999999992</v>
+      </c>
+      <c r="O447" s="44">
+        <v>3500</v>
+      </c>
+      <c r="P447" s="1">
+        <f t="shared" si="167"/>
+        <v>12300</v>
+      </c>
+      <c r="Q447" s="1">
+        <f t="shared" si="166"/>
+        <v>7380000</v>
+      </c>
+    </row>
+    <row r="448" spans="1:17">
+      <c r="D448" s="187"/>
+      <c r="E448" s="182"/>
+      <c r="F448" s="182"/>
+      <c r="G448" s="188"/>
+      <c r="H448" s="197">
+        <f>SUM(H438:H447)</f>
+        <v>203500</v>
+      </c>
+      <c r="I448" s="179"/>
+      <c r="J448" s="189"/>
+      <c r="K448" s="189"/>
+      <c r="L448" s="190"/>
+    </row>
+    <row r="449" spans="2:12" s="55" customFormat="1">
+      <c r="B449" s="56" t="s">
         <v>450</v>
       </c>
-      <c r="C437" s="57"/>
-      <c r="E437" s="118"/>
-      <c r="F437" s="119"/>
-      <c r="G437" s="21"/>
-      <c r="L437" s="46"/>
-    </row>
-    <row r="438" spans="1:12">
-      <c r="B438" s="1" t="s">
+      <c r="C449" s="57"/>
+      <c r="E449" s="117"/>
+      <c r="F449" s="118"/>
+      <c r="G449" s="21"/>
+      <c r="L449" s="46"/>
+    </row>
+    <row r="450" spans="2:12">
+      <c r="B450" s="1" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="439" spans="1:12">
-      <c r="B439" s="1" t="s">
+    <row r="451" spans="2:12">
+      <c r="B451" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="440" spans="1:12">
-      <c r="B440" s="1" t="s">
+    <row r="452" spans="2:12">
+      <c r="B452" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="C440" s="1"/>
-      <c r="F440" s="115"/>
-      <c r="G440" s="1"/>
-      <c r="L440" s="1"/>
-    </row>
-    <row r="441" spans="1:12">
-      <c r="B441" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C441" s="1"/>
-      <c r="F441" s="115"/>
-      <c r="G441" s="1"/>
-      <c r="L441" s="1"/>
-    </row>
-    <row r="442" spans="1:12">
-      <c r="B442" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C442" s="1"/>
-      <c r="F442" s="115"/>
-      <c r="G442" s="1"/>
-      <c r="L442" s="1"/>
-    </row>
-    <row r="444" spans="1:12">
-      <c r="B444" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="C444" s="1"/>
-      <c r="F444" s="115"/>
-      <c r="G444" s="1"/>
-      <c r="L444" s="1"/>
-    </row>
-    <row r="445" spans="1:12">
-      <c r="B445" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C445" s="1"/>
-      <c r="F445" s="115"/>
-      <c r="G445" s="1"/>
-      <c r="L445" s="1"/>
-    </row>
-    <row r="446" spans="1:12">
-      <c r="B446" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="C446" s="1"/>
-      <c r="F446" s="115"/>
-      <c r="G446" s="1"/>
-      <c r="L446" s="1"/>
-    </row>
-    <row r="447" spans="1:12">
-      <c r="B447" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="C447" s="1"/>
-      <c r="F447" s="115"/>
-      <c r="G447" s="1"/>
-      <c r="L447" s="1"/>
-    </row>
-    <row r="448" spans="1:12">
-      <c r="B448" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="C448" s="1"/>
-      <c r="F448" s="115"/>
-      <c r="G448" s="1"/>
-      <c r="L448" s="1"/>
-    </row>
-    <row r="449" spans="1:12">
-      <c r="B449" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C449" s="1"/>
-      <c r="F449" s="115"/>
-      <c r="G449" s="1"/>
-      <c r="L449" s="1"/>
-    </row>
-    <row r="450" spans="1:12">
-      <c r="B450" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C450" s="1"/>
-      <c r="F450" s="115"/>
-      <c r="G450" s="1"/>
-      <c r="L450" s="1"/>
-    </row>
-    <row r="452" spans="1:12">
-      <c r="B452" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="C452" s="1"/>
-      <c r="F452" s="115"/>
+      <c r="F452" s="114"/>
       <c r="G452" s="1"/>
       <c r="L452" s="1"/>
     </row>
-    <row r="453" spans="1:12">
+    <row r="453" spans="2:12">
       <c r="B453" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C453" s="1"/>
-      <c r="F453" s="115"/>
+      <c r="F453" s="114"/>
       <c r="G453" s="1"/>
       <c r="L453" s="1"/>
     </row>
-    <row r="455" spans="1:12">
-      <c r="A455" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B455" s="28" t="s">
+    <row r="454" spans="2:12">
+      <c r="B454" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C454" s="1"/>
+      <c r="F454" s="114"/>
+      <c r="G454" s="1"/>
+      <c r="L454" s="1"/>
+    </row>
+    <row r="456" spans="2:12">
+      <c r="B456" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C456" s="1"/>
+      <c r="F456" s="114"/>
+      <c r="G456" s="1"/>
+      <c r="L456" s="1"/>
+    </row>
+    <row r="457" spans="2:12">
+      <c r="B457" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C457" s="1"/>
+      <c r="F457" s="114"/>
+      <c r="G457" s="1"/>
+      <c r="L457" s="1"/>
+    </row>
+    <row r="458" spans="2:12">
+      <c r="B458" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C458" s="1"/>
+      <c r="F458" s="114"/>
+      <c r="G458" s="1"/>
+      <c r="L458" s="1"/>
+    </row>
+    <row r="459" spans="2:12">
+      <c r="B459" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C459" s="1"/>
+      <c r="F459" s="114"/>
+      <c r="G459" s="1"/>
+      <c r="L459" s="1"/>
+    </row>
+    <row r="460" spans="2:12">
+      <c r="B460" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C460" s="1"/>
+      <c r="F460" s="114"/>
+      <c r="G460" s="1"/>
+      <c r="L460" s="1"/>
+    </row>
+    <row r="461" spans="2:12">
+      <c r="B461" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C461" s="1"/>
+      <c r="F461" s="114"/>
+      <c r="G461" s="1"/>
+      <c r="L461" s="1"/>
+    </row>
+    <row r="462" spans="2:12">
+      <c r="B462" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C462" s="1"/>
+      <c r="F462" s="114"/>
+      <c r="G462" s="1"/>
+      <c r="L462" s="1"/>
+    </row>
+    <row r="464" spans="2:12">
+      <c r="B464" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C464" s="1"/>
+      <c r="F464" s="114"/>
+      <c r="G464" s="1"/>
+      <c r="L464" s="1"/>
+    </row>
+    <row r="465" spans="1:12">
+      <c r="B465" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C465" s="1"/>
+      <c r="F465" s="114"/>
+      <c r="G465" s="1"/>
+      <c r="L465" s="1"/>
+    </row>
+    <row r="467" spans="1:12">
+      <c r="A467" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B467" s="28" t="s">
         <v>613</v>
       </c>
-      <c r="C455" s="44"/>
-      <c r="D455" s="28" t="s">
+      <c r="C467" s="44"/>
+      <c r="D467" s="28" t="s">
         <v>614</v>
       </c>
-      <c r="E455" s="148"/>
-      <c r="F455" s="120">
+      <c r="E467" s="147"/>
+      <c r="F467" s="119">
         <v>100</v>
       </c>
-      <c r="G455" s="48">
+      <c r="G467" s="48">
         <v>200</v>
       </c>
-      <c r="H455" s="33">
+      <c r="H467" s="33">
         <v>100</v>
       </c>
-      <c r="I455" s="102">
-        <f t="shared" ref="I455" si="161">H455/10</f>
+      <c r="I467" s="102">
+        <f t="shared" ref="I467" si="172">H467/10</f>
         <v>10</v>
       </c>
-      <c r="J455" s="163">
-        <f t="shared" ref="J455" si="162">H455/G455</f>
+      <c r="J467" s="162">
+        <f t="shared" ref="J467" si="173">H467/G467</f>
         <v>0.5</v>
       </c>
-      <c r="K455" s="162">
-        <f t="shared" ref="K455" si="163">G455/H455</f>
+      <c r="K467" s="161">
+        <f t="shared" ref="K467" si="174">G467/H467</f>
         <v>2</v>
       </c>
-      <c r="L455" s="45">
-        <f t="shared" ref="L455" si="164">K455/K$2</f>
+      <c r="L467" s="45">
+        <f t="shared" ref="L467" si="175">K467/K$2</f>
         <v>0.94399999999999995</v>
       </c>
     </row>
@@ -20269,7 +21049,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L6:L10">
-    <cfRule type="dataBar" priority="47">
+    <cfRule type="dataBar" priority="51">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20283,7 +21063,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L13:L17">
-    <cfRule type="dataBar" priority="15">
+    <cfRule type="dataBar" priority="19">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20297,7 +21077,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L20:L25">
-    <cfRule type="dataBar" priority="48">
+    <cfRule type="dataBar" priority="52">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20311,7 +21091,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L27:L31">
-    <cfRule type="dataBar" priority="45">
+    <cfRule type="dataBar" priority="49">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20325,7 +21105,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L33:L37">
-    <cfRule type="dataBar" priority="44">
+    <cfRule type="dataBar" priority="48">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20339,7 +21119,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L40:L44">
-    <cfRule type="dataBar" priority="35">
+    <cfRule type="dataBar" priority="39">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20353,7 +21133,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L46:L50">
-    <cfRule type="dataBar" priority="34">
+    <cfRule type="dataBar" priority="38">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20367,7 +21147,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L52:L56">
-    <cfRule type="dataBar" priority="33">
+    <cfRule type="dataBar" priority="37">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20381,7 +21161,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L58:L62">
-    <cfRule type="dataBar" priority="32">
+    <cfRule type="dataBar" priority="36">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20395,7 +21175,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L65:L69">
-    <cfRule type="dataBar" priority="43">
+    <cfRule type="dataBar" priority="47">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20409,7 +21189,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L71:L75">
-    <cfRule type="dataBar" priority="42">
+    <cfRule type="dataBar" priority="46">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20423,7 +21203,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L77:L81">
-    <cfRule type="dataBar" priority="31">
+    <cfRule type="dataBar" priority="35">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20437,7 +21217,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L84:L88">
-    <cfRule type="dataBar" priority="30">
+    <cfRule type="dataBar" priority="34">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20451,7 +21231,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L90:L94">
-    <cfRule type="dataBar" priority="29">
+    <cfRule type="dataBar" priority="33">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20465,7 +21245,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L96:L100">
-    <cfRule type="dataBar" priority="28">
+    <cfRule type="dataBar" priority="32">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20479,7 +21259,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L103:L107">
-    <cfRule type="dataBar" priority="41">
+    <cfRule type="dataBar" priority="45">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20493,7 +21273,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L109:L113">
-    <cfRule type="dataBar" priority="27">
+    <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20507,7 +21287,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L117:L128">
-    <cfRule type="dataBar" priority="40">
+    <cfRule type="dataBar" priority="44">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20521,7 +21301,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L132:L153">
-    <cfRule type="dataBar" priority="49">
+    <cfRule type="dataBar" priority="53">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20535,7 +21315,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L156:L180">
-    <cfRule type="dataBar" priority="50">
+    <cfRule type="dataBar" priority="54">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20549,7 +21329,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L183:L202">
-    <cfRule type="dataBar" priority="39">
+    <cfRule type="dataBar" priority="43">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20563,7 +21343,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L204:L223">
-    <cfRule type="dataBar" priority="38">
+    <cfRule type="dataBar" priority="42">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20577,7 +21357,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L225:L239">
-    <cfRule type="dataBar" priority="37">
+    <cfRule type="dataBar" priority="41">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20591,7 +21371,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L241:L250">
-    <cfRule type="dataBar" priority="36">
+    <cfRule type="dataBar" priority="40">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20605,7 +21385,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L291:L298">
-    <cfRule type="dataBar" priority="51">
+    <cfRule type="dataBar" priority="55">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20619,7 +21399,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L300:L307">
-    <cfRule type="dataBar" priority="24">
+    <cfRule type="dataBar" priority="28">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20633,7 +21413,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L310:L317">
-    <cfRule type="dataBar" priority="23">
+    <cfRule type="dataBar" priority="27">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20647,7 +21427,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L319:L326">
-    <cfRule type="dataBar" priority="22">
+    <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20661,7 +21441,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L328:L332">
-    <cfRule type="dataBar" priority="21">
+    <cfRule type="dataBar" priority="25">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20675,7 +21455,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L334:L338">
-    <cfRule type="dataBar" priority="20">
+    <cfRule type="dataBar" priority="24">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20689,7 +21469,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L396:L405">
-    <cfRule type="dataBar" priority="13">
+    <cfRule type="dataBar" priority="17">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20703,7 +21483,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L407:L415">
-    <cfRule type="dataBar" priority="19">
+    <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20716,8 +21496,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L417:L435">
-    <cfRule type="dataBar" priority="12">
+  <conditionalFormatting sqref="L417:L436">
+    <cfRule type="dataBar" priority="16">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20731,7 +21511,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L376:L393">
-    <cfRule type="dataBar" priority="14">
+    <cfRule type="dataBar" priority="18">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20745,7 +21525,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L365:L374">
-    <cfRule type="dataBar" priority="11">
+    <cfRule type="dataBar" priority="15">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20759,7 +21539,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L291:L326">
-    <cfRule type="dataBar" priority="10">
+    <cfRule type="dataBar" priority="14">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20773,7 +21553,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L328:L338">
-    <cfRule type="dataBar" priority="9">
+    <cfRule type="dataBar" priority="13">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20787,7 +21567,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L269:L288">
-    <cfRule type="dataBar" priority="8">
+    <cfRule type="dataBar" priority="12">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20801,7 +21581,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L183:L250">
-    <cfRule type="dataBar" priority="7">
+    <cfRule type="dataBar" priority="11">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20815,7 +21595,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L180">
-    <cfRule type="dataBar" priority="6">
+    <cfRule type="dataBar" priority="10">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20828,8 +21608,50 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L6:L435">
+  <conditionalFormatting sqref="L467">
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{697BCDA5-6DD0-4FA2-A6EF-9605CFB7C0C2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L467">
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E70611B5-6FD7-4807-9027-D7E6103C64D0}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L467">
     <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{42399625-6295-4C03-BDDE-07A3ABDB2C86}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L448">
+    <cfRule type="dataBar" priority="63">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20842,8 +21664,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L263:L435 L258:L261 L254:L256 L6:L252">
-    <cfRule type="dataBar" priority="4">
+  <conditionalFormatting sqref="L258:L261 L254:L256 L6:L252 L263:L448">
+    <cfRule type="dataBar" priority="65">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20856,8 +21678,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L455">
-    <cfRule type="dataBar" priority="3">
+  <conditionalFormatting sqref="L438:L448">
+    <cfRule type="dataBar" priority="70">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20865,13 +21687,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{697BCDA5-6DD0-4FA2-A6EF-9605CFB7C0C2}</x14:id>
+          <x14:id>{74620703-BF19-4640-AC24-E30BD4F7C856}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L455">
-    <cfRule type="dataBar" priority="2">
+  <conditionalFormatting sqref="L437:L448">
+    <cfRule type="dataBar" priority="72">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -20879,12 +21701,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E70611B5-6FD7-4807-9027-D7E6103C64D0}</x14:id>
+          <x14:id>{DDE7A09C-B005-4F3B-AFC9-56110C2EA5C2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L455">
+  <conditionalFormatting sqref="L438:L447">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -20893,7 +21715,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42399625-6295-4C03-BDDE-07A3ABDB2C86}</x14:id>
+          <x14:id>{6039BD2E-A36A-4178-BF24-B8582A2FF2AD}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21273,7 +22095,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>L417:L435</xm:sqref>
+          <xm:sqref>L417:L436</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{3E45A48B-3D70-42D1-BAC8-79BCC297763B}">
@@ -21367,6 +22189,43 @@
           <xm:sqref>L6:L180</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{697BCDA5-6DD0-4FA2-A6EF-9605CFB7C0C2}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L467</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{E70611B5-6FD7-4807-9027-D7E6103C64D0}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L467</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{42399625-6295-4C03-BDDE-07A3ABDB2C86}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L467</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{3E171C8C-BC18-4404-B040-C93AEC6CD1B3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
@@ -21377,7 +22236,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>L6:L435</xm:sqref>
+          <xm:sqref>L6:L448</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{6A0D2B79-679B-4D8C-AA40-0EB9DFA51DB1}">
@@ -21390,21 +22249,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>L263:L435 L258:L261 L254:L256 L6:L252</xm:sqref>
+          <xm:sqref>L258:L261 L254:L256 L6:L252 L263:L448</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{697BCDA5-6DD0-4FA2-A6EF-9605CFB7C0C2}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L455</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E70611B5-6FD7-4807-9027-D7E6103C64D0}">
+          <x14:cfRule type="dataBar" id="{74620703-BF19-4640-AC24-E30BD4F7C856}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21414,10 +22262,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>L455</xm:sqref>
+          <xm:sqref>L438:L448</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{42399625-6295-4C03-BDDE-07A3ABDB2C86}">
+          <x14:cfRule type="dataBar" id="{DDE7A09C-B005-4F3B-AFC9-56110C2EA5C2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -21427,7 +22275,20 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>L455</xm:sqref>
+          <xm:sqref>L437:L448</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6039BD2E-A36A-4178-BF24-B8582A2FF2AD}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L438:L447</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/BM(최종).xlsx
+++ b/BM(최종).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A3053E-D0B1-478C-821C-E15CCD85FC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637AD15A-1C33-4849-ABBF-71A07EEBB65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
+    <workbookView xWindow="44460" yWindow="2475" windowWidth="22740" windowHeight="15480" activeTab="1" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
   </bookViews>
   <sheets>
     <sheet name="재화 기준" sheetId="2" r:id="rId1"/>
@@ -2704,7 +2704,7 @@
     <numFmt numFmtId="178" formatCode="0\ &quot;개&quot;"/>
     <numFmt numFmtId="179" formatCode="_-\_xd83d_\_xdc8e_* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="0.0"/>
-    <numFmt numFmtId="183" formatCode="_-&quot;마&quot;&quot;일&quot;\ * #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="181" formatCode="_-&quot;마&quot;&quot;일&quot;\ * #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -3039,7 +3039,7 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3602,13 +3602,7 @@
     <xf numFmtId="179" fontId="0" fillId="22" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="181" fontId="3" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
@@ -3619,6 +3613,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -8619,12 +8616,12 @@
       </c>
     </row>
     <row r="114" spans="1:13">
-      <c r="F114" s="193">
+      <c r="F114" s="191">
         <f>SUM(F109:F113)</f>
         <v>3180</v>
       </c>
       <c r="G114" s="17"/>
-      <c r="H114" s="191">
+      <c r="H114" s="189">
         <f>SUM(H109:H113)</f>
         <v>107800</v>
       </c>
@@ -9395,11 +9392,11 @@
         <v>18000</v>
       </c>
       <c r="F137" s="128">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="G137" s="48">
         <f t="shared" si="54"/>
-        <v>115500</v>
+        <v>117000</v>
       </c>
       <c r="H137" s="49">
         <v>11000</v>
@@ -9410,15 +9407,15 @@
       </c>
       <c r="J137" s="50">
         <f t="shared" si="47"/>
-        <v>9.5238095238095233E-2</v>
+        <v>9.4017094017094016E-2</v>
       </c>
       <c r="K137" s="50">
         <f t="shared" si="48"/>
-        <v>10.5</v>
+        <v>10.636363636363637</v>
       </c>
       <c r="L137" s="45">
         <f t="shared" si="55"/>
-        <v>4.9559999999999995</v>
+        <v>5.0203636363636361</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>600</v>
@@ -10033,7 +10030,7 @@
     <row r="152" spans="1:13">
       <c r="D152" s="7"/>
       <c r="E152" s="67"/>
-      <c r="H152" s="191">
+      <c r="H152" s="189">
         <f>SUM(H132:H151)</f>
         <v>107800</v>
       </c>
@@ -11299,7 +11296,7 @@
       </c>
     </row>
     <row r="184" spans="1:13">
-      <c r="H184" s="191">
+      <c r="H184" s="189">
         <f>SUM(H159:H183)</f>
         <v>808500</v>
       </c>
@@ -12066,11 +12063,11 @@
       </c>
     </row>
     <row r="206" spans="1:12">
-      <c r="G206" s="192">
+      <c r="G206" s="190">
         <f>SUM(G186:G195)</f>
         <v>3140000</v>
       </c>
-      <c r="H206" s="191">
+      <c r="H206" s="189">
         <f>SUM(H186:H195)</f>
         <v>244200</v>
       </c>
@@ -13886,7 +13883,7 @@
       </c>
     </row>
     <row r="254" spans="1:12">
-      <c r="H254" s="191">
+      <c r="H254" s="189">
         <f>SUM(H244:H253)</f>
         <v>244200</v>
       </c>
@@ -13909,7 +13906,7 @@
       <c r="B256" s="28" t="s">
         <v>441</v>
       </c>
-      <c r="D256" s="188" t="s">
+      <c r="D256" s="192" t="s">
         <v>437</v>
       </c>
       <c r="E256" s="137"/>
@@ -13944,7 +13941,7 @@
       <c r="B257" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="D257" s="188"/>
+      <c r="D257" s="192"/>
       <c r="F257" s="116"/>
       <c r="G257" s="17"/>
       <c r="H257" s="9"/>
@@ -13953,7 +13950,7 @@
       <c r="K257" s="6"/>
     </row>
     <row r="258" spans="1:13">
-      <c r="D258" s="188"/>
+      <c r="D258" s="192"/>
       <c r="F258" s="116"/>
       <c r="G258" s="17"/>
       <c r="H258" s="9"/>
@@ -13971,7 +13968,7 @@
       <c r="B260" s="28" t="s">
         <v>438</v>
       </c>
-      <c r="D260" s="188" t="s">
+      <c r="D260" s="192" t="s">
         <v>494</v>
       </c>
       <c r="E260" s="137"/>
@@ -14006,15 +14003,15 @@
       <c r="B261" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D261" s="188"/>
+      <c r="D261" s="192"/>
       <c r="E261" s="137"/>
     </row>
     <row r="262" spans="1:13">
-      <c r="D262" s="188"/>
+      <c r="D262" s="192"/>
       <c r="E262" s="137"/>
     </row>
     <row r="263" spans="1:13" ht="13.5" customHeight="1">
-      <c r="D263" s="188"/>
+      <c r="D263" s="192"/>
       <c r="E263" s="137"/>
     </row>
     <row r="264" spans="1:13">
@@ -14027,7 +14024,7 @@
       <c r="B265" s="28" t="s">
         <v>439</v>
       </c>
-      <c r="D265" s="188" t="s">
+      <c r="D265" s="192" t="s">
         <v>436</v>
       </c>
       <c r="E265" s="137"/>
@@ -14062,15 +14059,15 @@
       <c r="B266" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D266" s="188"/>
+      <c r="D266" s="192"/>
       <c r="E266" s="137"/>
     </row>
     <row r="267" spans="1:13">
-      <c r="D267" s="188"/>
+      <c r="D267" s="192"/>
       <c r="E267" s="137"/>
     </row>
     <row r="268" spans="1:13">
-      <c r="D268" s="188"/>
+      <c r="D268" s="192"/>
       <c r="E268" s="137"/>
     </row>
     <row r="270" spans="1:13" s="55" customFormat="1">
@@ -15303,7 +15300,7 @@
       </c>
     </row>
     <row r="301" spans="1:13">
-      <c r="A301" s="189" t="s">
+      <c r="A301" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B301" s="163" t="s">
@@ -20953,7 +20950,7 @@
       <c r="G452" s="21"/>
       <c r="L452" s="46"/>
     </row>
-    <row r="453" spans="1:17" s="189" customFormat="1">
+    <row r="453" spans="1:17">
       <c r="A453" s="1" t="s">
         <v>74</v>
       </c>
@@ -20975,14 +20972,12 @@
       <c r="H453" s="33">
         <v>55000</v>
       </c>
-      <c r="I453" s="190">
+      <c r="I453" s="188">
         <f t="shared" ref="I453" si="174">H453/10</f>
         <v>5500</v>
       </c>
       <c r="J453" s="50"/>
       <c r="K453" s="50"/>
-      <c r="L453" s="45"/>
-      <c r="M453" s="1"/>
     </row>
     <row r="456" spans="1:17">
       <c r="B456" s="1" t="s">

--- a/BM(최종).xlsx
+++ b/BM(최종).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637AD15A-1C33-4849-ABBF-71A07EEBB65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13071460-7B60-46CE-9DBF-75EC81145D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44460" yWindow="2475" windowWidth="22740" windowHeight="15480" activeTab="1" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28965" windowHeight="20880" activeTab="1" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
   </bookViews>
   <sheets>
     <sheet name="재화 기준" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="633">
   <si>
     <t>개수</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2588,10 +2588,6 @@
   </si>
   <si>
     <t>다이아+골드</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>다이아+1,2,3,4 입장권</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -14183,7 +14179,7 @@
         <v>74</v>
       </c>
       <c r="B274" s="78" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C274" s="81" t="s">
         <v>152</v>
@@ -14227,7 +14223,7 @@
         <v>74</v>
       </c>
       <c r="B275" s="78" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C275" s="81" t="s">
         <v>153</v>
@@ -19103,17 +19099,17 @@
         <v>262</v>
       </c>
       <c r="D410" s="28" t="s">
-        <v>604</v>
+        <v>48</v>
       </c>
       <c r="E410" s="148">
-        <v>14000</v>
+        <v>60000</v>
       </c>
       <c r="F410" s="119">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G410" s="48">
         <f>4*10000*F410+E410</f>
-        <v>94000</v>
+        <v>60000</v>
       </c>
       <c r="H410" s="33">
         <v>3300</v>
@@ -19124,15 +19120,15 @@
       </c>
       <c r="J410" s="50">
         <f t="shared" ref="J410:J418" si="152">H410/G410</f>
-        <v>3.5106382978723406E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K410" s="50">
         <f t="shared" ref="K410:K418" si="153">G410/H410</f>
-        <v>28.484848484848484</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L410" s="45">
         <f t="shared" ref="L410" si="154">K410/K$2</f>
-        <v>13.444848484848483</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M410" s="1" t="s">
         <v>600</v>
@@ -19149,17 +19145,17 @@
         <v>263</v>
       </c>
       <c r="D411" s="28" t="s">
-        <v>604</v>
+        <v>456</v>
       </c>
       <c r="E411" s="148">
-        <v>24000</v>
+        <v>50000</v>
       </c>
       <c r="F411" s="119">
-        <v>3</v>
+        <v>150000</v>
       </c>
       <c r="G411" s="48">
-        <f t="shared" ref="G411:G418" si="155">4*10000*F411+E411</f>
-        <v>144000</v>
+        <f>E411+(F411*1/3)</f>
+        <v>100000</v>
       </c>
       <c r="H411" s="33">
         <v>5500</v>
@@ -19170,15 +19166,15 @@
       </c>
       <c r="J411" s="50">
         <f t="shared" si="152"/>
-        <v>3.8194444444444448E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K411" s="50">
         <f t="shared" si="153"/>
-        <v>26.181818181818183</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L411" s="45">
-        <f t="shared" ref="L411:L414" si="156">K411/K$2</f>
-        <v>12.357818181818182</v>
+        <f t="shared" ref="L411:L414" si="155">K411/K$2</f>
+        <v>8.581818181818182</v>
       </c>
       <c r="M411" s="1" t="s">
         <v>600</v>
@@ -19195,17 +19191,17 @@
         <v>264</v>
       </c>
       <c r="D412" s="28" t="s">
-        <v>604</v>
+        <v>456</v>
       </c>
       <c r="E412" s="148">
-        <v>48000</v>
+        <v>50000</v>
       </c>
       <c r="F412" s="119">
-        <v>4</v>
+        <v>450000</v>
       </c>
       <c r="G412" s="48">
-        <f t="shared" si="155"/>
-        <v>208000</v>
+        <f t="shared" ref="G412:G418" si="156">E412+(F412*1/3)</f>
+        <v>200000</v>
       </c>
       <c r="H412" s="33">
         <v>11000</v>
@@ -19216,15 +19212,15 @@
       </c>
       <c r="J412" s="50">
         <f t="shared" si="152"/>
-        <v>5.2884615384615384E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K412" s="50">
         <f t="shared" si="153"/>
-        <v>18.90909090909091</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L412" s="45">
-        <f t="shared" si="156"/>
-        <v>8.9250909090909083</v>
+        <f t="shared" si="155"/>
+        <v>8.581818181818182</v>
       </c>
       <c r="M412" s="1" t="s">
         <v>600</v>
@@ -19241,17 +19237,17 @@
         <v>265</v>
       </c>
       <c r="D413" s="28" t="s">
-        <v>604</v>
+        <v>456</v>
       </c>
       <c r="E413" s="147">
-        <v>150000</v>
+        <v>50000</v>
       </c>
       <c r="F413" s="119">
-        <v>10</v>
+        <v>1650000</v>
       </c>
       <c r="G413" s="48">
-        <f t="shared" si="155"/>
-        <v>550000</v>
+        <f t="shared" si="156"/>
+        <v>600000</v>
       </c>
       <c r="H413" s="33">
         <v>33000</v>
@@ -19262,15 +19258,15 @@
       </c>
       <c r="J413" s="50">
         <f t="shared" si="152"/>
-        <v>0.06</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K413" s="50">
         <f t="shared" si="153"/>
-        <v>16.666666666666668</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L413" s="45">
-        <f t="shared" si="156"/>
-        <v>7.8666666666666671</v>
+        <f t="shared" si="155"/>
+        <v>8.581818181818182</v>
       </c>
       <c r="M413" s="1" t="s">
         <v>600</v>
@@ -19287,36 +19283,36 @@
         <v>266</v>
       </c>
       <c r="D414" s="28" t="s">
-        <v>604</v>
+        <v>456</v>
       </c>
       <c r="E414" s="147">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="F414" s="119">
-        <v>15</v>
+        <v>1650000</v>
       </c>
       <c r="G414" s="48">
-        <f t="shared" si="155"/>
-        <v>800000</v>
+        <f t="shared" si="156"/>
+        <v>600000</v>
       </c>
       <c r="H414" s="33">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I414" s="102">
         <f t="shared" si="147"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J414" s="50">
         <f t="shared" si="152"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K414" s="50">
         <f t="shared" si="153"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L414" s="45">
-        <f t="shared" si="156"/>
-        <v>6.8654545454545453</v>
+        <f t="shared" si="155"/>
+        <v>8.581818181818182</v>
       </c>
       <c r="M414" s="1" t="s">
         <v>600</v>
@@ -19333,36 +19329,36 @@
         <v>267</v>
       </c>
       <c r="D415" s="28" t="s">
-        <v>604</v>
+        <v>456</v>
       </c>
       <c r="E415" s="147">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="F415" s="119">
-        <v>15</v>
+        <v>1650000</v>
       </c>
       <c r="G415" s="48">
-        <f t="shared" si="155"/>
-        <v>800000</v>
+        <f t="shared" si="156"/>
+        <v>600000</v>
       </c>
       <c r="H415" s="33">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I415" s="102">
         <f t="shared" si="147"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J415" s="50">
         <f t="shared" si="152"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K415" s="50">
         <f t="shared" si="153"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L415" s="45">
         <f t="shared" ref="L415:L418" si="157">K415/K$2</f>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M415" s="1" t="s">
         <v>600</v>
@@ -19379,36 +19375,36 @@
         <v>268</v>
       </c>
       <c r="D416" s="28" t="s">
-        <v>604</v>
+        <v>456</v>
       </c>
       <c r="E416" s="147">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="F416" s="119">
-        <v>15</v>
+        <v>1650000</v>
       </c>
       <c r="G416" s="48">
-        <f t="shared" si="155"/>
-        <v>800000</v>
+        <f t="shared" si="156"/>
+        <v>600000</v>
       </c>
       <c r="H416" s="33">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I416" s="102">
         <f t="shared" si="147"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J416" s="50">
         <f t="shared" si="152"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K416" s="50">
         <f t="shared" si="153"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L416" s="45">
         <f t="shared" si="157"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M416" s="1" t="s">
         <v>600</v>
@@ -19425,36 +19421,36 @@
         <v>269</v>
       </c>
       <c r="D417" s="28" t="s">
-        <v>604</v>
+        <v>456</v>
       </c>
       <c r="E417" s="147">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="F417" s="119">
-        <v>15</v>
+        <v>1650000</v>
       </c>
       <c r="G417" s="48">
-        <f t="shared" si="155"/>
-        <v>800000</v>
+        <f t="shared" si="156"/>
+        <v>600000</v>
       </c>
       <c r="H417" s="33">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I417" s="102">
         <f t="shared" si="147"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J417" s="50">
         <f t="shared" si="152"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K417" s="50">
         <f t="shared" si="153"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L417" s="45">
         <f t="shared" si="157"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M417" s="1" t="s">
         <v>600</v>
@@ -19471,36 +19467,36 @@
         <v>270</v>
       </c>
       <c r="D418" s="28" t="s">
-        <v>604</v>
+        <v>456</v>
       </c>
       <c r="E418" s="147">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="F418" s="119">
-        <v>15</v>
+        <v>1650000</v>
       </c>
       <c r="G418" s="48">
-        <f t="shared" si="155"/>
-        <v>800000</v>
+        <f t="shared" si="156"/>
+        <v>600000</v>
       </c>
       <c r="H418" s="33">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I418" s="102">
         <f t="shared" si="147"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J418" s="50">
         <f t="shared" si="152"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K418" s="50">
         <f t="shared" si="153"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L418" s="45">
         <f t="shared" si="157"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M418" s="1" t="s">
         <v>600</v>
@@ -19509,7 +19505,7 @@
     <row r="419" spans="1:13">
       <c r="H419" s="13">
         <f>SUM(H410:H418)</f>
-        <v>327800</v>
+        <v>217800</v>
       </c>
     </row>
     <row r="420" spans="1:13">
@@ -20343,7 +20339,7 @@
     </row>
     <row r="440" spans="1:17">
       <c r="B440" s="22" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D440" s="26"/>
       <c r="E440" s="139"/>
@@ -20355,13 +20351,13 @@
       <c r="K440" s="25"/>
       <c r="L440" s="89"/>
       <c r="N440" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="O440" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="P440" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="441" spans="1:17">
@@ -20369,13 +20365,13 @@
         <v>74</v>
       </c>
       <c r="B441" s="28" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C441" s="182">
         <v>200</v>
       </c>
       <c r="D441" s="69" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E441" s="147">
         <v>10000</v>
@@ -20408,7 +20404,7 @@
       </c>
       <c r="M441" s="178"/>
       <c r="N441" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="O441" s="44">
         <v>200</v>
@@ -20422,13 +20418,13 @@
         <v>74</v>
       </c>
       <c r="B442" s="28" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C442" s="182">
         <v>1000</v>
       </c>
       <c r="D442" s="69" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E442" s="183">
         <v>20000</v>
@@ -20460,7 +20456,7 @@
         <v>7.0370909090909084</v>
       </c>
       <c r="N442" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="O442" s="44">
         <v>300</v>
@@ -20479,13 +20475,13 @@
         <v>74</v>
       </c>
       <c r="B443" s="28" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C443" s="182">
         <v>2000</v>
       </c>
       <c r="D443" s="69" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E443" s="183">
         <v>30000</v>
@@ -20517,7 +20513,7 @@
         <v>7.0799999999999992</v>
       </c>
       <c r="N443" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="O443" s="44">
         <v>500</v>
@@ -20536,13 +20532,13 @@
         <v>74</v>
       </c>
       <c r="B444" s="28" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C444" s="182">
         <v>3000</v>
       </c>
       <c r="D444" s="69" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E444" s="183">
         <v>45000</v>
@@ -20574,7 +20570,7 @@
         <v>7.0799999999999992</v>
       </c>
       <c r="N444" s="1" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="O444" s="44">
         <v>700</v>
@@ -20593,13 +20589,13 @@
         <v>74</v>
       </c>
       <c r="B445" s="28" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C445" s="182">
         <v>4000</v>
       </c>
       <c r="D445" s="69" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E445" s="147">
         <v>20000</v>
@@ -20631,7 +20627,7 @@
         <v>7.0370909090909084</v>
       </c>
       <c r="N445" s="1" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="O445" s="44">
         <v>900</v>
@@ -20650,13 +20646,13 @@
         <v>74</v>
       </c>
       <c r="B446" s="28" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C446" s="182">
         <v>5000</v>
       </c>
       <c r="D446" s="69" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E446" s="147">
         <v>30000</v>
@@ -20688,7 +20684,7 @@
         <v>7.0799999999999992</v>
       </c>
       <c r="N446" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="O446" s="44">
         <v>1100</v>
@@ -20707,13 +20703,13 @@
         <v>74</v>
       </c>
       <c r="B447" s="28" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C447" s="182">
         <v>6000</v>
       </c>
       <c r="D447" s="69" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E447" s="147">
         <v>45000</v>
@@ -20745,7 +20741,7 @@
         <v>7.0799999999999992</v>
       </c>
       <c r="N447" s="1" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="O447" s="44">
         <v>1400</v>
@@ -20764,13 +20760,13 @@
         <v>74</v>
       </c>
       <c r="B448" s="28" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C448" s="182">
         <v>7000</v>
       </c>
       <c r="D448" s="69" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E448" s="183">
         <v>20000</v>
@@ -20802,7 +20798,7 @@
         <v>7.0370909090909084</v>
       </c>
       <c r="N448" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="O448" s="44">
         <v>1700</v>
@@ -20821,13 +20817,13 @@
         <v>74</v>
       </c>
       <c r="B449" s="28" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C449" s="182">
         <v>8000</v>
       </c>
       <c r="D449" s="69" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E449" s="183">
         <v>30000</v>
@@ -20859,7 +20855,7 @@
         <v>7.0799999999999992</v>
       </c>
       <c r="N449" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="O449" s="44">
         <v>2000</v>
@@ -20878,13 +20874,13 @@
         <v>74</v>
       </c>
       <c r="B450" s="28" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C450" s="182">
         <v>9000</v>
       </c>
       <c r="D450" s="69" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E450" s="183">
         <v>45000</v>
@@ -20959,7 +20955,7 @@
       </c>
       <c r="C453" s="44"/>
       <c r="D453" s="28" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E453" s="147"/>
       <c r="F453" s="119">
@@ -21107,11 +21103,11 @@
         <v>74</v>
       </c>
       <c r="B471" s="28" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C471" s="44"/>
       <c r="D471" s="28" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E471" s="147"/>
       <c r="F471" s="119">
@@ -21878,7 +21874,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="G227 I32 I45 G302 G206" formula="1"/>
+    <ignoredError sqref="G227 I32 I45 G302 G206 G411" formula="1"/>
     <ignoredError sqref="P13:P17 P4 P6:P10 H311 F311 F302 H302 H206" formulaRange="1"/>
     <ignoredError sqref="J399:J408" evalError="1"/>
   </ignoredErrors>

--- a/BM(최종).xlsx
+++ b/BM(최종).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13071460-7B60-46CE-9DBF-75EC81145D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C96008-F8E8-40B6-95CB-DF6F55193CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28965" windowHeight="20880" activeTab="1" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
+    <workbookView xWindow="-105" yWindow="285" windowWidth="27300" windowHeight="15360" activeTab="1" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
   </bookViews>
   <sheets>
     <sheet name="재화 기준" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="634">
   <si>
     <t>개수</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2588,6 +2588,10 @@
   </si>
   <si>
     <t>다이아+골드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다이아+1,2,3,4 입장권</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3035,7 +3039,7 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3613,6 +3617,9 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="나쁨" xfId="1" builtinId="27"/>
@@ -11320,12 +11327,12 @@
         <v>107</v>
       </c>
       <c r="E186" s="130">
-        <v>2800</v>
+        <v>3750</v>
       </c>
       <c r="F186" s="129"/>
       <c r="G186" s="80">
         <f>E186*25</f>
-        <v>70000</v>
+        <v>93750</v>
       </c>
       <c r="H186" s="82">
         <v>5500</v>
@@ -11336,15 +11343,15 @@
       </c>
       <c r="J186" s="83">
         <f t="shared" ref="J186:J205" si="84">H186/G186</f>
-        <v>7.857142857142857E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K186" s="83">
         <f t="shared" ref="K186:K205" si="85">G186/H186</f>
-        <v>12.727272727272727</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L186" s="45">
         <f>K186/K$2</f>
-        <v>6.0072727272727269</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="187" spans="1:13">
@@ -11359,12 +11366,12 @@
         <v>108</v>
       </c>
       <c r="E187" s="130">
-        <v>4000</v>
+        <v>5300</v>
       </c>
       <c r="F187" s="129"/>
       <c r="G187" s="80">
         <f t="shared" ref="G187:G205" si="86">E187*25</f>
-        <v>100000</v>
+        <v>132500</v>
       </c>
       <c r="H187" s="82">
         <v>7700</v>
@@ -11375,15 +11382,15 @@
       </c>
       <c r="J187" s="83">
         <f t="shared" si="84"/>
-        <v>7.6999999999999999E-2</v>
+        <v>5.811320754716981E-2</v>
       </c>
       <c r="K187" s="83">
         <f t="shared" si="85"/>
-        <v>12.987012987012987</v>
+        <v>17.207792207792206</v>
       </c>
       <c r="L187" s="45">
         <f>K187/K$2</f>
-        <v>6.1298701298701292</v>
+        <v>8.1220779220779207</v>
       </c>
     </row>
     <row r="188" spans="1:13">
@@ -11398,12 +11405,12 @@
         <v>109</v>
       </c>
       <c r="E188" s="130">
-        <v>5600</v>
+        <v>7500</v>
       </c>
       <c r="F188" s="129"/>
       <c r="G188" s="80">
         <f t="shared" si="86"/>
-        <v>140000</v>
+        <v>187500</v>
       </c>
       <c r="H188" s="82">
         <v>11000</v>
@@ -11414,15 +11421,15 @@
       </c>
       <c r="J188" s="83">
         <f t="shared" si="84"/>
-        <v>7.857142857142857E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K188" s="83">
         <f t="shared" si="85"/>
-        <v>12.727272727272727</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L188" s="45">
         <f>K188/K$2</f>
-        <v>6.0072727272727269</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="189" spans="1:13">
@@ -11437,12 +11444,12 @@
         <v>110</v>
       </c>
       <c r="E189" s="130">
-        <v>11200</v>
+        <v>15000</v>
       </c>
       <c r="F189" s="129"/>
       <c r="G189" s="80">
         <f t="shared" si="86"/>
-        <v>280000</v>
+        <v>375000</v>
       </c>
       <c r="H189" s="82">
         <v>22000</v>
@@ -11453,15 +11460,15 @@
       </c>
       <c r="J189" s="83">
         <f t="shared" si="84"/>
-        <v>7.857142857142857E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K189" s="83">
         <f t="shared" si="85"/>
-        <v>12.727272727272727</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L189" s="45">
         <f>K189/K$2</f>
-        <v>6.0072727272727269</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="190" spans="1:13">
@@ -11476,12 +11483,12 @@
         <v>111</v>
       </c>
       <c r="E190" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F190" s="129"/>
       <c r="G190" s="80">
         <f t="shared" si="86"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H190" s="82">
         <v>33000</v>
@@ -11492,15 +11499,15 @@
       </c>
       <c r="J190" s="83">
         <f t="shared" si="84"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K190" s="83">
         <f t="shared" si="85"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L190" s="45">
         <f>K190/K$2</f>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="191" spans="1:13">
@@ -11515,12 +11522,12 @@
         <v>112</v>
       </c>
       <c r="E191" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F191" s="129"/>
       <c r="G191" s="80">
         <f t="shared" si="86"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H191" s="82">
         <v>33000</v>
@@ -11531,15 +11538,15 @@
       </c>
       <c r="J191" s="83">
         <f t="shared" si="84"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K191" s="83">
         <f t="shared" si="85"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L191" s="45">
         <f t="shared" ref="L191:L195" si="87">K191/K$2</f>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="192" spans="1:13">
@@ -11554,12 +11561,12 @@
         <v>113</v>
       </c>
       <c r="E192" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F192" s="129"/>
       <c r="G192" s="80">
         <f t="shared" si="86"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H192" s="82">
         <v>33000</v>
@@ -11570,15 +11577,15 @@
       </c>
       <c r="J192" s="83">
         <f t="shared" si="84"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K192" s="83">
         <f t="shared" si="85"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L192" s="45">
         <f t="shared" si="87"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -11593,12 +11600,12 @@
         <v>114</v>
       </c>
       <c r="E193" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F193" s="129"/>
       <c r="G193" s="80">
         <f t="shared" si="86"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H193" s="82">
         <v>33000</v>
@@ -11609,15 +11616,15 @@
       </c>
       <c r="J193" s="83">
         <f t="shared" si="84"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K193" s="83">
         <f t="shared" si="85"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L193" s="45">
         <f t="shared" si="87"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -11632,12 +11639,12 @@
         <v>359</v>
       </c>
       <c r="E194" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F194" s="129"/>
       <c r="G194" s="80">
         <f t="shared" si="86"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H194" s="82">
         <v>33000</v>
@@ -11648,15 +11655,15 @@
       </c>
       <c r="J194" s="83">
         <f t="shared" si="84"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K194" s="83">
         <f t="shared" si="85"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L194" s="45">
         <f t="shared" si="87"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -11671,12 +11678,12 @@
         <v>360</v>
       </c>
       <c r="E195" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F195" s="129"/>
       <c r="G195" s="80">
         <f t="shared" si="86"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H195" s="82">
         <v>33000</v>
@@ -11687,15 +11694,15 @@
       </c>
       <c r="J195" s="83">
         <f t="shared" si="84"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K195" s="83">
         <f t="shared" si="85"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L195" s="45">
         <f t="shared" si="87"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="196" spans="1:12">
@@ -12061,7 +12068,7 @@
     <row r="206" spans="1:12">
       <c r="G206" s="190">
         <f>SUM(G186:G195)</f>
-        <v>3140000</v>
+        <v>4163750</v>
       </c>
       <c r="H206" s="189">
         <f>SUM(H186:H195)</f>
@@ -12081,12 +12088,12 @@
         <v>93</v>
       </c>
       <c r="E207" s="130">
-        <v>2800</v>
+        <v>3750</v>
       </c>
       <c r="F207" s="129"/>
       <c r="G207" s="80">
         <f>E207*25</f>
-        <v>70000</v>
+        <v>93750</v>
       </c>
       <c r="H207" s="82">
         <v>5500</v>
@@ -12097,15 +12104,15 @@
       </c>
       <c r="J207" s="83">
         <f t="shared" ref="J207:J226" si="90">H207/G207</f>
-        <v>7.857142857142857E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K207" s="83">
         <f t="shared" ref="K207:K226" si="91">G207/H207</f>
-        <v>12.727272727272727</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L207" s="45">
         <f t="shared" ref="L207:L216" si="92">K207/K$2</f>
-        <v>6.0072727272727269</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="208" spans="1:12">
@@ -12120,12 +12127,12 @@
         <v>92</v>
       </c>
       <c r="E208" s="130">
-        <v>4000</v>
+        <v>5300</v>
       </c>
       <c r="F208" s="129"/>
       <c r="G208" s="80">
         <f t="shared" ref="G208:G226" si="93">E208*25</f>
-        <v>100000</v>
+        <v>132500</v>
       </c>
       <c r="H208" s="82">
         <v>7700</v>
@@ -12136,15 +12143,15 @@
       </c>
       <c r="J208" s="83">
         <f t="shared" si="90"/>
-        <v>7.6999999999999999E-2</v>
+        <v>5.811320754716981E-2</v>
       </c>
       <c r="K208" s="83">
         <f t="shared" si="91"/>
-        <v>12.987012987012987</v>
+        <v>17.207792207792206</v>
       </c>
       <c r="L208" s="45">
         <f t="shared" si="92"/>
-        <v>6.1298701298701292</v>
+        <v>8.1220779220779207</v>
       </c>
     </row>
     <row r="209" spans="1:12">
@@ -12159,12 +12166,12 @@
         <v>94</v>
       </c>
       <c r="E209" s="130">
-        <v>5600</v>
+        <v>7500</v>
       </c>
       <c r="F209" s="129"/>
       <c r="G209" s="80">
         <f t="shared" si="93"/>
-        <v>140000</v>
+        <v>187500</v>
       </c>
       <c r="H209" s="82">
         <v>11000</v>
@@ -12175,15 +12182,15 @@
       </c>
       <c r="J209" s="83">
         <f t="shared" si="90"/>
-        <v>7.857142857142857E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K209" s="83">
         <f t="shared" si="91"/>
-        <v>12.727272727272727</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L209" s="45">
         <f t="shared" si="92"/>
-        <v>6.0072727272727269</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="210" spans="1:12">
@@ -12198,12 +12205,12 @@
         <v>95</v>
       </c>
       <c r="E210" s="130">
-        <v>11200</v>
+        <v>15000</v>
       </c>
       <c r="F210" s="129"/>
       <c r="G210" s="80">
         <f t="shared" si="93"/>
-        <v>280000</v>
+        <v>375000</v>
       </c>
       <c r="H210" s="82">
         <v>22000</v>
@@ -12214,15 +12221,15 @@
       </c>
       <c r="J210" s="83">
         <f t="shared" si="90"/>
-        <v>7.857142857142857E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K210" s="83">
         <f t="shared" si="91"/>
-        <v>12.727272727272727</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L210" s="45">
         <f t="shared" si="92"/>
-        <v>6.0072727272727269</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="211" spans="1:12">
@@ -12237,12 +12244,12 @@
         <v>96</v>
       </c>
       <c r="E211" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F211" s="129"/>
       <c r="G211" s="80">
         <f t="shared" si="93"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H211" s="82">
         <v>33000</v>
@@ -12253,15 +12260,15 @@
       </c>
       <c r="J211" s="83">
         <f t="shared" si="90"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K211" s="83">
         <f t="shared" si="91"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L211" s="45">
         <f t="shared" si="92"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="212" spans="1:12">
@@ -12276,12 +12283,12 @@
         <v>97</v>
       </c>
       <c r="E212" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F212" s="129"/>
       <c r="G212" s="80">
         <f t="shared" si="93"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H212" s="82">
         <v>33000</v>
@@ -12292,15 +12299,15 @@
       </c>
       <c r="J212" s="83">
         <f t="shared" si="90"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K212" s="83">
         <f t="shared" si="91"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L212" s="45">
         <f t="shared" si="92"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="213" spans="1:12">
@@ -12315,12 +12322,12 @@
         <v>98</v>
       </c>
       <c r="E213" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F213" s="129"/>
       <c r="G213" s="80">
         <f t="shared" si="93"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H213" s="82">
         <v>33000</v>
@@ -12331,15 +12338,15 @@
       </c>
       <c r="J213" s="83">
         <f t="shared" si="90"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K213" s="83">
         <f t="shared" si="91"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L213" s="45">
         <f t="shared" si="92"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -12354,12 +12361,12 @@
         <v>387</v>
       </c>
       <c r="E214" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F214" s="129"/>
       <c r="G214" s="80">
         <f t="shared" si="93"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H214" s="82">
         <v>33000</v>
@@ -12370,15 +12377,15 @@
       </c>
       <c r="J214" s="83">
         <f t="shared" si="90"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K214" s="83">
         <f t="shared" si="91"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L214" s="45">
         <f t="shared" si="92"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="215" spans="1:12">
@@ -12393,12 +12400,12 @@
         <v>383</v>
       </c>
       <c r="E215" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F215" s="129"/>
       <c r="G215" s="80">
         <f t="shared" si="93"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H215" s="82">
         <v>33000</v>
@@ -12409,15 +12416,15 @@
       </c>
       <c r="J215" s="83">
         <f t="shared" si="90"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K215" s="83">
         <f t="shared" si="91"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L215" s="45">
         <f t="shared" si="92"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="216" spans="1:12">
@@ -12432,12 +12439,12 @@
         <v>385</v>
       </c>
       <c r="E216" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F216" s="129"/>
       <c r="G216" s="80">
         <f t="shared" si="93"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H216" s="82">
         <v>33000</v>
@@ -12448,15 +12455,15 @@
       </c>
       <c r="J216" s="83">
         <f t="shared" si="90"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K216" s="83">
         <f t="shared" si="91"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L216" s="45">
         <f t="shared" si="92"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="217" spans="1:12">
@@ -12822,7 +12829,7 @@
     <row r="227" spans="1:12">
       <c r="G227" s="18">
         <f>SUM(G207:G226)</f>
-        <v>7390000</v>
+        <v>8413750</v>
       </c>
       <c r="H227" s="13">
         <f>SUM(H207:H226)</f>
@@ -12844,12 +12851,12 @@
         <v>428</v>
       </c>
       <c r="E228" s="130">
-        <v>2800</v>
+        <v>3750</v>
       </c>
       <c r="F228" s="129"/>
       <c r="G228" s="80">
         <f>E228*25</f>
-        <v>70000</v>
+        <v>93750</v>
       </c>
       <c r="H228" s="82">
         <v>5500</v>
@@ -12860,15 +12867,15 @@
       </c>
       <c r="J228" s="83">
         <f t="shared" ref="J228:J242" si="96">H228/G228</f>
-        <v>7.857142857142857E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K228" s="83">
         <f t="shared" ref="K228:K242" si="97">G228/H228</f>
-        <v>12.727272727272727</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L228" s="45">
         <f t="shared" ref="L228:L242" si="98">K228/K$2</f>
-        <v>6.0072727272727269</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="229" spans="1:12">
@@ -12886,12 +12893,12 @@
         <v>428</v>
       </c>
       <c r="E229" s="130">
-        <v>4000</v>
+        <v>5300</v>
       </c>
       <c r="F229" s="129"/>
       <c r="G229" s="80">
         <f t="shared" ref="G229:G242" si="99">E229*25</f>
-        <v>100000</v>
+        <v>132500</v>
       </c>
       <c r="H229" s="82">
         <v>7700</v>
@@ -12902,15 +12909,15 @@
       </c>
       <c r="J229" s="83">
         <f t="shared" si="96"/>
-        <v>7.6999999999999999E-2</v>
+        <v>5.811320754716981E-2</v>
       </c>
       <c r="K229" s="83">
         <f t="shared" si="97"/>
-        <v>12.987012987012987</v>
+        <v>17.207792207792206</v>
       </c>
       <c r="L229" s="45">
         <f t="shared" si="98"/>
-        <v>6.1298701298701292</v>
+        <v>8.1220779220779207</v>
       </c>
     </row>
     <row r="230" spans="1:12">
@@ -12928,12 +12935,12 @@
         <v>427</v>
       </c>
       <c r="E230" s="130">
-        <v>5600</v>
+        <v>7500</v>
       </c>
       <c r="F230" s="129"/>
       <c r="G230" s="80">
         <f t="shared" si="99"/>
-        <v>140000</v>
+        <v>187500</v>
       </c>
       <c r="H230" s="82">
         <v>11000</v>
@@ -12944,15 +12951,15 @@
       </c>
       <c r="J230" s="83">
         <f t="shared" si="96"/>
-        <v>7.857142857142857E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K230" s="83">
         <f t="shared" si="97"/>
-        <v>12.727272727272727</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L230" s="45">
         <f t="shared" si="98"/>
-        <v>6.0072727272727269</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="231" spans="1:12">
@@ -12970,12 +12977,12 @@
         <v>427</v>
       </c>
       <c r="E231" s="130">
-        <v>11200</v>
+        <v>15000</v>
       </c>
       <c r="F231" s="129"/>
       <c r="G231" s="80">
         <f t="shared" si="99"/>
-        <v>280000</v>
+        <v>375000</v>
       </c>
       <c r="H231" s="82">
         <v>22000</v>
@@ -12986,15 +12993,15 @@
       </c>
       <c r="J231" s="83">
         <f t="shared" si="96"/>
-        <v>7.857142857142857E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K231" s="83">
         <f t="shared" si="97"/>
-        <v>12.727272727272727</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L231" s="45">
         <f t="shared" si="98"/>
-        <v>6.0072727272727269</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="232" spans="1:12">
@@ -13012,12 +13019,12 @@
         <v>427</v>
       </c>
       <c r="E232" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F232" s="129"/>
       <c r="G232" s="80">
         <f t="shared" si="99"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H232" s="82">
         <v>33000</v>
@@ -13028,15 +13035,15 @@
       </c>
       <c r="J232" s="83">
         <f t="shared" si="96"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K232" s="83">
         <f t="shared" si="97"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L232" s="45">
         <f t="shared" si="98"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="233" spans="1:12">
@@ -13054,12 +13061,12 @@
         <v>427</v>
       </c>
       <c r="E233" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F233" s="129"/>
       <c r="G233" s="80">
         <f t="shared" si="99"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H233" s="82">
         <v>33000</v>
@@ -13070,15 +13077,15 @@
       </c>
       <c r="J233" s="83">
         <f t="shared" si="96"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K233" s="83">
         <f t="shared" si="97"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L233" s="45">
         <f t="shared" si="98"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="234" spans="1:12">
@@ -13096,12 +13103,12 @@
         <v>427</v>
       </c>
       <c r="E234" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F234" s="129"/>
       <c r="G234" s="80">
         <f t="shared" si="99"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H234" s="82">
         <v>33000</v>
@@ -13112,15 +13119,15 @@
       </c>
       <c r="J234" s="83">
         <f t="shared" si="96"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K234" s="83">
         <f t="shared" si="97"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L234" s="45">
         <f t="shared" si="98"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="235" spans="1:12">
@@ -13138,12 +13145,12 @@
         <v>427</v>
       </c>
       <c r="E235" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F235" s="129"/>
       <c r="G235" s="80">
         <f t="shared" si="99"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H235" s="82">
         <v>33000</v>
@@ -13154,15 +13161,15 @@
       </c>
       <c r="J235" s="83">
         <f t="shared" si="96"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K235" s="83">
         <f t="shared" si="97"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L235" s="45">
         <f t="shared" si="98"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="236" spans="1:12">
@@ -13180,12 +13187,12 @@
         <v>427</v>
       </c>
       <c r="E236" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F236" s="129"/>
       <c r="G236" s="80">
         <f t="shared" si="99"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H236" s="82">
         <v>33000</v>
@@ -13196,15 +13203,15 @@
       </c>
       <c r="J236" s="83">
         <f t="shared" si="96"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K236" s="83">
         <f t="shared" si="97"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L236" s="45">
         <f t="shared" si="98"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="237" spans="1:12">
@@ -13222,12 +13229,12 @@
         <v>427</v>
       </c>
       <c r="E237" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F237" s="129"/>
       <c r="G237" s="80">
         <f t="shared" si="99"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H237" s="82">
         <v>33000</v>
@@ -13238,15 +13245,15 @@
       </c>
       <c r="J237" s="83">
         <f t="shared" si="96"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K237" s="83">
         <f t="shared" si="97"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L237" s="45">
         <f t="shared" si="98"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="238" spans="1:12">
@@ -13264,12 +13271,12 @@
         <v>427</v>
       </c>
       <c r="E238" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F238" s="129"/>
       <c r="G238" s="80">
         <f t="shared" si="99"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H238" s="82">
         <v>33000</v>
@@ -13280,15 +13287,15 @@
       </c>
       <c r="J238" s="83">
         <f t="shared" si="96"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K238" s="83">
         <f t="shared" si="97"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L238" s="45">
         <f t="shared" si="98"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="239" spans="1:12">
@@ -13306,12 +13313,12 @@
         <v>427</v>
       </c>
       <c r="E239" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F239" s="129"/>
       <c r="G239" s="80">
         <f t="shared" si="99"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H239" s="82">
         <v>33000</v>
@@ -13322,15 +13329,15 @@
       </c>
       <c r="J239" s="83">
         <f t="shared" si="96"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K239" s="83">
         <f t="shared" si="97"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L239" s="45">
         <f t="shared" si="98"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="240" spans="1:12">
@@ -13348,12 +13355,12 @@
         <v>427</v>
       </c>
       <c r="E240" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F240" s="129"/>
       <c r="G240" s="80">
         <f t="shared" si="99"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H240" s="82">
         <v>33000</v>
@@ -13364,15 +13371,15 @@
       </c>
       <c r="J240" s="83">
         <f t="shared" si="96"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K240" s="83">
         <f t="shared" si="97"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L240" s="45">
         <f t="shared" si="98"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="241" spans="1:12">
@@ -13390,12 +13397,12 @@
         <v>427</v>
       </c>
       <c r="E241" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F241" s="129"/>
       <c r="G241" s="80">
         <f t="shared" si="99"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H241" s="82">
         <v>33000</v>
@@ -13406,15 +13413,15 @@
       </c>
       <c r="J241" s="83">
         <f t="shared" si="96"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K241" s="83">
         <f t="shared" si="97"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L241" s="45">
         <f t="shared" si="98"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="242" spans="1:12">
@@ -13432,12 +13439,12 @@
         <v>427</v>
       </c>
       <c r="E242" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F242" s="129"/>
       <c r="G242" s="80">
         <f t="shared" si="99"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H242" s="82">
         <v>33000</v>
@@ -13448,15 +13455,15 @@
       </c>
       <c r="J242" s="83">
         <f t="shared" si="96"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K242" s="83">
         <f t="shared" si="97"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L242" s="45">
         <f t="shared" si="98"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="243" spans="1:12">
@@ -13482,12 +13489,12 @@
         <v>434</v>
       </c>
       <c r="E244" s="130">
-        <v>2800</v>
+        <v>3750</v>
       </c>
       <c r="F244" s="129"/>
       <c r="G244" s="80">
         <f>E244*25</f>
-        <v>70000</v>
+        <v>93750</v>
       </c>
       <c r="H244" s="82">
         <v>5500</v>
@@ -13498,15 +13505,15 @@
       </c>
       <c r="J244" s="83">
         <f t="shared" ref="J244:J253" si="101">H244/G244</f>
-        <v>7.857142857142857E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K244" s="83">
         <f t="shared" ref="K244:K253" si="102">G244/H244</f>
-        <v>12.727272727272727</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L244" s="45">
         <f t="shared" ref="L244:L253" si="103">K244/K$2</f>
-        <v>6.0072727272727269</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="245" spans="1:12">
@@ -13523,12 +13530,12 @@
         <v>434</v>
       </c>
       <c r="E245" s="130">
-        <v>4000</v>
+        <v>5300</v>
       </c>
       <c r="F245" s="129"/>
       <c r="G245" s="80">
         <f t="shared" ref="G245:G253" si="104">E245*25</f>
-        <v>100000</v>
+        <v>132500</v>
       </c>
       <c r="H245" s="82">
         <v>7700</v>
@@ -13539,15 +13546,15 @@
       </c>
       <c r="J245" s="83">
         <f t="shared" si="101"/>
-        <v>7.6999999999999999E-2</v>
+        <v>5.811320754716981E-2</v>
       </c>
       <c r="K245" s="83">
         <f t="shared" si="102"/>
-        <v>12.987012987012987</v>
+        <v>17.207792207792206</v>
       </c>
       <c r="L245" s="45">
         <f t="shared" si="103"/>
-        <v>6.1298701298701292</v>
+        <v>8.1220779220779207</v>
       </c>
     </row>
     <row r="246" spans="1:12">
@@ -13564,12 +13571,12 @@
         <v>434</v>
       </c>
       <c r="E246" s="130">
-        <v>5600</v>
+        <v>7500</v>
       </c>
       <c r="F246" s="129"/>
       <c r="G246" s="80">
         <f t="shared" si="104"/>
-        <v>140000</v>
+        <v>187500</v>
       </c>
       <c r="H246" s="82">
         <v>11000</v>
@@ -13580,15 +13587,15 @@
       </c>
       <c r="J246" s="83">
         <f t="shared" si="101"/>
-        <v>7.857142857142857E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K246" s="83">
         <f t="shared" si="102"/>
-        <v>12.727272727272727</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L246" s="45">
         <f t="shared" si="103"/>
-        <v>6.0072727272727269</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="247" spans="1:12">
@@ -13605,12 +13612,12 @@
         <v>434</v>
       </c>
       <c r="E247" s="130">
-        <v>11200</v>
+        <v>15000</v>
       </c>
       <c r="F247" s="129"/>
       <c r="G247" s="80">
         <f t="shared" si="104"/>
-        <v>280000</v>
+        <v>375000</v>
       </c>
       <c r="H247" s="82">
         <v>22000</v>
@@ -13621,15 +13628,15 @@
       </c>
       <c r="J247" s="83">
         <f t="shared" si="101"/>
-        <v>7.857142857142857E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K247" s="83">
         <f t="shared" si="102"/>
-        <v>12.727272727272727</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L247" s="45">
         <f t="shared" si="103"/>
-        <v>6.0072727272727269</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="248" spans="1:12">
@@ -13646,12 +13653,12 @@
         <v>434</v>
       </c>
       <c r="E248" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F248" s="129"/>
       <c r="G248" s="80">
         <f t="shared" si="104"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H248" s="82">
         <v>33000</v>
@@ -13662,15 +13669,15 @@
       </c>
       <c r="J248" s="83">
         <f t="shared" si="101"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K248" s="83">
         <f t="shared" si="102"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L248" s="45">
         <f t="shared" si="103"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="249" spans="1:12">
@@ -13687,12 +13694,12 @@
         <v>434</v>
       </c>
       <c r="E249" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F249" s="129"/>
       <c r="G249" s="80">
         <f t="shared" si="104"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H249" s="82">
         <v>33000</v>
@@ -13703,15 +13710,15 @@
       </c>
       <c r="J249" s="83">
         <f t="shared" si="101"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K249" s="83">
         <f t="shared" si="102"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L249" s="45">
         <f t="shared" si="103"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="250" spans="1:12">
@@ -13728,12 +13735,12 @@
         <v>434</v>
       </c>
       <c r="E250" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F250" s="129"/>
       <c r="G250" s="80">
         <f t="shared" si="104"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H250" s="82">
         <v>33000</v>
@@ -13744,15 +13751,15 @@
       </c>
       <c r="J250" s="83">
         <f t="shared" si="101"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K250" s="83">
         <f t="shared" si="102"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L250" s="45">
         <f t="shared" si="103"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="251" spans="1:12">
@@ -13769,12 +13776,12 @@
         <v>434</v>
       </c>
       <c r="E251" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F251" s="129"/>
       <c r="G251" s="80">
         <f t="shared" si="104"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H251" s="82">
         <v>33000</v>
@@ -13785,15 +13792,15 @@
       </c>
       <c r="J251" s="83">
         <f t="shared" si="101"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K251" s="83">
         <f t="shared" si="102"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L251" s="45">
         <f t="shared" si="103"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="252" spans="1:12">
@@ -13810,12 +13817,12 @@
         <v>434</v>
       </c>
       <c r="E252" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F252" s="129"/>
       <c r="G252" s="80">
         <f t="shared" si="104"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H252" s="82">
         <v>33000</v>
@@ -13826,15 +13833,15 @@
       </c>
       <c r="J252" s="83">
         <f t="shared" si="101"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K252" s="83">
         <f t="shared" si="102"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L252" s="45">
         <f t="shared" si="103"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="253" spans="1:12">
@@ -13851,12 +13858,12 @@
         <v>434</v>
       </c>
       <c r="E253" s="130">
-        <v>17000</v>
+        <v>22500</v>
       </c>
       <c r="F253" s="129"/>
       <c r="G253" s="80">
         <f t="shared" si="104"/>
-        <v>425000</v>
+        <v>562500</v>
       </c>
       <c r="H253" s="82">
         <v>33000</v>
@@ -13867,15 +13874,15 @@
       </c>
       <c r="J253" s="83">
         <f t="shared" si="101"/>
-        <v>7.7647058823529416E-2</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="K253" s="83">
         <f t="shared" si="102"/>
-        <v>12.878787878787879</v>
+        <v>17.045454545454547</v>
       </c>
       <c r="L253" s="45">
         <f t="shared" si="103"/>
-        <v>6.0787878787878782</v>
+        <v>8.045454545454545</v>
       </c>
     </row>
     <row r="254" spans="1:12">
@@ -14130,7 +14137,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="273" spans="1:13">
+    <row r="273" spans="1:14">
       <c r="A273" s="1" t="s">
         <v>74</v>
       </c>
@@ -14144,12 +14151,12 @@
         <v>48</v>
       </c>
       <c r="E273" s="129">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="F273" s="129"/>
       <c r="G273" s="80">
         <f t="shared" si="106"/>
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="H273" s="82">
         <v>11000</v>
@@ -14160,26 +14167,29 @@
       </c>
       <c r="J273" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K273" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L273" s="45">
         <f t="shared" si="110"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M273" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="274" spans="1:13">
+      <c r="N273" s="193">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14">
       <c r="A274" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B274" s="78" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C274" s="81" t="s">
         <v>152</v>
@@ -14188,12 +14198,12 @@
         <v>48</v>
       </c>
       <c r="E274" s="129">
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="F274" s="129"/>
       <c r="G274" s="80">
         <f t="shared" si="106"/>
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="H274" s="82">
         <v>33000</v>
@@ -14204,26 +14214,29 @@
       </c>
       <c r="J274" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K274" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L274" s="45">
         <f t="shared" si="110"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M274" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="275" spans="1:13">
+      <c r="N274" s="193">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14">
       <c r="A275" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B275" s="78" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C275" s="81" t="s">
         <v>153</v>
@@ -14232,37 +14245,40 @@
         <v>48</v>
       </c>
       <c r="E275" s="129">
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="F275" s="129"/>
       <c r="G275" s="80">
         <f t="shared" si="106"/>
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="H275" s="82">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I275" s="103">
         <f t="shared" si="107"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J275" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K275" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L275" s="45">
         <f t="shared" si="110"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M275" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="276" spans="1:13">
+      <c r="N275" s="193">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14">
       <c r="A276" s="1" t="s">
         <v>74</v>
       </c>
@@ -14276,12 +14292,12 @@
         <v>48</v>
       </c>
       <c r="E276" s="129">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="F276" s="129"/>
       <c r="G276" s="80">
         <f t="shared" si="106"/>
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="H276" s="82">
         <v>5500</v>
@@ -14292,21 +14308,24 @@
       </c>
       <c r="J276" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K276" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L276" s="45">
         <f t="shared" ref="L276:L279" si="111">K276/K$2</f>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M276" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="277" spans="1:13">
+      <c r="N276" s="193">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14">
       <c r="A277" s="1" t="s">
         <v>74</v>
       </c>
@@ -14320,12 +14339,12 @@
         <v>48</v>
       </c>
       <c r="E277" s="129">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="F277" s="129"/>
       <c r="G277" s="80">
         <f t="shared" si="106"/>
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="H277" s="82">
         <v>11000</v>
@@ -14336,21 +14355,24 @@
       </c>
       <c r="J277" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K277" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L277" s="45">
         <f t="shared" si="111"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M277" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="278" spans="1:13">
+      <c r="N277" s="193">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="278" spans="1:14">
       <c r="A278" s="1" t="s">
         <v>74</v>
       </c>
@@ -14364,12 +14386,12 @@
         <v>48</v>
       </c>
       <c r="E278" s="129">
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="F278" s="129"/>
       <c r="G278" s="80">
         <f t="shared" si="106"/>
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="H278" s="82">
         <v>33000</v>
@@ -14380,21 +14402,24 @@
       </c>
       <c r="J278" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K278" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L278" s="45">
         <f t="shared" si="111"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M278" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="279" spans="1:13">
+      <c r="N278" s="193">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14">
       <c r="A279" s="1" t="s">
         <v>74</v>
       </c>
@@ -14408,37 +14433,40 @@
         <v>48</v>
       </c>
       <c r="E279" s="129">
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="F279" s="129"/>
       <c r="G279" s="80">
         <f t="shared" si="106"/>
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="H279" s="82">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I279" s="103">
         <f t="shared" si="107"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J279" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K279" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L279" s="45">
         <f t="shared" si="111"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M279" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="280" spans="1:13">
+      <c r="N279" s="193">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14">
       <c r="A280" s="1" t="s">
         <v>74</v>
       </c>
@@ -14452,12 +14480,12 @@
         <v>48</v>
       </c>
       <c r="E280" s="129">
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="F280" s="129"/>
       <c r="G280" s="80">
         <f t="shared" si="106"/>
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="H280" s="82">
         <v>33000</v>
@@ -14468,21 +14496,24 @@
       </c>
       <c r="J280" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K280" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L280" s="45">
         <f>K280/K$2</f>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M280" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="281" spans="1:13">
+      <c r="N280" s="193">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14">
       <c r="A281" s="1" t="s">
         <v>74</v>
       </c>
@@ -14496,12 +14527,12 @@
         <v>48</v>
       </c>
       <c r="E281" s="129">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="F281" s="129"/>
       <c r="G281" s="80">
         <f t="shared" si="106"/>
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="H281" s="82">
         <v>11000</v>
@@ -14512,21 +14543,24 @@
       </c>
       <c r="J281" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K281" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L281" s="45">
         <f t="shared" ref="L281:L283" si="112">K281/K$2</f>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M281" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="282" spans="1:13">
+      <c r="N281" s="193">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14">
       <c r="A282" s="1" t="s">
         <v>74</v>
       </c>
@@ -14540,12 +14574,12 @@
         <v>48</v>
       </c>
       <c r="E282" s="129">
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="F282" s="129"/>
       <c r="G282" s="80">
         <f t="shared" si="106"/>
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="H282" s="82">
         <v>33000</v>
@@ -14556,21 +14590,24 @@
       </c>
       <c r="J282" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K282" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L282" s="45">
         <f t="shared" si="112"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M282" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="283" spans="1:13">
+      <c r="N282" s="193">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14">
       <c r="A283" s="1" t="s">
         <v>74</v>
       </c>
@@ -14584,37 +14621,40 @@
         <v>48</v>
       </c>
       <c r="E283" s="129">
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="F283" s="129"/>
       <c r="G283" s="80">
         <f t="shared" si="106"/>
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="H283" s="82">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I283" s="103">
         <f t="shared" si="107"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J283" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K283" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L283" s="45">
         <f t="shared" si="112"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M283" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="284" spans="1:13">
+      <c r="N283" s="193">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14">
       <c r="A284" s="1" t="s">
         <v>74</v>
       </c>
@@ -14628,12 +14668,12 @@
         <v>48</v>
       </c>
       <c r="E284" s="129">
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="F284" s="129"/>
       <c r="G284" s="80">
         <f t="shared" si="106"/>
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="H284" s="82">
         <v>33000</v>
@@ -14644,21 +14684,24 @@
       </c>
       <c r="J284" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K284" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L284" s="45">
         <f>K284/K$2</f>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M284" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="285" spans="1:13">
+      <c r="N284" s="193">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14">
       <c r="A285" s="1" t="s">
         <v>74</v>
       </c>
@@ -14672,12 +14715,12 @@
         <v>48</v>
       </c>
       <c r="E285" s="129">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="F285" s="129"/>
       <c r="G285" s="80">
         <f t="shared" si="106"/>
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="H285" s="82">
         <v>11000</v>
@@ -14688,21 +14731,24 @@
       </c>
       <c r="J285" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K285" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L285" s="45">
         <f t="shared" ref="L285:L287" si="113">K285/K$2</f>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M285" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="286" spans="1:13">
+      <c r="N285" s="193">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14">
       <c r="A286" s="1" t="s">
         <v>74</v>
       </c>
@@ -14716,12 +14762,12 @@
         <v>48</v>
       </c>
       <c r="E286" s="129">
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="F286" s="129"/>
       <c r="G286" s="80">
         <f t="shared" si="106"/>
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="H286" s="82">
         <v>33000</v>
@@ -14732,21 +14778,24 @@
       </c>
       <c r="J286" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K286" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L286" s="45">
         <f t="shared" si="113"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M286" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="287" spans="1:13">
+      <c r="N286" s="193">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14">
       <c r="A287" s="1" t="s">
         <v>74</v>
       </c>
@@ -14760,37 +14809,40 @@
         <v>48</v>
       </c>
       <c r="E287" s="129">
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="F287" s="129"/>
       <c r="G287" s="80">
         <f t="shared" si="106"/>
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="H287" s="82">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I287" s="103">
         <f t="shared" si="107"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J287" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K287" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L287" s="45">
         <f t="shared" si="113"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M287" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="288" spans="1:13">
+      <c r="N287" s="193">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14">
       <c r="A288" s="1" t="s">
         <v>74</v>
       </c>
@@ -14804,12 +14856,12 @@
         <v>48</v>
       </c>
       <c r="E288" s="129">
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="F288" s="129"/>
       <c r="G288" s="80">
         <f t="shared" si="106"/>
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="H288" s="82">
         <v>33000</v>
@@ -14820,21 +14872,24 @@
       </c>
       <c r="J288" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K288" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L288" s="45">
         <f>K288/K$2</f>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M288" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="289" spans="1:13">
+      <c r="N288" s="193">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14">
       <c r="A289" s="1" t="s">
         <v>74</v>
       </c>
@@ -14848,12 +14903,12 @@
         <v>48</v>
       </c>
       <c r="E289" s="129">
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="F289" s="129"/>
       <c r="G289" s="80">
         <f t="shared" si="106"/>
-        <v>160000</v>
+        <v>200000</v>
       </c>
       <c r="H289" s="82">
         <v>11000</v>
@@ -14864,21 +14919,24 @@
       </c>
       <c r="J289" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K289" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L289" s="45">
         <f t="shared" ref="L289:L291" si="114">K289/K$2</f>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M289" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="290" spans="1:13">
+      <c r="N289" s="193">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14">
       <c r="A290" s="1" t="s">
         <v>74</v>
       </c>
@@ -14892,12 +14950,12 @@
         <v>48</v>
       </c>
       <c r="E290" s="129">
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="F290" s="129"/>
       <c r="G290" s="80">
         <f t="shared" si="106"/>
-        <v>480000</v>
+        <v>600000</v>
       </c>
       <c r="H290" s="82">
         <v>33000</v>
@@ -14908,21 +14966,24 @@
       </c>
       <c r="J290" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K290" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L290" s="45">
         <f t="shared" si="114"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M290" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="291" spans="1:13">
+      <c r="N290" s="193">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14">
       <c r="A291" s="1" t="s">
         <v>74</v>
       </c>
@@ -14936,44 +14997,47 @@
         <v>48</v>
       </c>
       <c r="E291" s="129">
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="F291" s="129"/>
       <c r="G291" s="80">
         <f t="shared" si="106"/>
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="H291" s="82">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I291" s="103">
         <f t="shared" si="107"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J291" s="83">
         <f t="shared" si="108"/>
-        <v>6.8750000000000006E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K291" s="83">
         <f t="shared" si="109"/>
-        <v>14.545454545454545</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L291" s="45">
         <f t="shared" si="114"/>
-        <v>6.8654545454545453</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M291" s="1" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="293" spans="1:13">
+      <c r="N291" s="193">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14">
       <c r="B293" s="22" t="s">
         <v>240</v>
       </c>
       <c r="D293" s="25"/>
       <c r="E293" s="138"/>
     </row>
-    <row r="294" spans="1:13">
+    <row r="294" spans="1:14">
       <c r="A294" s="1" t="s">
         <v>74</v>
       </c>
@@ -15019,7 +15083,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="295" spans="1:13">
+    <row r="295" spans="1:14">
       <c r="A295" s="1" t="s">
         <v>74</v>
       </c>
@@ -15033,14 +15097,14 @@
         <v>509</v>
       </c>
       <c r="E295" s="147">
-        <v>14000</v>
+        <v>10000</v>
       </c>
       <c r="F295" s="128">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="G295" s="48">
         <f t="shared" ref="G295:G301" si="119">F295*100+E295</f>
-        <v>72000</v>
+        <v>60000</v>
       </c>
       <c r="H295" s="49">
         <v>3300</v>
@@ -15051,21 +15115,21 @@
       </c>
       <c r="J295" s="50">
         <f t="shared" si="116"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K295" s="50">
         <f t="shared" si="117"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L295" s="45">
         <f t="shared" si="118"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M295" s="1" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="296" spans="1:13">
+    <row r="296" spans="1:14">
       <c r="A296" s="1" t="s">
         <v>74</v>
       </c>
@@ -15079,14 +15143,14 @@
         <v>509</v>
       </c>
       <c r="E296" s="147">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="F296" s="128">
-        <v>960</v>
+        <v>800</v>
       </c>
       <c r="G296" s="48">
         <f t="shared" si="119"/>
-        <v>120000</v>
+        <v>100000</v>
       </c>
       <c r="H296" s="49">
         <v>5500</v>
@@ -15097,21 +15161,21 @@
       </c>
       <c r="J296" s="50">
         <f t="shared" si="116"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K296" s="50">
         <f t="shared" si="117"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L296" s="45">
         <f t="shared" si="118"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M296" s="1" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="297" spans="1:13">
+    <row r="297" spans="1:14">
       <c r="A297" s="1" t="s">
         <v>74</v>
       </c>
@@ -15125,14 +15189,14 @@
         <v>509</v>
       </c>
       <c r="E297" s="147">
-        <v>41000</v>
+        <v>30000</v>
       </c>
       <c r="F297" s="128">
-        <v>2000</v>
+        <v>1700</v>
       </c>
       <c r="G297" s="48">
         <f t="shared" si="119"/>
-        <v>241000</v>
+        <v>200000</v>
       </c>
       <c r="H297" s="49">
         <v>11000</v>
@@ -15143,21 +15207,21 @@
       </c>
       <c r="J297" s="50">
         <f t="shared" si="116"/>
-        <v>4.5643153526970952E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K297" s="50">
         <f t="shared" si="117"/>
-        <v>21.90909090909091</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L297" s="45">
         <f t="shared" si="118"/>
-        <v>10.341090909090909</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M297" s="1" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="298" spans="1:13">
+    <row r="298" spans="1:14">
       <c r="A298" s="1" t="s">
         <v>74</v>
       </c>
@@ -15171,14 +15235,14 @@
         <v>509</v>
       </c>
       <c r="E298" s="147">
-        <v>140000</v>
+        <v>90000</v>
       </c>
       <c r="F298" s="128">
-        <v>5800</v>
+        <v>5100</v>
       </c>
       <c r="G298" s="48">
         <f t="shared" si="119"/>
-        <v>720000</v>
+        <v>600000</v>
       </c>
       <c r="H298" s="49">
         <v>33000</v>
@@ -15189,21 +15253,21 @@
       </c>
       <c r="J298" s="50">
         <f t="shared" si="116"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K298" s="50">
         <f t="shared" si="117"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L298" s="45">
         <f t="shared" si="118"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M298" s="1" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="299" spans="1:13">
+    <row r="299" spans="1:14">
       <c r="A299" s="1" t="s">
         <v>74</v>
       </c>
@@ -15217,39 +15281,39 @@
         <v>509</v>
       </c>
       <c r="E299" s="147">
-        <v>240000</v>
+        <v>90000</v>
       </c>
       <c r="F299" s="128">
-        <v>9600</v>
+        <v>5100</v>
       </c>
       <c r="G299" s="48">
         <f t="shared" si="119"/>
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="H299" s="49">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I299" s="100">
         <f t="shared" si="115"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J299" s="50">
         <f t="shared" si="116"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K299" s="50">
         <f t="shared" si="117"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L299" s="45">
         <f t="shared" si="118"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M299" s="1" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="300" spans="1:13">
+    <row r="300" spans="1:14">
       <c r="A300" s="1" t="s">
         <v>74</v>
       </c>
@@ -15263,39 +15327,39 @@
         <v>509</v>
       </c>
       <c r="E300" s="147">
-        <v>240000</v>
+        <v>90000</v>
       </c>
       <c r="F300" s="128">
-        <v>9600</v>
+        <v>5100</v>
       </c>
       <c r="G300" s="48">
         <f t="shared" si="119"/>
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="H300" s="49">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I300" s="100">
         <f t="shared" si="115"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J300" s="50">
         <f t="shared" si="116"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K300" s="50">
         <f t="shared" si="117"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L300" s="45">
         <f t="shared" ref="L300:L301" si="120">K300/K$2</f>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M300" s="1" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="301" spans="1:13">
+    <row r="301" spans="1:14">
       <c r="A301" s="1" t="s">
         <v>74</v>
       </c>
@@ -15341,27 +15405,27 @@
         <v>600</v>
       </c>
     </row>
-    <row r="302" spans="1:13">
+    <row r="302" spans="1:14">
       <c r="D302" s="26"/>
       <c r="E302" s="139"/>
       <c r="F302" s="140">
         <f>SUM(F295:F300)</f>
-        <v>28540</v>
+        <v>18300</v>
       </c>
       <c r="G302" s="53">
         <f>SUM(G295:G300)</f>
-        <v>3553000</v>
+        <v>2160000</v>
       </c>
       <c r="H302" s="52">
         <f>SUM(H295:H300)</f>
-        <v>162800</v>
+        <v>118800</v>
       </c>
       <c r="I302" s="52"/>
       <c r="J302" s="25"/>
       <c r="K302" s="25"/>
       <c r="L302" s="89"/>
     </row>
-    <row r="303" spans="1:13">
+    <row r="303" spans="1:14">
       <c r="A303" s="1" t="s">
         <v>74</v>
       </c>
@@ -15407,7 +15471,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="304" spans="1:13">
+    <row r="304" spans="1:14">
       <c r="A304" s="1" t="s">
         <v>74</v>
       </c>
@@ -15421,14 +15485,14 @@
         <v>513</v>
       </c>
       <c r="E304" s="147">
-        <v>14000</v>
+        <v>10000</v>
       </c>
       <c r="F304" s="128">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="G304" s="48">
         <f t="shared" ref="G304:G310" si="124">F304*100+E304</f>
-        <v>72000</v>
+        <v>60000</v>
       </c>
       <c r="H304" s="49">
         <v>3300</v>
@@ -15439,15 +15503,15 @@
       </c>
       <c r="J304" s="50">
         <f t="shared" si="121"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K304" s="50">
         <f t="shared" si="122"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L304" s="45">
         <f t="shared" si="123"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M304" s="1" t="s">
         <v>600</v>
@@ -15467,14 +15531,14 @@
         <v>513</v>
       </c>
       <c r="E305" s="147">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="F305" s="128">
-        <v>960</v>
+        <v>800</v>
       </c>
       <c r="G305" s="48">
         <f t="shared" si="124"/>
-        <v>120000</v>
+        <v>100000</v>
       </c>
       <c r="H305" s="49">
         <v>5500</v>
@@ -15485,15 +15549,15 @@
       </c>
       <c r="J305" s="50">
         <f t="shared" si="121"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K305" s="50">
         <f t="shared" si="122"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L305" s="45">
         <f t="shared" si="123"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M305" s="1" t="s">
         <v>600</v>
@@ -15513,14 +15577,14 @@
         <v>513</v>
       </c>
       <c r="E306" s="147">
-        <v>41000</v>
+        <v>30000</v>
       </c>
       <c r="F306" s="128">
-        <v>2000</v>
+        <v>1700</v>
       </c>
       <c r="G306" s="48">
         <f t="shared" si="124"/>
-        <v>241000</v>
+        <v>200000</v>
       </c>
       <c r="H306" s="49">
         <v>11000</v>
@@ -15531,15 +15595,15 @@
       </c>
       <c r="J306" s="50">
         <f t="shared" si="121"/>
-        <v>4.5643153526970952E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K306" s="50">
         <f t="shared" si="122"/>
-        <v>21.90909090909091</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L306" s="45">
         <f t="shared" si="123"/>
-        <v>10.341090909090909</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M306" s="1" t="s">
         <v>600</v>
@@ -15559,14 +15623,14 @@
         <v>513</v>
       </c>
       <c r="E307" s="147">
-        <v>140000</v>
+        <v>90000</v>
       </c>
       <c r="F307" s="128">
-        <v>5800</v>
+        <v>5100</v>
       </c>
       <c r="G307" s="48">
         <f t="shared" si="124"/>
-        <v>720000</v>
+        <v>600000</v>
       </c>
       <c r="H307" s="49">
         <v>33000</v>
@@ -15577,15 +15641,15 @@
       </c>
       <c r="J307" s="50">
         <f t="shared" si="121"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K307" s="50">
         <f t="shared" si="122"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L307" s="45">
         <f t="shared" si="123"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M307" s="1" t="s">
         <v>600</v>
@@ -15605,33 +15669,33 @@
         <v>513</v>
       </c>
       <c r="E308" s="147">
-        <v>240000</v>
+        <v>90000</v>
       </c>
       <c r="F308" s="128">
-        <v>9600</v>
+        <v>5100</v>
       </c>
       <c r="G308" s="48">
         <f t="shared" si="124"/>
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="H308" s="49">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I308" s="100">
         <f t="shared" si="115"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J308" s="50">
         <f t="shared" si="121"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K308" s="50">
         <f t="shared" si="122"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L308" s="45">
         <f t="shared" si="123"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M308" s="1" t="s">
         <v>600</v>
@@ -15651,33 +15715,33 @@
         <v>513</v>
       </c>
       <c r="E309" s="147">
-        <v>240000</v>
+        <v>90000</v>
       </c>
       <c r="F309" s="128">
-        <v>9600</v>
+        <v>5100</v>
       </c>
       <c r="G309" s="48">
         <f t="shared" si="124"/>
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="H309" s="49">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I309" s="100">
         <f t="shared" si="115"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J309" s="50">
         <f t="shared" si="121"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K309" s="50">
         <f t="shared" si="122"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L309" s="45">
         <f t="shared" ref="L309:L310" si="125">K309/K$2</f>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M309" s="1" t="s">
         <v>600</v>
@@ -15734,15 +15798,15 @@
       <c r="E311" s="67"/>
       <c r="F311" s="140">
         <f>SUM(F304:F309)</f>
-        <v>28540</v>
+        <v>18300</v>
       </c>
       <c r="G311" s="53">
         <f>SUM(G304:G309)</f>
-        <v>3553000</v>
+        <v>2160000</v>
       </c>
       <c r="H311" s="52">
         <f>SUM(H304:H309)</f>
-        <v>162800</v>
+        <v>118800</v>
       </c>
       <c r="I311" s="52"/>
       <c r="J311" s="25"/>
@@ -15823,14 +15887,14 @@
         <v>511</v>
       </c>
       <c r="E314" s="147">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="F314" s="128">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="G314" s="32">
         <f t="shared" ref="G314:G320" si="130">F314*150+E314</f>
-        <v>72000</v>
+        <v>60000</v>
       </c>
       <c r="H314" s="49">
         <v>3300</v>
@@ -15841,15 +15905,15 @@
       </c>
       <c r="J314" s="34">
         <f t="shared" si="127"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K314" s="34">
         <f t="shared" si="128"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L314" s="88">
         <f t="shared" si="129"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M314" s="1" t="s">
         <v>600</v>
@@ -15869,14 +15933,14 @@
         <v>511</v>
       </c>
       <c r="E315" s="147">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="F315" s="128">
-        <v>650</v>
+        <v>530</v>
       </c>
       <c r="G315" s="32">
         <f t="shared" si="130"/>
-        <v>120500</v>
+        <v>99500</v>
       </c>
       <c r="H315" s="49">
         <v>5500</v>
@@ -15887,15 +15951,15 @@
       </c>
       <c r="J315" s="34">
         <f t="shared" si="127"/>
-        <v>4.5643153526970952E-2</v>
+        <v>5.5276381909547742E-2</v>
       </c>
       <c r="K315" s="34">
         <f t="shared" si="128"/>
-        <v>21.90909090909091</v>
+        <v>18.09090909090909</v>
       </c>
       <c r="L315" s="88">
         <f t="shared" si="129"/>
-        <v>10.341090909090909</v>
+        <v>8.5389090909090903</v>
       </c>
       <c r="M315" s="1" t="s">
         <v>600</v>
@@ -15915,14 +15979,14 @@
         <v>511</v>
       </c>
       <c r="E316" s="147">
-        <v>45000</v>
+        <v>48000</v>
       </c>
       <c r="F316" s="128">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="G316" s="32">
         <f t="shared" si="130"/>
-        <v>240000</v>
+        <v>198000</v>
       </c>
       <c r="H316" s="49">
         <v>11000</v>
@@ -15933,15 +15997,15 @@
       </c>
       <c r="J316" s="34">
         <f t="shared" si="127"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5555555555555552E-2</v>
       </c>
       <c r="K316" s="34">
         <f t="shared" si="128"/>
-        <v>21.818181818181817</v>
+        <v>18</v>
       </c>
       <c r="L316" s="88">
         <f t="shared" si="129"/>
-        <v>10.298181818181817</v>
+        <v>8.4959999999999987</v>
       </c>
       <c r="M316" s="1" t="s">
         <v>600</v>
@@ -15964,11 +16028,11 @@
         <v>150000</v>
       </c>
       <c r="F317" s="128">
-        <v>3800</v>
+        <v>3000</v>
       </c>
       <c r="G317" s="32">
         <f t="shared" si="130"/>
-        <v>720000</v>
+        <v>600000</v>
       </c>
       <c r="H317" s="49">
         <v>33000</v>
@@ -15979,15 +16043,15 @@
       </c>
       <c r="J317" s="34">
         <f t="shared" si="127"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K317" s="34">
         <f t="shared" si="128"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L317" s="88">
         <f t="shared" si="129"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M317" s="1" t="s">
         <v>600</v>
@@ -16007,33 +16071,33 @@
         <v>511</v>
       </c>
       <c r="E318" s="147">
-        <v>210000</v>
+        <v>150000</v>
       </c>
       <c r="F318" s="128">
-        <v>6600</v>
+        <v>3000</v>
       </c>
       <c r="G318" s="32">
         <f t="shared" si="130"/>
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="H318" s="49">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I318" s="100">
         <f t="shared" si="126"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J318" s="34">
         <f t="shared" si="127"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K318" s="34">
         <f t="shared" si="128"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L318" s="88">
         <f t="shared" si="129"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M318" s="1" t="s">
         <v>600</v>
@@ -16053,33 +16117,33 @@
         <v>511</v>
       </c>
       <c r="E319" s="147">
-        <v>210000</v>
+        <v>150000</v>
       </c>
       <c r="F319" s="128">
-        <v>6600</v>
+        <v>3000</v>
       </c>
       <c r="G319" s="32">
         <f t="shared" si="130"/>
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="H319" s="49">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I319" s="100">
         <f t="shared" si="126"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J319" s="34">
         <f t="shared" si="127"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K319" s="34">
         <f t="shared" si="128"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L319" s="88">
         <f t="shared" si="129"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M319" s="1" t="s">
         <v>600</v>
@@ -16195,14 +16259,14 @@
         <v>512</v>
       </c>
       <c r="E323" s="147">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="F323" s="128">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="G323" s="32">
         <f t="shared" ref="G323:G329" si="134">F323*150+E323</f>
-        <v>72000</v>
+        <v>60000</v>
       </c>
       <c r="H323" s="49">
         <v>3300</v>
@@ -16213,15 +16277,15 @@
       </c>
       <c r="J323" s="34">
         <f t="shared" si="131"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K323" s="34">
         <f t="shared" si="132"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L323" s="88">
         <f t="shared" si="133"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M323" s="1" t="s">
         <v>600</v>
@@ -16241,14 +16305,14 @@
         <v>512</v>
       </c>
       <c r="E324" s="147">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="F324" s="128">
-        <v>650</v>
+        <v>530</v>
       </c>
       <c r="G324" s="32">
         <f t="shared" si="134"/>
-        <v>120500</v>
+        <v>99500</v>
       </c>
       <c r="H324" s="49">
         <v>5500</v>
@@ -16259,15 +16323,15 @@
       </c>
       <c r="J324" s="34">
         <f t="shared" si="131"/>
-        <v>4.5643153526970952E-2</v>
+        <v>5.5276381909547742E-2</v>
       </c>
       <c r="K324" s="34">
         <f t="shared" si="132"/>
-        <v>21.90909090909091</v>
+        <v>18.09090909090909</v>
       </c>
       <c r="L324" s="88">
         <f t="shared" si="133"/>
-        <v>10.341090909090909</v>
+        <v>8.5389090909090903</v>
       </c>
       <c r="M324" s="1" t="s">
         <v>600</v>
@@ -16287,14 +16351,14 @@
         <v>512</v>
       </c>
       <c r="E325" s="147">
-        <v>45000</v>
+        <v>48000</v>
       </c>
       <c r="F325" s="128">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="G325" s="32">
         <f t="shared" si="134"/>
-        <v>240000</v>
+        <v>198000</v>
       </c>
       <c r="H325" s="49">
         <v>11000</v>
@@ -16305,15 +16369,15 @@
       </c>
       <c r="J325" s="34">
         <f t="shared" si="131"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5555555555555552E-2</v>
       </c>
       <c r="K325" s="34">
         <f t="shared" si="132"/>
-        <v>21.818181818181817</v>
+        <v>18</v>
       </c>
       <c r="L325" s="88">
         <f t="shared" si="133"/>
-        <v>10.298181818181817</v>
+        <v>8.4959999999999987</v>
       </c>
       <c r="M325" s="1" t="s">
         <v>600</v>
@@ -16336,11 +16400,11 @@
         <v>150000</v>
       </c>
       <c r="F326" s="128">
-        <v>3800</v>
+        <v>3000</v>
       </c>
       <c r="G326" s="32">
         <f t="shared" si="134"/>
-        <v>720000</v>
+        <v>600000</v>
       </c>
       <c r="H326" s="49">
         <v>33000</v>
@@ -16351,15 +16415,15 @@
       </c>
       <c r="J326" s="34">
         <f t="shared" si="131"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K326" s="34">
         <f t="shared" si="132"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L326" s="88">
         <f t="shared" si="133"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M326" s="1" t="s">
         <v>600</v>
@@ -16379,33 +16443,33 @@
         <v>512</v>
       </c>
       <c r="E327" s="147">
-        <v>210000</v>
+        <v>150000</v>
       </c>
       <c r="F327" s="128">
-        <v>6600</v>
+        <v>3000</v>
       </c>
       <c r="G327" s="32">
         <f t="shared" si="134"/>
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="H327" s="49">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I327" s="100">
         <f t="shared" si="126"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J327" s="34">
         <f t="shared" si="131"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K327" s="34">
         <f t="shared" si="132"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L327" s="88">
         <f t="shared" si="133"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M327" s="1" t="s">
         <v>600</v>
@@ -16425,33 +16489,33 @@
         <v>512</v>
       </c>
       <c r="E328" s="147">
-        <v>210000</v>
+        <v>150000</v>
       </c>
       <c r="F328" s="128">
-        <v>6600</v>
+        <v>3000</v>
       </c>
       <c r="G328" s="32">
         <f t="shared" si="134"/>
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="H328" s="49">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I328" s="100">
         <f t="shared" si="126"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J328" s="34">
         <f t="shared" si="131"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K328" s="34">
         <f t="shared" si="132"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L328" s="88">
         <f t="shared" si="133"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M328" s="1" t="s">
         <v>600</v>
@@ -17064,7 +17128,7 @@
       <c r="J352" s="90"/>
       <c r="K352" s="90"/>
     </row>
-    <row r="353" spans="1:12">
+    <row r="353" spans="1:14">
       <c r="A353" s="1" t="s">
         <v>74</v>
       </c>
@@ -17083,10 +17147,10 @@
       <c r="J353" s="90"/>
       <c r="K353" s="90"/>
     </row>
-    <row r="354" spans="1:12">
+    <row r="354" spans="1:14">
       <c r="D354" s="12"/>
     </row>
-    <row r="355" spans="1:12">
+    <row r="355" spans="1:14">
       <c r="A355" s="1" t="s">
         <v>74</v>
       </c>
@@ -17105,7 +17169,7 @@
       <c r="J355" s="90"/>
       <c r="K355" s="90"/>
     </row>
-    <row r="356" spans="1:12">
+    <row r="356" spans="1:14">
       <c r="A356" s="1" t="s">
         <v>74</v>
       </c>
@@ -17124,7 +17188,7 @@
       <c r="J356" s="90"/>
       <c r="K356" s="90"/>
     </row>
-    <row r="357" spans="1:12">
+    <row r="357" spans="1:14">
       <c r="A357" s="1" t="s">
         <v>74</v>
       </c>
@@ -17143,7 +17207,7 @@
       <c r="J357" s="90"/>
       <c r="K357" s="90"/>
     </row>
-    <row r="358" spans="1:12">
+    <row r="358" spans="1:14">
       <c r="A358" s="1" t="s">
         <v>74</v>
       </c>
@@ -17162,7 +17226,7 @@
       <c r="J358" s="90"/>
       <c r="K358" s="90"/>
     </row>
-    <row r="359" spans="1:12">
+    <row r="359" spans="1:14">
       <c r="A359" s="1" t="s">
         <v>74</v>
       </c>
@@ -17181,10 +17245,10 @@
       <c r="J359" s="90"/>
       <c r="K359" s="90"/>
     </row>
-    <row r="360" spans="1:12">
+    <row r="360" spans="1:14">
       <c r="D360" s="12"/>
     </row>
-    <row r="361" spans="1:12">
+    <row r="361" spans="1:14">
       <c r="A361" s="1" t="s">
         <v>74</v>
       </c>
@@ -17203,7 +17267,7 @@
       <c r="J361" s="90"/>
       <c r="K361" s="90"/>
     </row>
-    <row r="362" spans="1:12">
+    <row r="362" spans="1:14">
       <c r="A362" s="1" t="s">
         <v>74</v>
       </c>
@@ -17222,7 +17286,7 @@
       <c r="J362" s="90"/>
       <c r="K362" s="90"/>
     </row>
-    <row r="363" spans="1:12">
+    <row r="363" spans="1:14">
       <c r="A363" s="1" t="s">
         <v>74</v>
       </c>
@@ -17241,7 +17305,7 @@
       <c r="J363" s="90"/>
       <c r="K363" s="90"/>
     </row>
-    <row r="364" spans="1:12">
+    <row r="364" spans="1:14">
       <c r="A364" s="1" t="s">
         <v>74</v>
       </c>
@@ -17260,7 +17324,7 @@
       <c r="J364" s="90"/>
       <c r="K364" s="90"/>
     </row>
-    <row r="365" spans="1:12">
+    <row r="365" spans="1:14">
       <c r="A365" s="1" t="s">
         <v>74</v>
       </c>
@@ -17279,17 +17343,17 @@
       <c r="J365" s="90"/>
       <c r="K365" s="90"/>
     </row>
-    <row r="366" spans="1:12">
+    <row r="366" spans="1:14">
       <c r="D366" s="12"/>
     </row>
-    <row r="367" spans="1:12">
+    <row r="367" spans="1:14">
       <c r="B367" s="22" t="s">
         <v>241</v>
       </c>
       <c r="D367" s="26"/>
       <c r="E367" s="139"/>
     </row>
-    <row r="368" spans="1:12">
+    <row r="368" spans="1:14">
       <c r="A368" s="1" t="s">
         <v>74</v>
       </c>
@@ -17303,14 +17367,14 @@
         <v>455</v>
       </c>
       <c r="E368" s="147">
-        <v>14000</v>
+        <v>10000</v>
       </c>
       <c r="F368" s="128">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="G368" s="32">
         <f>F368*200+E368</f>
-        <v>72000</v>
+        <v>60000</v>
       </c>
       <c r="H368" s="33">
         <v>3300</v>
@@ -17321,15 +17385,18 @@
       </c>
       <c r="J368" s="34">
         <f t="shared" ref="J368:J377" si="140">H368/G368</f>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K368" s="34">
         <f t="shared" ref="K368:K377" si="141">G368/H368</f>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L368" s="88">
         <f>K368/K$2</f>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
+      </c>
+      <c r="N368" s="102">
+        <v>330</v>
       </c>
     </row>
     <row r="369" spans="1:14">
@@ -17349,11 +17416,11 @@
         <v>20000</v>
       </c>
       <c r="F369" s="128">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G369" s="32">
         <f t="shared" ref="G369:G377" si="142">F369*200+E369</f>
-        <v>120000</v>
+        <v>100000</v>
       </c>
       <c r="H369" s="33">
         <v>5500</v>
@@ -17364,15 +17431,18 @@
       </c>
       <c r="J369" s="34">
         <f t="shared" si="140"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K369" s="34">
         <f t="shared" si="141"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L369" s="88">
         <f t="shared" ref="L369:L376" si="143">K369/K$2</f>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
+      </c>
+      <c r="N369" s="102">
+        <v>550</v>
       </c>
     </row>
     <row r="370" spans="1:14">
@@ -17392,11 +17462,11 @@
         <v>40000</v>
       </c>
       <c r="F370" s="128">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="G370" s="32">
         <f t="shared" si="142"/>
-        <v>240000</v>
+        <v>200000</v>
       </c>
       <c r="H370" s="33">
         <v>11000</v>
@@ -17407,15 +17477,18 @@
       </c>
       <c r="J370" s="34">
         <f t="shared" si="140"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K370" s="34">
         <f t="shared" si="141"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L370" s="88">
         <f t="shared" si="143"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
+      </c>
+      <c r="N370" s="102">
+        <v>1100</v>
       </c>
     </row>
     <row r="371" spans="1:14">
@@ -17435,11 +17508,11 @@
         <v>120000</v>
       </c>
       <c r="F371" s="128">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="G371" s="32">
         <f t="shared" si="142"/>
-        <v>720000</v>
+        <v>600000</v>
       </c>
       <c r="H371" s="33">
         <v>33000</v>
@@ -17450,15 +17523,18 @@
       </c>
       <c r="J371" s="34">
         <f t="shared" si="140"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K371" s="34">
         <f t="shared" si="141"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L371" s="88">
         <f t="shared" si="143"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
+      </c>
+      <c r="N371" s="102">
+        <v>3300</v>
       </c>
     </row>
     <row r="372" spans="1:14">
@@ -17475,33 +17551,36 @@
         <v>455</v>
       </c>
       <c r="E372" s="147">
-        <v>240000</v>
+        <v>120000</v>
       </c>
       <c r="F372" s="128">
-        <v>4800</v>
+        <v>2400</v>
       </c>
       <c r="G372" s="32">
         <f t="shared" si="142"/>
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="H372" s="33">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I372" s="102">
         <f t="shared" si="139"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J372" s="34">
         <f t="shared" si="140"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K372" s="34">
         <f t="shared" si="141"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L372" s="88">
         <f t="shared" si="143"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
+      </c>
+      <c r="N372" s="102">
+        <v>3300</v>
       </c>
     </row>
     <row r="373" spans="1:14">
@@ -17521,11 +17600,11 @@
         <v>40000</v>
       </c>
       <c r="F373" s="128">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="G373" s="32">
         <f t="shared" si="142"/>
-        <v>240000</v>
+        <v>200000</v>
       </c>
       <c r="H373" s="33">
         <v>11000</v>
@@ -17536,15 +17615,18 @@
       </c>
       <c r="J373" s="34">
         <f t="shared" si="140"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K373" s="34">
         <f t="shared" si="141"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L373" s="88">
         <f t="shared" si="143"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
+      </c>
+      <c r="N373" s="102">
+        <v>1100</v>
       </c>
     </row>
     <row r="374" spans="1:14">
@@ -17564,11 +17646,11 @@
         <v>120000</v>
       </c>
       <c r="F374" s="128">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="G374" s="32">
         <f t="shared" si="142"/>
-        <v>720000</v>
+        <v>600000</v>
       </c>
       <c r="H374" s="33">
         <v>33000</v>
@@ -17579,15 +17661,18 @@
       </c>
       <c r="J374" s="34">
         <f t="shared" si="140"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K374" s="34">
         <f t="shared" si="141"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L374" s="88">
         <f t="shared" si="143"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
+      </c>
+      <c r="N374" s="102">
+        <v>3300</v>
       </c>
     </row>
     <row r="375" spans="1:14">
@@ -17604,33 +17689,36 @@
         <v>455</v>
       </c>
       <c r="E375" s="147">
-        <v>240000</v>
+        <v>120000</v>
       </c>
       <c r="F375" s="128">
-        <v>4800</v>
+        <v>2400</v>
       </c>
       <c r="G375" s="32">
         <f t="shared" si="142"/>
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="H375" s="33">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I375" s="102">
         <f t="shared" si="139"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J375" s="34">
         <f t="shared" si="140"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K375" s="34">
         <f t="shared" si="141"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L375" s="88">
         <f t="shared" si="143"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
+      </c>
+      <c r="N375" s="102">
+        <v>3300</v>
       </c>
     </row>
     <row r="376" spans="1:14">
@@ -17650,11 +17738,11 @@
         <v>120000</v>
       </c>
       <c r="F376" s="128">
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="G376" s="32">
         <f t="shared" si="142"/>
-        <v>720000</v>
+        <v>600000</v>
       </c>
       <c r="H376" s="33">
         <v>33000</v>
@@ -17665,15 +17753,18 @@
       </c>
       <c r="J376" s="34">
         <f t="shared" si="140"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K376" s="34">
         <f t="shared" si="141"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L376" s="88">
         <f t="shared" si="143"/>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
+      </c>
+      <c r="N376" s="102">
+        <v>3300</v>
       </c>
     </row>
     <row r="377" spans="1:14">
@@ -17690,33 +17781,36 @@
         <v>455</v>
       </c>
       <c r="E377" s="147">
-        <v>240000</v>
+        <v>120000</v>
       </c>
       <c r="F377" s="128">
-        <v>4800</v>
+        <v>2400</v>
       </c>
       <c r="G377" s="32">
         <f t="shared" si="142"/>
-        <v>1200000</v>
+        <v>600000</v>
       </c>
       <c r="H377" s="33">
-        <v>55000</v>
+        <v>33000</v>
       </c>
       <c r="I377" s="102">
         <f t="shared" si="139"/>
-        <v>5500</v>
+        <v>3300</v>
       </c>
       <c r="J377" s="34">
         <f t="shared" si="140"/>
-        <v>4.583333333333333E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K377" s="34">
         <f t="shared" si="141"/>
-        <v>21.818181818181817</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L377" s="88">
         <f>K377/K$2</f>
-        <v>10.298181818181817</v>
+        <v>8.581818181818182</v>
+      </c>
+      <c r="N377" s="102">
+        <v>3300</v>
       </c>
     </row>
     <row r="378" spans="1:14">
@@ -18616,7 +18710,7 @@
         <v>602</v>
       </c>
       <c r="E399" s="147">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="F399" s="128">
         <v>2744056000</v>
@@ -18664,7 +18758,7 @@
         <v>603</v>
       </c>
       <c r="E400" s="147">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="F400" s="128">
         <v>18341848000</v>
@@ -18712,7 +18806,7 @@
         <v>603</v>
       </c>
       <c r="E401" s="147">
-        <v>48000</v>
+        <v>40000</v>
       </c>
       <c r="F401" s="128">
         <v>47804344000</v>
@@ -18760,7 +18854,7 @@
         <v>603</v>
       </c>
       <c r="E402" s="147">
-        <v>48000</v>
+        <v>40000</v>
       </c>
       <c r="F402" s="128">
         <v>79740101000</v>
@@ -18808,7 +18902,7 @@
         <v>603</v>
       </c>
       <c r="E403" s="147">
-        <v>48000</v>
+        <v>40000</v>
       </c>
       <c r="F403" s="128">
         <v>129783016999.99998</v>
@@ -18856,7 +18950,7 @@
         <v>603</v>
       </c>
       <c r="E404" s="147">
-        <v>48000</v>
+        <v>40000</v>
       </c>
       <c r="F404" s="128">
         <v>164535042000</v>
@@ -18904,7 +18998,7 @@
         <v>603</v>
       </c>
       <c r="E405" s="147">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="F405" s="128">
         <v>190188355000</v>
@@ -18952,7 +19046,7 @@
         <v>603</v>
       </c>
       <c r="E406" s="147">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="F406" s="128">
         <v>201543692000</v>
@@ -19000,7 +19094,7 @@
         <v>603</v>
       </c>
       <c r="E407" s="147">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="F407" s="128">
         <v>257869052000</v>
@@ -19048,7 +19142,7 @@
         <v>603</v>
       </c>
       <c r="E408" s="147">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="F408" s="128">
         <v>321126764000</v>
@@ -19099,17 +19193,17 @@
         <v>262</v>
       </c>
       <c r="D410" s="28" t="s">
-        <v>48</v>
+        <v>604</v>
       </c>
       <c r="E410" s="148">
-        <v>60000</v>
+        <v>14000</v>
       </c>
       <c r="F410" s="119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G410" s="48">
         <f>4*10000*F410+E410</f>
-        <v>60000</v>
+        <v>94000</v>
       </c>
       <c r="H410" s="33">
         <v>3300</v>
@@ -19120,15 +19214,15 @@
       </c>
       <c r="J410" s="50">
         <f t="shared" ref="J410:J418" si="152">H410/G410</f>
-        <v>5.5E-2</v>
+        <v>3.5106382978723406E-2</v>
       </c>
       <c r="K410" s="50">
         <f t="shared" ref="K410:K418" si="153">G410/H410</f>
-        <v>18.181818181818183</v>
+        <v>28.484848484848484</v>
       </c>
       <c r="L410" s="45">
         <f t="shared" ref="L410" si="154">K410/K$2</f>
-        <v>8.581818181818182</v>
+        <v>13.444848484848483</v>
       </c>
       <c r="M410" s="1" t="s">
         <v>600</v>
@@ -19145,17 +19239,17 @@
         <v>263</v>
       </c>
       <c r="D411" s="28" t="s">
-        <v>456</v>
+        <v>604</v>
       </c>
       <c r="E411" s="148">
-        <v>50000</v>
+        <v>24000</v>
       </c>
       <c r="F411" s="119">
-        <v>150000</v>
+        <v>3</v>
       </c>
       <c r="G411" s="48">
-        <f>E411+(F411*1/3)</f>
-        <v>100000</v>
+        <f t="shared" ref="G411:G418" si="155">4*10000*F411+E411</f>
+        <v>144000</v>
       </c>
       <c r="H411" s="33">
         <v>5500</v>
@@ -19166,15 +19260,15 @@
       </c>
       <c r="J411" s="50">
         <f t="shared" si="152"/>
-        <v>5.5E-2</v>
+        <v>3.8194444444444448E-2</v>
       </c>
       <c r="K411" s="50">
         <f t="shared" si="153"/>
-        <v>18.181818181818183</v>
+        <v>26.181818181818183</v>
       </c>
       <c r="L411" s="45">
-        <f t="shared" ref="L411:L414" si="155">K411/K$2</f>
-        <v>8.581818181818182</v>
+        <f t="shared" ref="L411:L414" si="156">K411/K$2</f>
+        <v>12.357818181818182</v>
       </c>
       <c r="M411" s="1" t="s">
         <v>600</v>
@@ -19191,17 +19285,17 @@
         <v>264</v>
       </c>
       <c r="D412" s="28" t="s">
-        <v>456</v>
+        <v>604</v>
       </c>
       <c r="E412" s="148">
-        <v>50000</v>
+        <v>48000</v>
       </c>
       <c r="F412" s="119">
-        <v>450000</v>
+        <v>4</v>
       </c>
       <c r="G412" s="48">
-        <f t="shared" ref="G412:G418" si="156">E412+(F412*1/3)</f>
-        <v>200000</v>
+        <f t="shared" si="155"/>
+        <v>208000</v>
       </c>
       <c r="H412" s="33">
         <v>11000</v>
@@ -19212,15 +19306,15 @@
       </c>
       <c r="J412" s="50">
         <f t="shared" si="152"/>
-        <v>5.5E-2</v>
+        <v>5.2884615384615384E-2</v>
       </c>
       <c r="K412" s="50">
         <f t="shared" si="153"/>
-        <v>18.181818181818183</v>
+        <v>18.90909090909091</v>
       </c>
       <c r="L412" s="45">
-        <f t="shared" si="155"/>
-        <v>8.581818181818182</v>
+        <f t="shared" si="156"/>
+        <v>8.9250909090909083</v>
       </c>
       <c r="M412" s="1" t="s">
         <v>600</v>
@@ -19237,17 +19331,17 @@
         <v>265</v>
       </c>
       <c r="D413" s="28" t="s">
-        <v>456</v>
+        <v>604</v>
       </c>
       <c r="E413" s="147">
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="F413" s="119">
-        <v>1650000</v>
+        <v>10</v>
       </c>
       <c r="G413" s="48">
-        <f t="shared" si="156"/>
-        <v>600000</v>
+        <f t="shared" si="155"/>
+        <v>550000</v>
       </c>
       <c r="H413" s="33">
         <v>33000</v>
@@ -19258,15 +19352,15 @@
       </c>
       <c r="J413" s="50">
         <f t="shared" si="152"/>
-        <v>5.5E-2</v>
+        <v>0.06</v>
       </c>
       <c r="K413" s="50">
         <f t="shared" si="153"/>
-        <v>18.181818181818183</v>
+        <v>16.666666666666668</v>
       </c>
       <c r="L413" s="45">
-        <f t="shared" si="155"/>
-        <v>8.581818181818182</v>
+        <f t="shared" si="156"/>
+        <v>7.8666666666666671</v>
       </c>
       <c r="M413" s="1" t="s">
         <v>600</v>
@@ -19283,36 +19377,36 @@
         <v>266</v>
       </c>
       <c r="D414" s="28" t="s">
-        <v>456</v>
+        <v>604</v>
       </c>
       <c r="E414" s="147">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="F414" s="119">
-        <v>1650000</v>
+        <v>15</v>
       </c>
       <c r="G414" s="48">
-        <f t="shared" si="156"/>
-        <v>600000</v>
+        <f t="shared" si="155"/>
+        <v>800000</v>
       </c>
       <c r="H414" s="33">
-        <v>33000</v>
+        <v>55000</v>
       </c>
       <c r="I414" s="102">
         <f t="shared" si="147"/>
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="J414" s="50">
         <f t="shared" si="152"/>
-        <v>5.5E-2</v>
+        <v>6.8750000000000006E-2</v>
       </c>
       <c r="K414" s="50">
         <f t="shared" si="153"/>
-        <v>18.181818181818183</v>
+        <v>14.545454545454545</v>
       </c>
       <c r="L414" s="45">
-        <f t="shared" si="155"/>
-        <v>8.581818181818182</v>
+        <f t="shared" si="156"/>
+        <v>6.8654545454545453</v>
       </c>
       <c r="M414" s="1" t="s">
         <v>600</v>
@@ -19329,36 +19423,36 @@
         <v>267</v>
       </c>
       <c r="D415" s="28" t="s">
-        <v>456</v>
+        <v>604</v>
       </c>
       <c r="E415" s="147">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="F415" s="119">
-        <v>1650000</v>
+        <v>15</v>
       </c>
       <c r="G415" s="48">
-        <f t="shared" si="156"/>
-        <v>600000</v>
+        <f t="shared" si="155"/>
+        <v>800000</v>
       </c>
       <c r="H415" s="33">
-        <v>33000</v>
+        <v>55000</v>
       </c>
       <c r="I415" s="102">
         <f t="shared" si="147"/>
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="J415" s="50">
         <f t="shared" si="152"/>
-        <v>5.5E-2</v>
+        <v>6.8750000000000006E-2</v>
       </c>
       <c r="K415" s="50">
         <f t="shared" si="153"/>
-        <v>18.181818181818183</v>
+        <v>14.545454545454545</v>
       </c>
       <c r="L415" s="45">
         <f t="shared" ref="L415:L418" si="157">K415/K$2</f>
-        <v>8.581818181818182</v>
+        <v>6.8654545454545453</v>
       </c>
       <c r="M415" s="1" t="s">
         <v>600</v>
@@ -19375,36 +19469,36 @@
         <v>268</v>
       </c>
       <c r="D416" s="28" t="s">
-        <v>456</v>
+        <v>604</v>
       </c>
       <c r="E416" s="147">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="F416" s="119">
-        <v>1650000</v>
+        <v>15</v>
       </c>
       <c r="G416" s="48">
-        <f t="shared" si="156"/>
-        <v>600000</v>
+        <f t="shared" si="155"/>
+        <v>800000</v>
       </c>
       <c r="H416" s="33">
-        <v>33000</v>
+        <v>55000</v>
       </c>
       <c r="I416" s="102">
         <f t="shared" si="147"/>
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="J416" s="50">
         <f t="shared" si="152"/>
-        <v>5.5E-2</v>
+        <v>6.8750000000000006E-2</v>
       </c>
       <c r="K416" s="50">
         <f t="shared" si="153"/>
-        <v>18.181818181818183</v>
+        <v>14.545454545454545</v>
       </c>
       <c r="L416" s="45">
         <f t="shared" si="157"/>
-        <v>8.581818181818182</v>
+        <v>6.8654545454545453</v>
       </c>
       <c r="M416" s="1" t="s">
         <v>600</v>
@@ -19421,36 +19515,36 @@
         <v>269</v>
       </c>
       <c r="D417" s="28" t="s">
-        <v>456</v>
+        <v>604</v>
       </c>
       <c r="E417" s="147">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="F417" s="119">
-        <v>1650000</v>
+        <v>15</v>
       </c>
       <c r="G417" s="48">
-        <f t="shared" si="156"/>
-        <v>600000</v>
+        <f t="shared" si="155"/>
+        <v>800000</v>
       </c>
       <c r="H417" s="33">
-        <v>33000</v>
+        <v>55000</v>
       </c>
       <c r="I417" s="102">
         <f t="shared" si="147"/>
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="J417" s="50">
         <f t="shared" si="152"/>
-        <v>5.5E-2</v>
+        <v>6.8750000000000006E-2</v>
       </c>
       <c r="K417" s="50">
         <f t="shared" si="153"/>
-        <v>18.181818181818183</v>
+        <v>14.545454545454545</v>
       </c>
       <c r="L417" s="45">
         <f t="shared" si="157"/>
-        <v>8.581818181818182</v>
+        <v>6.8654545454545453</v>
       </c>
       <c r="M417" s="1" t="s">
         <v>600</v>
@@ -19467,36 +19561,36 @@
         <v>270</v>
       </c>
       <c r="D418" s="28" t="s">
-        <v>456</v>
+        <v>604</v>
       </c>
       <c r="E418" s="147">
-        <v>50000</v>
+        <v>200000</v>
       </c>
       <c r="F418" s="119">
-        <v>1650000</v>
+        <v>15</v>
       </c>
       <c r="G418" s="48">
-        <f t="shared" si="156"/>
-        <v>600000</v>
+        <f t="shared" si="155"/>
+        <v>800000</v>
       </c>
       <c r="H418" s="33">
-        <v>33000</v>
+        <v>55000</v>
       </c>
       <c r="I418" s="102">
         <f t="shared" si="147"/>
-        <v>3300</v>
+        <v>5500</v>
       </c>
       <c r="J418" s="50">
         <f t="shared" si="152"/>
-        <v>5.5E-2</v>
+        <v>6.8750000000000006E-2</v>
       </c>
       <c r="K418" s="50">
         <f t="shared" si="153"/>
-        <v>18.181818181818183</v>
+        <v>14.545454545454545</v>
       </c>
       <c r="L418" s="45">
         <f t="shared" si="157"/>
-        <v>8.581818181818182</v>
+        <v>6.8654545454545453</v>
       </c>
       <c r="M418" s="1" t="s">
         <v>600</v>
@@ -19505,7 +19599,7 @@
     <row r="419" spans="1:13">
       <c r="H419" s="13">
         <f>SUM(H410:H418)</f>
-        <v>217800</v>
+        <v>327800</v>
       </c>
     </row>
     <row r="420" spans="1:13">
@@ -20339,7 +20433,7 @@
     </row>
     <row r="440" spans="1:17">
       <c r="B440" s="22" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D440" s="26"/>
       <c r="E440" s="139"/>
@@ -20351,13 +20445,13 @@
       <c r="K440" s="25"/>
       <c r="L440" s="89"/>
       <c r="N440" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O440" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="P440" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="441" spans="1:17">
@@ -20365,13 +20459,13 @@
         <v>74</v>
       </c>
       <c r="B441" s="28" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C441" s="182">
         <v>200</v>
       </c>
       <c r="D441" s="69" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E441" s="147">
         <v>10000</v>
@@ -20404,7 +20498,7 @@
       </c>
       <c r="M441" s="178"/>
       <c r="N441" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O441" s="44">
         <v>200</v>
@@ -20418,13 +20512,13 @@
         <v>74</v>
       </c>
       <c r="B442" s="28" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C442" s="182">
         <v>1000</v>
       </c>
       <c r="D442" s="69" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E442" s="183">
         <v>20000</v>
@@ -20456,7 +20550,7 @@
         <v>7.0370909090909084</v>
       </c>
       <c r="N442" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O442" s="44">
         <v>300</v>
@@ -20475,13 +20569,13 @@
         <v>74</v>
       </c>
       <c r="B443" s="28" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C443" s="182">
         <v>2000</v>
       </c>
       <c r="D443" s="69" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E443" s="183">
         <v>30000</v>
@@ -20513,7 +20607,7 @@
         <v>7.0799999999999992</v>
       </c>
       <c r="N443" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O443" s="44">
         <v>500</v>
@@ -20532,13 +20626,13 @@
         <v>74</v>
       </c>
       <c r="B444" s="28" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C444" s="182">
         <v>3000</v>
       </c>
       <c r="D444" s="69" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E444" s="183">
         <v>45000</v>
@@ -20570,7 +20664,7 @@
         <v>7.0799999999999992</v>
       </c>
       <c r="N444" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O444" s="44">
         <v>700</v>
@@ -20589,13 +20683,13 @@
         <v>74</v>
       </c>
       <c r="B445" s="28" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C445" s="182">
         <v>4000</v>
       </c>
       <c r="D445" s="69" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E445" s="147">
         <v>20000</v>
@@ -20627,7 +20721,7 @@
         <v>7.0370909090909084</v>
       </c>
       <c r="N445" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="O445" s="44">
         <v>900</v>
@@ -20646,13 +20740,13 @@
         <v>74</v>
       </c>
       <c r="B446" s="28" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C446" s="182">
         <v>5000</v>
       </c>
       <c r="D446" s="69" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E446" s="147">
         <v>30000</v>
@@ -20684,7 +20778,7 @@
         <v>7.0799999999999992</v>
       </c>
       <c r="N446" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O446" s="44">
         <v>1100</v>
@@ -20703,13 +20797,13 @@
         <v>74</v>
       </c>
       <c r="B447" s="28" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C447" s="182">
         <v>6000</v>
       </c>
       <c r="D447" s="69" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E447" s="147">
         <v>45000</v>
@@ -20741,7 +20835,7 @@
         <v>7.0799999999999992</v>
       </c>
       <c r="N447" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="O447" s="44">
         <v>1400</v>
@@ -20760,13 +20854,13 @@
         <v>74</v>
       </c>
       <c r="B448" s="28" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C448" s="182">
         <v>7000</v>
       </c>
       <c r="D448" s="69" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E448" s="183">
         <v>20000</v>
@@ -20798,7 +20892,7 @@
         <v>7.0370909090909084</v>
       </c>
       <c r="N448" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O448" s="44">
         <v>1700</v>
@@ -20817,13 +20911,13 @@
         <v>74</v>
       </c>
       <c r="B449" s="28" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C449" s="182">
         <v>8000</v>
       </c>
       <c r="D449" s="69" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E449" s="183">
         <v>30000</v>
@@ -20855,7 +20949,7 @@
         <v>7.0799999999999992</v>
       </c>
       <c r="N449" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O449" s="44">
         <v>2000</v>
@@ -20874,13 +20968,13 @@
         <v>74</v>
       </c>
       <c r="B450" s="28" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C450" s="182">
         <v>9000</v>
       </c>
       <c r="D450" s="69" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E450" s="183">
         <v>45000</v>
@@ -20955,7 +21049,7 @@
       </c>
       <c r="C453" s="44"/>
       <c r="D453" s="28" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E453" s="147"/>
       <c r="F453" s="119">
@@ -21103,11 +21197,11 @@
         <v>74</v>
       </c>
       <c r="B471" s="28" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C471" s="44"/>
       <c r="D471" s="28" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E471" s="147"/>
       <c r="F471" s="119">
@@ -21153,6 +21247,34 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{EFD7BE13-65A7-4F71-8221-2F2BAF3F5F8D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L183">
+    <cfRule type="dataBar" priority="94">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5C0E93B6-19A8-4E38-85A4-30A2DB3F5B56}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L451">
+    <cfRule type="dataBar" priority="96">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3E171C8C-BC18-4404-B040-C93AEC6CD1B3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21395,6 +21517,34 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L149:L151">
+    <cfRule type="dataBar" priority="93">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{17EE9319-948D-4DE7-9836-7CB0701A4AC2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L152:L156 L132:L148">
+    <cfRule type="dataBar" priority="88">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2A29568F-EA4F-4BBF-9268-F447B5C0D02D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L159:L183">
     <cfRule type="dataBar" priority="58">
       <dataBar>
@@ -21419,6 +21569,20 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{739283B8-39C7-400D-9B66-D87F9D83C420}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L186:L253">
+    <cfRule type="dataBar" priority="15">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D07E7712-D2B0-40D1-A103-B6518083ECC9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21465,6 +21629,34 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L261:L264 L257:L259 L266:L451 L6:L255">
+    <cfRule type="dataBar" priority="69">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6A0D2B79-679B-4D8C-AA40-0EB9DFA51DB1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L272:L291">
+    <cfRule type="dataBar" priority="16">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D3774836-057B-49BF-A577-3C1CC0561486}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L294:L301">
     <cfRule type="dataBar" priority="59">
       <dataBar>
@@ -21475,6 +21667,20 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{7D9C5564-B205-4606-8518-7542143A913A}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L294:L329">
+    <cfRule type="dataBar" priority="18">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9F5CE0D0-0F2B-4415-BFB1-5DCA8F3236ED}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21535,6 +21741,20 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L331:L341">
+    <cfRule type="dataBar" priority="17">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DFBA62C5-ADE3-44C2-9168-8112116135AE}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L337:L341">
     <cfRule type="dataBar" priority="28">
       <dataBar>
@@ -21545,6 +21765,34 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{F1A9F9CD-22DA-4E27-8701-C931B410FCF0}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L368:L377">
+    <cfRule type="dataBar" priority="19">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{18BC91AE-2BB9-44A0-89CF-709D3612A9FB}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L379:L396">
+    <cfRule type="dataBar" priority="22">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3E45A48B-3D70-42D1-BAC8-79BCC297763B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21591,160 +21839,6 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L379:L396">
-    <cfRule type="dataBar" priority="22">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3E45A48B-3D70-42D1-BAC8-79BCC297763B}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L368:L377">
-    <cfRule type="dataBar" priority="19">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{18BC91AE-2BB9-44A0-89CF-709D3612A9FB}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L294:L329">
-    <cfRule type="dataBar" priority="18">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9F5CE0D0-0F2B-4415-BFB1-5DCA8F3236ED}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L331:L341">
-    <cfRule type="dataBar" priority="17">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DFBA62C5-ADE3-44C2-9168-8112116135AE}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L272:L291">
-    <cfRule type="dataBar" priority="16">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D3774836-057B-49BF-A577-3C1CC0561486}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L186:L253">
-    <cfRule type="dataBar" priority="15">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D07E7712-D2B0-40D1-A103-B6518083ECC9}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L471">
-    <cfRule type="dataBar" priority="11">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{697BCDA5-6DD0-4FA2-A6EF-9605CFB7C0C2}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L471">
-    <cfRule type="dataBar" priority="10">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E70611B5-6FD7-4807-9027-D7E6103C64D0}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L471">
-    <cfRule type="dataBar" priority="9">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42399625-6295-4C03-BDDE-07A3ABDB2C86}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L261:L264 L257:L259 L266:L451 L6:L255">
-    <cfRule type="dataBar" priority="69">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6A0D2B79-679B-4D8C-AA40-0EB9DFA51DB1}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L441:L451">
-    <cfRule type="dataBar" priority="74">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{74620703-BF19-4640-AC24-E30BD4F7C856}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="L440:L451">
     <cfRule type="dataBar" priority="76">
       <dataBar>
@@ -21773,8 +21867,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L152:L156 L132:L148">
-    <cfRule type="dataBar" priority="88">
+  <conditionalFormatting sqref="L441:L451">
+    <cfRule type="dataBar" priority="74">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -21782,49 +21876,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2A29568F-EA4F-4BBF-9268-F447B5C0D02D}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L149:L151">
-    <cfRule type="dataBar" priority="93">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17EE9319-948D-4DE7-9836-7CB0701A4AC2}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L6:L183">
-    <cfRule type="dataBar" priority="94">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5C0E93B6-19A8-4E38-85A4-30A2DB3F5B56}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L6:L451">
-    <cfRule type="dataBar" priority="96">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3E171C8C-BC18-4404-B040-C93AEC6CD1B3}</x14:id>
+          <x14:id>{74620703-BF19-4640-AC24-E30BD4F7C856}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21842,8 +21894,18 @@
         </ext>
       </extLst>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L453">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{296AD117-EB92-4B03-AF90-D22F9F14A569}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -21857,8 +21919,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L453">
-    <cfRule type="dataBar" priority="3">
+  <conditionalFormatting sqref="L471">
+    <cfRule type="dataBar" priority="11">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -21866,7 +21928,31 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{296AD117-EB92-4B03-AF90-D22F9F14A569}</x14:id>
+          <x14:id>{697BCDA5-6DD0-4FA2-A6EF-9605CFB7C0C2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E70611B5-6FD7-4807-9027-D7E6103C64D0}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{42399625-6295-4C03-BDDE-07A3ABDB2C86}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -21874,7 +21960,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="G227 I32 I45 G302 G206 G411" formula="1"/>
+    <ignoredError sqref="G227 I32 I45 G302 G206" formula="1"/>
     <ignoredError sqref="P13:P17 P4 P6:P10 H311 F311 F302 H302 H206" formulaRange="1"/>
     <ignoredError sqref="J399:J408" evalError="1"/>
   </ignoredErrors>
@@ -21891,6 +21977,32 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>L6:L10</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{5C0E93B6-19A8-4E38-85A4-30A2DB3F5B56}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L6:L183</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{3E171C8C-BC18-4404-B040-C93AEC6CD1B3}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L6:L451</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{DF02CB43-31EF-4457-9F48-52A3600B0A42}">
@@ -22080,6 +22192,28 @@
           <xm:sqref>L117:L128</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{17EE9319-948D-4DE7-9836-7CB0701A4AC2}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L149:L151</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{2A29568F-EA4F-4BBF-9268-F447B5C0D02D}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L152:L156 L132:L148</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{75749600-0CE8-4C3B-8C5E-557B960909C9}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
@@ -22100,6 +22234,19 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>L186:L205</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D07E7712-D2B0-40D1-A103-B6518083ECC9}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L186:L253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{EFAC932B-A7A8-4433-A61B-143378AE2D30}">
@@ -22135,6 +22282,32 @@
           <xm:sqref>L244:L253</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6A0D2B79-679B-4D8C-AA40-0EB9DFA51DB1}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L261:L264 L257:L259 L266:L451 L6:L255</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D3774836-057B-49BF-A577-3C1CC0561486}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L272:L291</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{7D9C5564-B205-4606-8518-7542143A913A}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
@@ -22144,6 +22317,19 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>L294:L301</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9F5CE0D0-0F2B-4415-BFB1-5DCA8F3236ED}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L294:L329</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{C300A0E2-648C-4005-AE4A-F3DDA166FCA7}">
@@ -22190,6 +22376,19 @@
           <xm:sqref>L331:L335</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{DFBA62C5-ADE3-44C2-9168-8112116135AE}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L331:L341</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{F1A9F9CD-22DA-4E27-8701-C931B410FCF0}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
@@ -22199,6 +22398,32 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>L337:L341</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{18BC91AE-2BB9-44A0-89CF-709D3612A9FB}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L368:L377</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{3E45A48B-3D70-42D1-BAC8-79BCC297763B}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L379:L396</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{E64BD501-892F-411D-9804-071034C4E308}">
@@ -22238,147 +22463,6 @@
           <xm:sqref>L420:L439</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3E45A48B-3D70-42D1-BAC8-79BCC297763B}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L379:L396</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{18BC91AE-2BB9-44A0-89CF-709D3612A9FB}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L368:L377</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9F5CE0D0-0F2B-4415-BFB1-5DCA8F3236ED}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L294:L329</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{DFBA62C5-ADE3-44C2-9168-8112116135AE}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L331:L341</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D3774836-057B-49BF-A577-3C1CC0561486}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L272:L291</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D07E7712-D2B0-40D1-A103-B6518083ECC9}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L186:L253</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{697BCDA5-6DD0-4FA2-A6EF-9605CFB7C0C2}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L471</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E70611B5-6FD7-4807-9027-D7E6103C64D0}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L471</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{42399625-6295-4C03-BDDE-07A3ABDB2C86}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L471</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6A0D2B79-679B-4D8C-AA40-0EB9DFA51DB1}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L261:L264 L257:L259 L266:L451 L6:L255</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{74620703-BF19-4640-AC24-E30BD4F7C856}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L441:L451</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{DDE7A09C-B005-4F3B-AFC9-56110C2EA5C2}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
@@ -22405,29 +22489,7 @@
           <xm:sqref>L441:L450</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2A29568F-EA4F-4BBF-9268-F447B5C0D02D}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L152:L156 L132:L148</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{17EE9319-948D-4DE7-9836-7CB0701A4AC2}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L149:L151</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5C0E93B6-19A8-4E38-85A4-30A2DB3F5B56}">
+          <x14:cfRule type="dataBar" id="{74620703-BF19-4640-AC24-E30BD4F7C856}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22437,20 +22499,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>L6:L183</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3E171C8C-BC18-4404-B040-C93AEC6CD1B3}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L6:L451</xm:sqref>
+          <xm:sqref>L441:L451</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{E992D9F9-2B21-4A1B-96E4-917ECECB4F18}">
@@ -22461,9 +22510,16 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>L453</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{296AD117-EB92-4B03-AF90-D22F9F14A569}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
           <x14:cfRule type="dataBar" id="{5841C66C-0AEE-4DD8-A91D-988B42D834AA}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
@@ -22477,7 +22533,15 @@
           <xm:sqref>L453</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{296AD117-EB92-4B03-AF90-D22F9F14A569}">
+          <x14:cfRule type="dataBar" id="{697BCDA5-6DD0-4FA2-A6EF-9605CFB7C0C2}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{E70611B5-6FD7-4807-9027-D7E6103C64D0}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -22487,7 +22551,17 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>L453</xm:sqref>
+          <x14:cfRule type="dataBar" id="{42399625-6295-4C03-BDDE-07A3ABDB2C86}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L471</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/BM(최종).xlsx
+++ b/BM(최종).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dksru\Desktop\NanseExcel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DFD6517-2073-4D56-89F9-A802A422AA6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168A1D89-5B06-426A-BA76-D159F6111ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
+    <workbookView xWindow="37395" yWindow="375" windowWidth="28800" windowHeight="15360" activeTab="1" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
   </bookViews>
   <sheets>
     <sheet name="재화 기준" sheetId="2" r:id="rId1"/>
@@ -2431,10 +2431,10 @@
     <xf numFmtId="41" fontId="17" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4"/>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="나쁨" xfId="1" builtinId="27"/>
@@ -4984,19 +4984,19 @@
       </c>
     </row>
     <row r="52" spans="1:13">
-      <c r="A52" s="161"/>
-      <c r="B52" s="161"/>
-      <c r="C52" s="161"/>
-      <c r="D52" s="161"/>
-      <c r="E52" s="161"/>
-      <c r="F52" s="161"/>
-      <c r="G52" s="161"/>
-      <c r="H52" s="161"/>
-      <c r="I52" s="161"/>
-      <c r="J52" s="161"/>
-      <c r="K52" s="161"/>
-      <c r="L52" s="161"/>
-      <c r="M52" s="161"/>
+      <c r="A52" s="160"/>
+      <c r="B52" s="160"/>
+      <c r="C52" s="160"/>
+      <c r="D52" s="160"/>
+      <c r="E52" s="160"/>
+      <c r="F52" s="160"/>
+      <c r="G52" s="160"/>
+      <c r="H52" s="160"/>
+      <c r="I52" s="160"/>
+      <c r="J52" s="160"/>
+      <c r="K52" s="160"/>
+      <c r="L52" s="160"/>
+      <c r="M52" s="160"/>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="1" t="s">
@@ -9722,7 +9722,7 @@
       <c r="B182" s="27" t="s">
         <v>325</v>
       </c>
-      <c r="D182" s="160" t="s">
+      <c r="D182" s="161" t="s">
         <v>321</v>
       </c>
       <c r="E182" s="119"/>
@@ -9757,7 +9757,7 @@
       <c r="B183" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="D183" s="160"/>
+      <c r="D183" s="161"/>
       <c r="F183" s="103"/>
       <c r="G183" s="16"/>
       <c r="H183" s="9"/>
@@ -9766,7 +9766,7 @@
       <c r="K183" s="6"/>
     </row>
     <row r="184" spans="1:12">
-      <c r="D184" s="160"/>
+      <c r="D184" s="161"/>
       <c r="F184" s="103"/>
       <c r="G184" s="16"/>
       <c r="H184" s="9"/>
@@ -9784,7 +9784,7 @@
       <c r="B186" s="27" t="s">
         <v>322</v>
       </c>
-      <c r="D186" s="160" t="s">
+      <c r="D186" s="161" t="s">
         <v>367</v>
       </c>
       <c r="E186" s="119"/>
@@ -9819,15 +9819,15 @@
       <c r="B187" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="D187" s="160"/>
+      <c r="D187" s="161"/>
       <c r="E187" s="119"/>
     </row>
     <row r="188" spans="1:12">
-      <c r="D188" s="160"/>
+      <c r="D188" s="161"/>
       <c r="E188" s="119"/>
     </row>
     <row r="189" spans="1:12" ht="13.5" customHeight="1">
-      <c r="D189" s="160"/>
+      <c r="D189" s="161"/>
       <c r="E189" s="119"/>
     </row>
     <row r="190" spans="1:12">
@@ -9840,7 +9840,7 @@
       <c r="B191" s="27" t="s">
         <v>323</v>
       </c>
-      <c r="D191" s="160" t="s">
+      <c r="D191" s="161" t="s">
         <v>320</v>
       </c>
       <c r="E191" s="119"/>
@@ -9875,15 +9875,15 @@
       <c r="B192" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="D192" s="160"/>
+      <c r="D192" s="161"/>
       <c r="E192" s="119"/>
     </row>
     <row r="193" spans="1:14">
-      <c r="D193" s="160"/>
+      <c r="D193" s="161"/>
       <c r="E193" s="119"/>
     </row>
     <row r="194" spans="1:14">
-      <c r="D194" s="160"/>
+      <c r="D194" s="161"/>
       <c r="E194" s="119"/>
     </row>
     <row r="196" spans="1:14" s="54" customFormat="1">
@@ -9993,7 +9993,7 @@
       <c r="M199" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N199" s="161"/>
+      <c r="N199" s="160"/>
     </row>
     <row r="200" spans="1:14">
       <c r="A200" s="1" t="s">
@@ -10038,7 +10038,7 @@
       <c r="M200" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N200" s="161"/>
+      <c r="N200" s="160"/>
     </row>
     <row r="201" spans="1:14">
       <c r="A201" s="1" t="s">
@@ -10083,7 +10083,7 @@
       <c r="M201" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N201" s="161"/>
+      <c r="N201" s="160"/>
     </row>
     <row r="202" spans="1:14">
       <c r="A202" s="1" t="s">
@@ -10128,7 +10128,7 @@
       <c r="M202" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N202" s="161"/>
+      <c r="N202" s="160"/>
     </row>
     <row r="203" spans="1:14">
       <c r="A203" s="1" t="s">
@@ -10173,7 +10173,7 @@
       <c r="M203" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N203" s="161"/>
+      <c r="N203" s="160"/>
     </row>
     <row r="204" spans="1:14">
       <c r="A204" s="1" t="s">
@@ -10218,7 +10218,7 @@
       <c r="M204" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N204" s="161"/>
+      <c r="N204" s="160"/>
     </row>
     <row r="205" spans="1:14">
       <c r="A205" s="1" t="s">
@@ -10263,7 +10263,7 @@
       <c r="M205" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N205" s="161"/>
+      <c r="N205" s="160"/>
     </row>
     <row r="206" spans="1:14">
       <c r="A206" s="1" t="s">
@@ -10308,7 +10308,7 @@
       <c r="M206" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N206" s="161"/>
+      <c r="N206" s="160"/>
     </row>
     <row r="207" spans="1:14">
       <c r="A207" s="1" t="s">
@@ -10353,7 +10353,7 @@
       <c r="M207" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N207" s="161"/>
+      <c r="N207" s="160"/>
     </row>
     <row r="208" spans="1:14">
       <c r="A208" s="1" t="s">
@@ -10398,7 +10398,7 @@
       <c r="M208" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N208" s="161"/>
+      <c r="N208" s="160"/>
     </row>
     <row r="209" spans="1:14">
       <c r="A209" s="1" t="s">
@@ -10443,7 +10443,7 @@
       <c r="M209" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N209" s="161"/>
+      <c r="N209" s="160"/>
     </row>
     <row r="210" spans="1:14">
       <c r="A210" s="1" t="s">
@@ -10488,7 +10488,7 @@
       <c r="M210" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N210" s="161"/>
+      <c r="N210" s="160"/>
     </row>
     <row r="211" spans="1:14">
       <c r="A211" s="1" t="s">
@@ -10533,7 +10533,7 @@
       <c r="M211" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N211" s="161"/>
+      <c r="N211" s="160"/>
     </row>
     <row r="212" spans="1:14">
       <c r="A212" s="1" t="s">
@@ -10578,7 +10578,7 @@
       <c r="M212" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N212" s="161"/>
+      <c r="N212" s="160"/>
     </row>
     <row r="213" spans="1:14">
       <c r="A213" s="1" t="s">
@@ -10623,7 +10623,7 @@
       <c r="M213" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N213" s="161"/>
+      <c r="N213" s="160"/>
     </row>
     <row r="214" spans="1:14">
       <c r="A214" s="1" t="s">
@@ -10668,7 +10668,7 @@
       <c r="M214" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N214" s="161"/>
+      <c r="N214" s="160"/>
     </row>
     <row r="215" spans="1:14">
       <c r="A215" s="1" t="s">
@@ -10713,7 +10713,7 @@
       <c r="M215" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N215" s="161"/>
+      <c r="N215" s="160"/>
     </row>
     <row r="216" spans="1:14">
       <c r="A216" s="1" t="s">
@@ -10758,7 +10758,7 @@
       <c r="M216" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N216" s="161"/>
+      <c r="N216" s="160"/>
     </row>
     <row r="217" spans="1:14">
       <c r="A217" s="1" t="s">
@@ -10803,7 +10803,7 @@
       <c r="M217" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="N217" s="161"/>
+      <c r="N217" s="160"/>
     </row>
     <row r="219" spans="1:14">
       <c r="B219" s="21" t="s">
@@ -12118,7 +12118,7 @@
         <f>K252/K$2</f>
         <v>8.581818181818182</v>
       </c>
-      <c r="N252" s="161"/>
+      <c r="N252" s="160"/>
     </row>
     <row r="253" spans="1:14">
       <c r="A253" s="1" t="s">
@@ -12162,7 +12162,7 @@
         <f t="shared" ref="L253:L260" si="114">K253/K$2</f>
         <v>8.581818181818182</v>
       </c>
-      <c r="N253" s="161"/>
+      <c r="N253" s="160"/>
     </row>
     <row r="254" spans="1:14">
       <c r="A254" s="1" t="s">
@@ -12206,7 +12206,7 @@
         <f t="shared" si="114"/>
         <v>8.581818181818182</v>
       </c>
-      <c r="N254" s="161"/>
+      <c r="N254" s="160"/>
     </row>
     <row r="255" spans="1:14">
       <c r="A255" s="1" t="s">
@@ -12250,7 +12250,7 @@
         <f t="shared" si="114"/>
         <v>8.581818181818182</v>
       </c>
-      <c r="N255" s="161"/>
+      <c r="N255" s="160"/>
     </row>
     <row r="256" spans="1:14">
       <c r="A256" s="1" t="s">
@@ -12294,7 +12294,7 @@
         <f t="shared" si="114"/>
         <v>8.581818181818182</v>
       </c>
-      <c r="N256" s="161"/>
+      <c r="N256" s="160"/>
     </row>
     <row r="257" spans="1:14">
       <c r="A257" s="1" t="s">
@@ -12338,7 +12338,7 @@
         <f t="shared" si="114"/>
         <v>8.581818181818182</v>
       </c>
-      <c r="N257" s="161"/>
+      <c r="N257" s="160"/>
     </row>
     <row r="258" spans="1:14">
       <c r="A258" s="1" t="s">
@@ -12382,7 +12382,7 @@
         <f t="shared" si="114"/>
         <v>8.581818181818182</v>
       </c>
-      <c r="N258" s="161"/>
+      <c r="N258" s="160"/>
     </row>
     <row r="259" spans="1:14">
       <c r="A259" s="1" t="s">
@@ -12426,7 +12426,7 @@
         <f t="shared" si="114"/>
         <v>8.581818181818182</v>
       </c>
-      <c r="N259" s="161"/>
+      <c r="N259" s="160"/>
     </row>
     <row r="260" spans="1:14">
       <c r="A260" s="1" t="s">
@@ -12470,7 +12470,7 @@
         <f t="shared" si="114"/>
         <v>8.581818181818182</v>
       </c>
-      <c r="N260" s="161"/>
+      <c r="N260" s="160"/>
     </row>
     <row r="261" spans="1:14">
       <c r="A261" s="1" t="s">
@@ -12514,7 +12514,7 @@
         <f>K261/K$2</f>
         <v>8.581818181818182</v>
       </c>
-      <c r="N261" s="161"/>
+      <c r="N261" s="160"/>
     </row>
     <row r="262" spans="1:14">
       <c r="E262" s="124" t="s">
@@ -14272,11 +14272,11 @@
         <v>10000</v>
       </c>
       <c r="F307" s="110">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G307" s="31">
         <f>E307+(F307*600)</f>
-        <v>82000</v>
+        <v>100000</v>
       </c>
       <c r="H307" s="48">
         <v>5500</v>
@@ -14287,15 +14287,15 @@
       </c>
       <c r="J307" s="33">
         <f t="shared" ref="J307:J314" si="129">H307/G307</f>
-        <v>6.7073170731707321E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K307" s="33">
         <f t="shared" ref="K307:K314" si="130">G307/H307</f>
-        <v>14.909090909090908</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L307" s="79">
         <f t="shared" ref="L307:L314" si="131">K307/K$2</f>
-        <v>7.0370909090909084</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M307" s="148"/>
       <c r="N307" s="1" t="s">
@@ -14325,11 +14325,11 @@
         <v>20000</v>
       </c>
       <c r="F308" s="154">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="G308" s="155">
         <f t="shared" ref="G308:G316" si="132">E308+(F308*600)</f>
-        <v>164000</v>
+        <v>200000</v>
       </c>
       <c r="H308" s="156">
         <v>11000</v>
@@ -14340,15 +14340,15 @@
       </c>
       <c r="J308" s="33">
         <f t="shared" si="129"/>
-        <v>6.7073170731707321E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K308" s="33">
         <f t="shared" si="130"/>
-        <v>14.909090909090908</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L308" s="79">
         <f t="shared" si="131"/>
-        <v>7.0370909090909084</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="N308" s="1" t="s">
         <v>442</v>
@@ -14379,14 +14379,14 @@
         <v>440</v>
       </c>
       <c r="E309" s="153">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="F309" s="154">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G309" s="155">
         <f t="shared" si="132"/>
-        <v>330000</v>
+        <v>400000</v>
       </c>
       <c r="H309" s="156">
         <v>22000</v>
@@ -14397,15 +14397,15 @@
       </c>
       <c r="J309" s="33">
         <f t="shared" si="129"/>
-        <v>6.6666666666666666E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K309" s="33">
         <f t="shared" si="130"/>
-        <v>15</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L309" s="79">
         <f t="shared" si="131"/>
-        <v>7.0799999999999992</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="N309" s="1" t="s">
         <v>443</v>
@@ -14436,14 +14436,14 @@
         <v>440</v>
       </c>
       <c r="E310" s="153">
-        <v>45000</v>
+        <v>60000</v>
       </c>
       <c r="F310" s="154">
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="G310" s="155">
         <f t="shared" si="132"/>
-        <v>495000</v>
+        <v>600000</v>
       </c>
       <c r="H310" s="156">
         <v>33000</v>
@@ -14454,15 +14454,15 @@
       </c>
       <c r="J310" s="33">
         <f t="shared" si="129"/>
-        <v>6.6666666666666666E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K310" s="33">
         <f t="shared" si="130"/>
-        <v>15</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L310" s="79">
         <f t="shared" si="131"/>
-        <v>7.0799999999999992</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="N310" s="1" t="s">
         <v>444</v>
@@ -14492,15 +14492,15 @@
       <c r="D311" s="67" t="s">
         <v>440</v>
       </c>
-      <c r="E311" s="126">
+      <c r="E311" s="153">
         <v>20000</v>
       </c>
-      <c r="F311" s="110">
-        <v>240</v>
+      <c r="F311" s="154">
+        <v>300</v>
       </c>
       <c r="G311" s="31">
         <f t="shared" si="132"/>
-        <v>164000</v>
+        <v>200000</v>
       </c>
       <c r="H311" s="48">
         <v>11000</v>
@@ -14511,15 +14511,15 @@
       </c>
       <c r="J311" s="33">
         <f t="shared" si="129"/>
-        <v>6.7073170731707321E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K311" s="33">
         <f t="shared" si="130"/>
-        <v>14.909090909090908</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L311" s="79">
         <f t="shared" si="131"/>
-        <v>7.0370909090909084</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="N311" s="1" t="s">
         <v>445</v>
@@ -14549,15 +14549,15 @@
       <c r="D312" s="67" t="s">
         <v>440</v>
       </c>
-      <c r="E312" s="126">
-        <v>30000</v>
-      </c>
-      <c r="F312" s="110">
-        <v>500</v>
+      <c r="E312" s="153">
+        <v>40000</v>
+      </c>
+      <c r="F312" s="154">
+        <v>600</v>
       </c>
       <c r="G312" s="31">
         <f t="shared" si="132"/>
-        <v>330000</v>
+        <v>400000</v>
       </c>
       <c r="H312" s="48">
         <v>22000</v>
@@ -14568,15 +14568,15 @@
       </c>
       <c r="J312" s="33">
         <f t="shared" si="129"/>
-        <v>6.6666666666666666E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K312" s="33">
         <f t="shared" si="130"/>
-        <v>15</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L312" s="79">
         <f t="shared" si="131"/>
-        <v>7.0799999999999992</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="N312" s="1" t="s">
         <v>446</v>
@@ -14606,15 +14606,15 @@
       <c r="D313" s="67" t="s">
         <v>440</v>
       </c>
-      <c r="E313" s="126">
-        <v>45000</v>
-      </c>
-      <c r="F313" s="110">
-        <v>750</v>
+      <c r="E313" s="153">
+        <v>60000</v>
+      </c>
+      <c r="F313" s="154">
+        <v>900</v>
       </c>
       <c r="G313" s="31">
         <f t="shared" si="132"/>
-        <v>495000</v>
+        <v>600000</v>
       </c>
       <c r="H313" s="48">
         <v>33000</v>
@@ -14625,15 +14625,15 @@
       </c>
       <c r="J313" s="33">
         <f t="shared" si="129"/>
-        <v>6.6666666666666666E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K313" s="33">
         <f t="shared" si="130"/>
-        <v>15</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L313" s="79">
         <f t="shared" si="131"/>
-        <v>7.0799999999999992</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="N313" s="1" t="s">
         <v>447</v>
@@ -14667,11 +14667,11 @@
         <v>20000</v>
       </c>
       <c r="F314" s="154">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="G314" s="155">
         <f t="shared" si="132"/>
-        <v>164000</v>
+        <v>200000</v>
       </c>
       <c r="H314" s="156">
         <v>11000</v>
@@ -14682,15 +14682,15 @@
       </c>
       <c r="J314" s="33">
         <f t="shared" si="129"/>
-        <v>6.7073170731707321E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K314" s="33">
         <f t="shared" si="130"/>
-        <v>14.909090909090908</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L314" s="79">
         <f t="shared" si="131"/>
-        <v>7.0370909090909084</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="N314" s="1" t="s">
         <v>448</v>
@@ -14721,14 +14721,14 @@
         <v>440</v>
       </c>
       <c r="E315" s="153">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="F315" s="154">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G315" s="155">
         <f t="shared" si="132"/>
-        <v>330000</v>
+        <v>400000</v>
       </c>
       <c r="H315" s="156">
         <v>22000</v>
@@ -14739,15 +14739,15 @@
       </c>
       <c r="J315" s="33">
         <f t="shared" ref="J315:J316" si="136">H315/G315</f>
-        <v>6.6666666666666666E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K315" s="33">
         <f t="shared" ref="K315:K316" si="137">G315/H315</f>
-        <v>15</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L315" s="79">
         <f t="shared" ref="L315:L316" si="138">K315/K$2</f>
-        <v>7.0799999999999992</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="N315" s="1" t="s">
         <v>449</v>
@@ -14778,14 +14778,14 @@
         <v>440</v>
       </c>
       <c r="E316" s="153">
-        <v>45000</v>
+        <v>60000</v>
       </c>
       <c r="F316" s="154">
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="G316" s="155">
         <f t="shared" si="132"/>
-        <v>495000</v>
+        <v>600000</v>
       </c>
       <c r="H316" s="156">
         <v>33000</v>
@@ -14796,15 +14796,15 @@
       </c>
       <c r="J316" s="33">
         <f t="shared" si="136"/>
-        <v>6.6666666666666666E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K316" s="33">
         <f t="shared" si="137"/>
-        <v>15</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L316" s="79">
         <f t="shared" si="138"/>
-        <v>7.0799999999999992</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="O316" s="43">
         <v>3500</v>
@@ -14838,6 +14838,32 @@
     <mergeCell ref="D186:D189"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="L4:L16">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{B2F9211E-D57A-4AEA-A524-AFB28AB7E709}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="111">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{99050187-FD6A-4B77-A839-102B91801CAF}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L20:L24">
     <cfRule type="dataBar" priority="62">
       <dataBar>
@@ -14848,6 +14874,20 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{EFD7BE13-65A7-4F71-8221-2F2BAF3F5F8D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L20:L109">
+    <cfRule type="dataBar" priority="212">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5C0E93B6-19A8-4E38-85A4-30A2DB3F5B56}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14918,6 +14958,20 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{B7B89474-42CD-40F3-B35C-1DD8BB29F8A5}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L62:L78 L82">
+    <cfRule type="dataBar" priority="205">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2A29568F-EA4F-4BBF-9268-F447B5C0D02D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -15034,6 +15088,76 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="L220:L225">
+    <cfRule type="dataBar" priority="238">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{7D9C5564-B205-4606-8518-7542143A913A}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L220:L249">
+    <cfRule type="dataBar" priority="266">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9F5CE0D0-0F2B-4415-BFB1-5DCA8F3236ED}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L227:L232">
+    <cfRule type="dataBar" priority="247">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C300A0E2-648C-4005-AE4A-F3DDA166FCA7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L235:L241">
+    <cfRule type="dataBar" priority="256">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{A537F0F1-8747-4B77-A595-D069780ED057}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L243:L249">
+    <cfRule type="dataBar" priority="265">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F1A9CA8F-9DA8-4A4C-854F-D87AE6E855A8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="L252:L261">
     <cfRule type="dataBar" priority="26">
       <dataBar>
@@ -15072,6 +15196,86 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{E64BD501-892F-411D-9804-071034C4E308}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L295:L303">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5AA44D2B-21AA-4B0C-95D9-B6ABF3E6CD68}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{143EDE08-4501-4E46-B376-BE1625C3C123}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5D357D3F-49A6-4D17-BEEF-B0F81E559298}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L304:L317 L20:L294">
+    <cfRule type="dataBar" priority="267">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3E171C8C-BC18-4404-B040-C93AEC6CD1B3}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L304:L317 L187:L190 L183:L185 L192:L294 L20:L181">
+    <cfRule type="dataBar" priority="270">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6A0D2B79-679B-4D8C-AA40-0EB9DFA51DB1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L305">
+    <cfRule type="dataBar" priority="276">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3E5F3BB8-69F4-4EA8-8E58-C3822801525C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -15118,216 +15322,6 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L295:L303">
-    <cfRule type="dataBar" priority="7">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5D357D3F-49A6-4D17-BEEF-B0F81E559298}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L295:L303">
-    <cfRule type="dataBar" priority="6">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{143EDE08-4501-4E46-B376-BE1625C3C123}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L295:L303">
-    <cfRule type="dataBar" priority="5">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5AA44D2B-21AA-4B0C-95D9-B6ABF3E6CD68}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L16">
-    <cfRule type="dataBar" priority="1">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B2F9211E-D57A-4AEA-A524-AFB28AB7E709}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L16">
-    <cfRule type="dataBar" priority="111">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99050187-FD6A-4B77-A839-102B91801CAF}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L62:L78 L82">
-    <cfRule type="dataBar" priority="205">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2A29568F-EA4F-4BBF-9268-F447B5C0D02D}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L20:L109">
-    <cfRule type="dataBar" priority="212">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5C0E93B6-19A8-4E38-85A4-30A2DB3F5B56}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L220:L225">
-    <cfRule type="dataBar" priority="238">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7D9C5564-B205-4606-8518-7542143A913A}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L227:L232">
-    <cfRule type="dataBar" priority="247">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C300A0E2-648C-4005-AE4A-F3DDA166FCA7}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L235:L241">
-    <cfRule type="dataBar" priority="256">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A537F0F1-8747-4B77-A595-D069780ED057}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L243:L249">
-    <cfRule type="dataBar" priority="265">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F1A9CA8F-9DA8-4A4C-854F-D87AE6E855A8}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L220:L249">
-    <cfRule type="dataBar" priority="266">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9F5CE0D0-0F2B-4415-BFB1-5DCA8F3236ED}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L304:L317 L20:L294">
-    <cfRule type="dataBar" priority="267">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3E171C8C-BC18-4404-B040-C93AEC6CD1B3}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L304:L317 L187:L190 L183:L185 L192:L294 L20:L181">
-    <cfRule type="dataBar" priority="270">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6A0D2B79-679B-4D8C-AA40-0EB9DFA51DB1}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L305">
-    <cfRule type="dataBar" priority="276">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3E5F3BB8-69F4-4EA8-8E58-C3822801525C}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
@@ -15339,6 +15333,27 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{B2F9211E-D57A-4AEA-A524-AFB28AB7E709}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{99050187-FD6A-4B77-A839-102B91801CAF}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L4:L16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{EFD7BE13-65A7-4F71-8221-2F2BAF3F5F8D}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
@@ -15348,6 +15363,19 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>L20:L24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{5C0E93B6-19A8-4E38-85A4-30A2DB3F5B56}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L20:L109</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{DF02CB43-31EF-4457-9F48-52A3600B0A42}">
@@ -15403,6 +15431,17 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>L53:L57</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{2A29568F-EA4F-4BBF-9268-F447B5C0D02D}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L62:L78 L82</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{17EE9319-948D-4DE7-9836-7CB0701A4AC2}">
@@ -15497,6 +15536,63 @@
           <xm:sqref>L198:L217</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{7D9C5564-B205-4606-8518-7542143A913A}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L220:L225</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9F5CE0D0-0F2B-4415-BFB1-5DCA8F3236ED}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L220:L249</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{C300A0E2-648C-4005-AE4A-F3DDA166FCA7}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L227:L232</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{A537F0F1-8747-4B77-A595-D069780ED057}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L235:L241</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{F1A9CA8F-9DA8-4A4C-854F-D87AE6E855A8}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L243:L249</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{18BC91AE-2BB9-44A0-89CF-709D3612A9FB}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
@@ -15534,6 +15630,76 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>L283:L292</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{5AA44D2B-21AA-4B0C-95D9-B6ABF3E6CD68}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{143EDE08-4501-4E46-B376-BE1625C3C123}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{5D357D3F-49A6-4D17-BEEF-B0F81E559298}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L295:L303</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{3E171C8C-BC18-4404-B040-C93AEC6CD1B3}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L304:L317 L20:L294</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6A0D2B79-679B-4D8C-AA40-0EB9DFA51DB1}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L304:L317 L187:L190 L183:L185 L192:L294 L20:L181</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{3E5F3BB8-69F4-4EA8-8E58-C3822801525C}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L305</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{DDE7A09C-B005-4F3B-AFC9-56110C2EA5C2}">
@@ -15574,187 +15740,6 @@
           </x14:cfRule>
           <xm:sqref>L307:L317</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5D357D3F-49A6-4D17-BEEF-B0F81E559298}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L295:L303</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{143EDE08-4501-4E46-B376-BE1625C3C123}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L295:L303</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5AA44D2B-21AA-4B0C-95D9-B6ABF3E6CD68}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L295:L303</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B2F9211E-D57A-4AEA-A524-AFB28AB7E709}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L4:L16</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{99050187-FD6A-4B77-A839-102B91801CAF}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L4:L16</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2A29568F-EA4F-4BBF-9268-F447B5C0D02D}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L62:L78 L82</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5C0E93B6-19A8-4E38-85A4-30A2DB3F5B56}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L20:L109</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7D9C5564-B205-4606-8518-7542143A913A}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L220:L225</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C300A0E2-648C-4005-AE4A-F3DDA166FCA7}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L227:L232</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A537F0F1-8747-4B77-A595-D069780ED057}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L235:L241</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F1A9CA8F-9DA8-4A4C-854F-D87AE6E855A8}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L243:L249</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9F5CE0D0-0F2B-4415-BFB1-5DCA8F3236ED}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L220:L249</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3E171C8C-BC18-4404-B040-C93AEC6CD1B3}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L304:L317 L20:L294</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6A0D2B79-679B-4D8C-AA40-0EB9DFA51DB1}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L304:L317 L187:L190 L183:L185 L192:L294 L20:L181</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3E5F3BB8-69F4-4EA8-8E58-C3822801525C}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L305</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/BM(최종).xlsx
+++ b/BM(최종).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dksru\Desktop\NanseExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1BEC61-2D6C-411B-947B-A3D22D20E7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B8FEDE-C6F4-4FAB-A56E-A68A76D73C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
   </bookViews>
@@ -9991,12 +9991,12 @@
         <v>48</v>
       </c>
       <c r="E200" s="108">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="F200" s="108"/>
       <c r="G200" s="70">
         <f t="shared" si="70"/>
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="H200" s="72">
         <v>33000</v>
@@ -10007,15 +10007,15 @@
       </c>
       <c r="J200" s="73">
         <f t="shared" si="72"/>
-        <v>0.16500000000000001</v>
+        <v>5.5E-2</v>
       </c>
       <c r="K200" s="73">
         <f t="shared" si="73"/>
-        <v>6.0606060606060606</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L200" s="43">
         <f>K200/K$2</f>
-        <v>2.8606060606060604</v>
+        <v>8.581818181818182</v>
       </c>
       <c r="M200" s="1" t="s">
         <v>414</v>
@@ -14406,6 +14406,20 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{EFD7BE13-65A7-4F71-8221-2F2BAF3F5F8D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L20:L100">
+    <cfRule type="dataBar" priority="296">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5C0E93B6-19A8-4E38-85A4-30A2DB3F5B56}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14574,6 +14588,20 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{2D0D8CCD-4F11-4341-87C6-36F16A7CA7AC}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L189:L207">
+    <cfRule type="dataBar" priority="278">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D3774836-057B-49BF-A577-3C1CC0561486}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -14812,34 +14840,6 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L189:L207">
-    <cfRule type="dataBar" priority="278">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D3774836-057B-49BF-A577-3C1CC0561486}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L20:L100">
-    <cfRule type="dataBar" priority="296">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5C0E93B6-19A8-4E38-85A4-30A2DB3F5B56}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
@@ -14881,6 +14881,19 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>L20:L24</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{5C0E93B6-19A8-4E38-85A4-30A2DB3F5B56}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L20:L100</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{DF02CB43-31EF-4457-9F48-52A3600B0A42}">
@@ -15015,6 +15028,19 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>L161:L170</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{D3774836-057B-49BF-A577-3C1CC0561486}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L189:L207</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{7D9C5564-B205-4606-8518-7542143A913A}">
@@ -15221,32 +15247,6 @@
           </x14:cfRule>
           <xm:sqref>L297:L307</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D3774836-057B-49BF-A577-3C1CC0561486}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L189:L207</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5C0E93B6-19A8-4E38-85A4-30A2DB3F5B56}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>L20:L100</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/BM(최종).xlsx
+++ b/BM(최종).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CBA515-9E05-44A4-A13D-3D81FC95E0C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFF0B2A-FF69-4156-8F35-976682E6336D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="20880" activeTab="2" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="20880" activeTab="2" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
   </bookViews>
   <sheets>
     <sheet name="재화 기준" sheetId="2" r:id="rId1"/>

--- a/BM(최종).xlsx
+++ b/BM(최종).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\투캉 공유 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFF0B2A-FF69-4156-8F35-976682E6336D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5FEEEC-EABF-4A1D-B225-74916BCF23B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="20880" activeTab="2" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20115" windowHeight="20880" activeTab="2" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
   </bookViews>
   <sheets>
     <sheet name="재화 기준" sheetId="2" r:id="rId1"/>

--- a/BM(최종).xlsx
+++ b/BM(최종).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnbv6\Desktop\공유 폴더\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E8776F-810F-47D7-8A2E-2EB1854A75A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A94B8F-D6BE-4D19-836D-896E29C6EC3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25800" yWindow="0" windowWidth="25800" windowHeight="20880" activeTab="4" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="37380" windowHeight="20880" activeTab="4" xr2:uid="{392C83F7-62C7-494A-8A61-050AF5CF3C50}"/>
   </bookViews>
   <sheets>
     <sheet name="재화 기준" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="511">
   <si>
     <t>개수</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1814,31 +1814,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>금화 (3D)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금화 (10D)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금화 (500조)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>500조</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10D</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3D</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>다이아 (5/5)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금화 (2D)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금화 (5D)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금화 (200조)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -15650,11 +15650,11 @@
         <v>5000</v>
       </c>
       <c r="E16" s="128">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F16" s="129">
         <f>D16+(E16*600)</f>
-        <v>176000</v>
+        <v>173000</v>
       </c>
       <c r="G16" s="130">
         <f>H16*10</f>
@@ -15665,11 +15665,11 @@
       </c>
       <c r="I16" s="131">
         <f>F16/G16</f>
-        <v>32</v>
+        <v>31.454545454545453</v>
       </c>
       <c r="J16" s="115">
         <f>I16/I$2</f>
-        <v>15.103999999999999</v>
+        <v>14.846545454545453</v>
       </c>
       <c r="K16" s="160"/>
       <c r="L16" s="160"/>
@@ -20850,7 +20850,7 @@
         <v>54</v>
       </c>
       <c r="B7" s="124" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C7" s="125" t="s">
         <v>447</v>
@@ -20899,20 +20899,20 @@
         <v>447</v>
       </c>
       <c r="D8" s="126" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E8" s="127">
         <v>0</v>
       </c>
       <c r="F8" s="128" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G8" s="129" t="e">
         <f t="shared" ref="G8" si="4">E8+(F8*150)</f>
         <v>#VALUE!</v>
       </c>
       <c r="H8" s="130">
-        <f t="shared" ref="H8:H15" si="5">I8*10</f>
+        <f t="shared" ref="H8:H14" si="5">I8*10</f>
         <v>5500</v>
       </c>
       <c r="I8" s="153">
@@ -20921,7 +20921,7 @@
       <c r="J8" s="131"/>
       <c r="K8" s="131"/>
       <c r="L8" s="115">
-        <f t="shared" ref="L8:L15" si="6">K8/K$2</f>
+        <f t="shared" ref="L8:L14" si="6">K8/K$2</f>
         <v>0</v>
       </c>
     </row>
@@ -20975,11 +20975,11 @@
         <v>550</v>
       </c>
       <c r="J10" s="131">
-        <f t="shared" ref="J10:J15" si="7">H10/G10</f>
+        <f t="shared" ref="J10:J14" si="7">H10/G10</f>
         <v>3.125E-2</v>
       </c>
       <c r="K10" s="131">
-        <f t="shared" ref="K10:K15" si="8">G10/H10</f>
+        <f t="shared" ref="K10:K14" si="8">G10/H10</f>
         <v>32</v>
       </c>
       <c r="L10" s="115">
@@ -21094,41 +21094,16 @@
       <c r="B15" s="124" t="s">
         <v>441</v>
       </c>
-      <c r="C15" s="125" t="s">
-        <v>447</v>
-      </c>
-      <c r="D15" s="126" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="127">
-        <v>0</v>
-      </c>
-      <c r="F15" s="128">
-        <v>530000</v>
-      </c>
-      <c r="G15" s="129">
-        <f>E15+(F15*1/3)</f>
-        <v>176666.66666666666</v>
-      </c>
-      <c r="H15" s="130">
-        <f t="shared" si="5"/>
-        <v>5500</v>
-      </c>
-      <c r="I15" s="153">
-        <v>550</v>
-      </c>
-      <c r="J15" s="131">
-        <f t="shared" si="7"/>
-        <v>3.1132075471698113E-2</v>
-      </c>
-      <c r="K15" s="131">
-        <f t="shared" si="8"/>
-        <v>32.121212121212118</v>
-      </c>
-      <c r="L15" s="115">
-        <f t="shared" si="6"/>
-        <v>15.161212121212118</v>
-      </c>
+      <c r="C15" s="125"/>
+      <c r="D15" s="126"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="128"/>
+      <c r="G15" s="129"/>
+      <c r="H15" s="130"/>
+      <c r="I15" s="153"/>
+      <c r="J15" s="131"/>
+      <c r="K15" s="131"/>
+      <c r="L15" s="115"/>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="109" t="s">
@@ -21253,7 +21228,7 @@
         <v>54</v>
       </c>
       <c r="B24" s="124" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C24" s="125" t="s">
         <v>447</v>
@@ -21302,7 +21277,7 @@
         <v>453</v>
       </c>
       <c r="D25" s="126" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E25" s="127"/>
       <c r="F25" s="128" t="s">
@@ -21495,41 +21470,16 @@
       <c r="B32" s="124" t="s">
         <v>441</v>
       </c>
-      <c r="C32" s="125" t="s">
-        <v>453</v>
-      </c>
-      <c r="D32" s="126" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="127">
-        <v>0</v>
-      </c>
-      <c r="F32" s="128">
-        <v>1060000</v>
-      </c>
-      <c r="G32" s="129">
-        <f>E32+(F32*1/3)</f>
-        <v>353333.33333333331</v>
-      </c>
-      <c r="H32" s="130">
-        <f t="shared" si="14"/>
-        <v>11000</v>
-      </c>
-      <c r="I32" s="153">
-        <v>1100</v>
-      </c>
-      <c r="J32" s="131">
-        <f t="shared" si="16"/>
-        <v>3.1132075471698113E-2</v>
-      </c>
-      <c r="K32" s="131">
-        <f t="shared" si="17"/>
-        <v>32.121212121212118</v>
-      </c>
-      <c r="L32" s="115">
-        <f t="shared" si="15"/>
-        <v>15.161212121212118</v>
-      </c>
+      <c r="C32" s="125"/>
+      <c r="D32" s="126"/>
+      <c r="E32" s="127"/>
+      <c r="F32" s="128"/>
+      <c r="G32" s="129"/>
+      <c r="H32" s="130"/>
+      <c r="I32" s="153"/>
+      <c r="J32" s="131"/>
+      <c r="K32" s="131"/>
+      <c r="L32" s="115"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="109" t="s">
@@ -21591,10 +21541,10 @@
         <v>0</v>
       </c>
       <c r="F34" s="128">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G34" s="129">
-        <f>E34+(F34*14000)</f>
+        <f>E34+(F34*7000)</f>
         <v>350000</v>
       </c>
       <c r="H34" s="130">
@@ -21768,7 +21718,7 @@
         <v>54</v>
       </c>
       <c r="B42" s="124" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C42" s="125" t="s">
         <v>447</v>
@@ -21817,13 +21767,13 @@
         <v>454</v>
       </c>
       <c r="D43" s="126" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="E43" s="127">
         <v>0</v>
       </c>
       <c r="F43" s="128" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G43" s="129" t="e">
         <f>E43+(F43*0.0035)</f>
@@ -21896,11 +21846,11 @@
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="185">
-        <v>1400000000</v>
+        <v>1200000000</v>
       </c>
       <c r="G46" s="129">
         <f>E46+(F46*0.00075)</f>
-        <v>1050000</v>
+        <v>900000</v>
       </c>
       <c r="H46" s="130">
         <f t="shared" ref="H46:H56" si="24">I46*10</f>
@@ -21932,11 +21882,11 @@
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="185">
-        <v>600000000</v>
+        <v>300000000</v>
       </c>
       <c r="G47" s="129">
         <f>E47+(F47*0.0035)</f>
-        <v>2100000</v>
+        <v>1050000</v>
       </c>
       <c r="H47" s="130">
         <f t="shared" si="24"/>
@@ -22038,41 +21988,16 @@
       <c r="B50" s="124" t="s">
         <v>441</v>
       </c>
-      <c r="C50" s="125" t="s">
-        <v>454</v>
-      </c>
-      <c r="D50" s="126" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="127">
-        <v>0</v>
-      </c>
-      <c r="F50" s="187">
-        <v>3180000</v>
-      </c>
-      <c r="G50" s="129">
-        <f>E50+(F50*1/3)</f>
-        <v>1060000</v>
-      </c>
-      <c r="H50" s="130">
-        <f t="shared" si="24"/>
-        <v>33000</v>
-      </c>
-      <c r="I50" s="153">
-        <v>3300</v>
-      </c>
-      <c r="J50" s="131">
-        <f t="shared" si="25"/>
-        <v>3.1132075471698113E-2</v>
-      </c>
-      <c r="K50" s="131">
-        <f t="shared" si="26"/>
-        <v>32.121212121212125</v>
-      </c>
-      <c r="L50" s="115">
-        <f t="shared" si="23"/>
-        <v>15.161212121212122</v>
-      </c>
+      <c r="C50" s="125"/>
+      <c r="D50" s="126"/>
+      <c r="E50" s="127"/>
+      <c r="F50" s="187"/>
+      <c r="G50" s="129"/>
+      <c r="H50" s="130"/>
+      <c r="I50" s="153"/>
+      <c r="J50" s="131"/>
+      <c r="K50" s="131"/>
+      <c r="L50" s="115"/>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="109" t="s">
@@ -22134,10 +22059,10 @@
         <v>0</v>
       </c>
       <c r="F52" s="128">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G52" s="129">
-        <f>E52+(F52*14000)</f>
+        <f>E52+(F52*7000)</f>
         <v>1050000</v>
       </c>
       <c r="H52" s="130">
@@ -22177,11 +22102,11 @@
         <v>0</v>
       </c>
       <c r="F53" s="128">
-        <v>900</v>
+        <v>960</v>
       </c>
       <c r="G53" s="129">
-        <f>E53+(F53*1200)</f>
-        <v>1080000</v>
+        <f>E53+(F53*1500)</f>
+        <v>1440000</v>
       </c>
       <c r="H53" s="130">
         <f t="shared" si="24"/>
@@ -22192,15 +22117,15 @@
       </c>
       <c r="J53" s="131">
         <f t="shared" si="25"/>
-        <v>3.0555555555555555E-2</v>
+        <v>2.2916666666666665E-2</v>
       </c>
       <c r="K53" s="131">
         <f t="shared" si="26"/>
-        <v>32.727272727272727</v>
+        <v>43.636363636363633</v>
       </c>
       <c r="L53" s="115">
         <f t="shared" si="23"/>
-        <v>15.447272727272725</v>
+        <v>20.596363636363634</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -22347,7 +22272,7 @@
         <v>54</v>
       </c>
       <c r="B60" s="124" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C60" s="125" t="s">
         <v>447</v>
@@ -22393,24 +22318,12 @@
         <v>434</v>
       </c>
       <c r="C61" s="125"/>
-      <c r="D61" s="126" t="s">
-        <v>506</v>
-      </c>
+      <c r="D61" s="126"/>
       <c r="E61" s="127"/>
-      <c r="F61" s="128" t="s">
-        <v>507</v>
-      </c>
-      <c r="G61" s="129" t="e">
-        <f>E61+(F61*0.0035)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H61" s="130">
-        <f t="shared" ref="H61" si="32">I61*10</f>
-        <v>33000</v>
-      </c>
-      <c r="I61" s="153">
-        <v>3300</v>
-      </c>
+      <c r="F61" s="128"/>
+      <c r="G61" s="129"/>
+      <c r="H61" s="130"/>
+      <c r="I61" s="153"/>
       <c r="J61" s="131"/>
       <c r="K61" s="131"/>
       <c r="L61" s="115"/>
@@ -22436,7 +22349,7 @@
       <c r="J62" s="131"/>
       <c r="K62" s="131"/>
       <c r="L62" s="115">
-        <f t="shared" ref="L62:L74" si="33">K62/K$2</f>
+        <f t="shared" ref="L62:L74" si="32">K62/K$2</f>
         <v>0</v>
       </c>
       <c r="N62" s="138"/>
@@ -22475,14 +22388,14 @@
       </c>
       <c r="E64" s="127"/>
       <c r="F64" s="185">
-        <v>3400000000</v>
+        <v>3600000000</v>
       </c>
       <c r="G64" s="129">
         <f>E64+(F64*0.0035)</f>
-        <v>11900000</v>
+        <v>12600000</v>
       </c>
       <c r="H64" s="130">
-        <f t="shared" ref="H64:H74" si="34">I64*10</f>
+        <f t="shared" ref="H64:H74" si="33">I64*10</f>
         <v>33000</v>
       </c>
       <c r="I64" s="153">
@@ -22491,7 +22404,7 @@
       <c r="J64" s="131"/>
       <c r="K64" s="131"/>
       <c r="L64" s="115">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="N64" s="132"/>
@@ -22511,14 +22424,14 @@
       </c>
       <c r="E65" s="127"/>
       <c r="F65" s="185">
-        <v>1200000000</v>
+        <v>900000000</v>
       </c>
       <c r="G65" s="129">
         <f>E65+(F65*0.0035)</f>
-        <v>4200000</v>
+        <v>3150000</v>
       </c>
       <c r="H65" s="130">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>33000</v>
       </c>
       <c r="I65" s="153">
@@ -22527,7 +22440,7 @@
       <c r="J65" s="131"/>
       <c r="K65" s="131"/>
       <c r="L65" s="115">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="N65" s="132"/>
@@ -22554,7 +22467,7 @@
         <v>12600000</v>
       </c>
       <c r="H66" s="130">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>33000</v>
       </c>
       <c r="I66" s="153">
@@ -22563,7 +22476,7 @@
       <c r="J66" s="131"/>
       <c r="K66" s="131"/>
       <c r="L66" s="115">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -22591,22 +22504,22 @@
         <v>1060000</v>
       </c>
       <c r="H67" s="130">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>33000</v>
       </c>
       <c r="I67" s="153">
         <v>3300</v>
       </c>
       <c r="J67" s="131">
-        <f t="shared" ref="J67:J74" si="35">H67/G67</f>
+        <f t="shared" ref="J67:J74" si="34">H67/G67</f>
         <v>3.1132075471698113E-2</v>
       </c>
       <c r="K67" s="131">
-        <f t="shared" ref="K67:K74" si="36">G67/H67</f>
+        <f t="shared" ref="K67:K74" si="35">G67/H67</f>
         <v>32.121212121212125</v>
       </c>
       <c r="L67" s="115">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>15.161212121212122</v>
       </c>
     </row>
@@ -22617,41 +22530,16 @@
       <c r="B68" s="124" t="s">
         <v>441</v>
       </c>
-      <c r="C68" s="125" t="s">
-        <v>457</v>
-      </c>
-      <c r="D68" s="126" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="127">
-        <v>0</v>
-      </c>
-      <c r="F68" s="128">
-        <v>3180000</v>
-      </c>
-      <c r="G68" s="129">
-        <f>E68+(F68*1/3)</f>
-        <v>1060000</v>
-      </c>
-      <c r="H68" s="130">
-        <f t="shared" si="34"/>
-        <v>33000</v>
-      </c>
-      <c r="I68" s="153">
-        <v>3300</v>
-      </c>
-      <c r="J68" s="131">
-        <f t="shared" si="35"/>
-        <v>3.1132075471698113E-2</v>
-      </c>
-      <c r="K68" s="131">
-        <f t="shared" si="36"/>
-        <v>32.121212121212125</v>
-      </c>
-      <c r="L68" s="115">
-        <f t="shared" si="33"/>
-        <v>15.161212121212122</v>
-      </c>
+      <c r="C68" s="125"/>
+      <c r="D68" s="126"/>
+      <c r="E68" s="127"/>
+      <c r="F68" s="128"/>
+      <c r="G68" s="129"/>
+      <c r="H68" s="130"/>
+      <c r="I68" s="153"/>
+      <c r="J68" s="131"/>
+      <c r="K68" s="131"/>
+      <c r="L68" s="115"/>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="109" t="s">
@@ -22677,22 +22565,22 @@
         <v>1045500</v>
       </c>
       <c r="H69" s="130">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>33000</v>
       </c>
       <c r="I69" s="153">
         <v>3300</v>
       </c>
       <c r="J69" s="131">
+        <f t="shared" si="34"/>
+        <v>3.1563845050215207E-2</v>
+      </c>
+      <c r="K69" s="131">
         <f t="shared" si="35"/>
-        <v>3.1563845050215207E-2</v>
-      </c>
-      <c r="K69" s="131">
-        <f t="shared" si="36"/>
         <v>31.681818181818183</v>
       </c>
       <c r="L69" s="115">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>14.953818181818182</v>
       </c>
     </row>
@@ -22713,29 +22601,29 @@
         <v>0</v>
       </c>
       <c r="F70" s="128">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="G70" s="129">
-        <f>E70+(F70*14000)</f>
+        <f>E70+(F70*7000)</f>
         <v>1050000</v>
       </c>
       <c r="H70" s="130">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>33000</v>
       </c>
       <c r="I70" s="153">
         <v>3300</v>
       </c>
       <c r="J70" s="131">
+        <f t="shared" si="34"/>
+        <v>3.1428571428571431E-2</v>
+      </c>
+      <c r="K70" s="131">
         <f t="shared" si="35"/>
-        <v>3.1428571428571431E-2</v>
-      </c>
-      <c r="K70" s="131">
-        <f t="shared" si="36"/>
         <v>31.818181818181817</v>
       </c>
       <c r="L70" s="115">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>15.018181818181816</v>
       </c>
     </row>
@@ -22756,30 +22644,30 @@
         <v>0</v>
       </c>
       <c r="F71" s="128">
-        <v>900</v>
+        <v>960</v>
       </c>
       <c r="G71" s="129">
-        <f>E71+(F71*1200)</f>
-        <v>1080000</v>
+        <f>E71+(F71*1500)</f>
+        <v>1440000</v>
       </c>
       <c r="H71" s="130">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>33000</v>
       </c>
       <c r="I71" s="153">
         <v>3300</v>
       </c>
       <c r="J71" s="131">
+        <f t="shared" si="34"/>
+        <v>2.2916666666666665E-2</v>
+      </c>
+      <c r="K71" s="131">
         <f t="shared" si="35"/>
-        <v>3.0555555555555555E-2</v>
-      </c>
-      <c r="K71" s="131">
-        <f t="shared" si="36"/>
-        <v>32.727272727272727</v>
+        <v>43.636363636363633</v>
       </c>
       <c r="L71" s="115">
-        <f t="shared" si="33"/>
-        <v>15.447272727272725</v>
+        <f t="shared" si="32"/>
+        <v>20.596363636363634</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -22839,26 +22727,26 @@
       <c r="E73" s="179"/>
       <c r="F73" s="180"/>
       <c r="G73" s="181">
-        <f t="shared" ref="G73:G74" si="37">E73+(F73*150)</f>
+        <f t="shared" ref="G73:G74" si="36">E73+(F73*150)</f>
         <v>0</v>
       </c>
       <c r="H73" s="182">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>33000</v>
       </c>
       <c r="I73" s="183">
         <v>3300</v>
       </c>
       <c r="J73" s="184" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K73" s="184">
         <f t="shared" si="35"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K73" s="184">
-        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L73" s="143">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -22878,26 +22766,26 @@
       <c r="E74" s="179"/>
       <c r="F74" s="180"/>
       <c r="G74" s="181">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H74" s="182">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>33000</v>
       </c>
       <c r="I74" s="183">
         <v>3300</v>
       </c>
       <c r="J74" s="184" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K74" s="184">
         <f t="shared" si="35"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K74" s="184">
-        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L74" s="143">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -22939,11 +22827,11 @@
         <v>0</v>
       </c>
       <c r="G78" s="129">
-        <f t="shared" ref="G78:G79" si="38">E78+(F78*150)</f>
+        <f t="shared" ref="G78:G79" si="37">E78+(F78*150)</f>
         <v>0</v>
       </c>
       <c r="H78" s="130">
-        <f t="shared" ref="H78:H88" si="39">I78*10</f>
+        <f t="shared" ref="H78:H88" si="38">I78*10</f>
         <v>0</v>
       </c>
       <c r="I78" s="153">
@@ -22952,7 +22840,7 @@
       <c r="J78" s="131"/>
       <c r="K78" s="131"/>
       <c r="L78" s="115">
-        <f t="shared" ref="L78:L88" si="40">K78/K$2</f>
+        <f t="shared" ref="L78:L88" si="39">K78/K$2</f>
         <v>0</v>
       </c>
     </row>
@@ -22976,11 +22864,11 @@
         <v>0</v>
       </c>
       <c r="G79" s="129">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="H79" s="130">
         <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="H79" s="130">
-        <f t="shared" si="39"/>
         <v>33000</v>
       </c>
       <c r="I79" s="153">
@@ -22989,7 +22877,7 @@
       <c r="J79" s="131"/>
       <c r="K79" s="131"/>
       <c r="L79" s="115">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
@@ -23017,7 +22905,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="130">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="I80" s="153">
@@ -23026,7 +22914,7 @@
       <c r="J80" s="131"/>
       <c r="K80" s="131"/>
       <c r="L80" s="115">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
     </row>
@@ -23054,22 +22942,22 @@
         <v>1050000</v>
       </c>
       <c r="H81" s="130">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>33000</v>
       </c>
       <c r="I81" s="153">
         <v>3300</v>
       </c>
       <c r="J81" s="131">
-        <f t="shared" ref="J81:J88" si="41">H81/G81</f>
+        <f t="shared" ref="J81:J88" si="40">H81/G81</f>
         <v>3.1428571428571431E-2</v>
       </c>
       <c r="K81" s="131">
-        <f t="shared" ref="K81:K88" si="42">G81/H81</f>
+        <f t="shared" ref="K81:K88" si="41">G81/H81</f>
         <v>31.818181818181817</v>
       </c>
       <c r="L81" s="115">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>15.018181818181816</v>
       </c>
     </row>
@@ -23097,22 +22985,22 @@
         <v>1050000</v>
       </c>
       <c r="H82" s="130">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>33000</v>
       </c>
       <c r="I82" s="153">
         <v>3300</v>
       </c>
       <c r="J82" s="131">
+        <f t="shared" si="40"/>
+        <v>3.1428571428571431E-2</v>
+      </c>
+      <c r="K82" s="131">
         <f t="shared" si="41"/>
-        <v>3.1428571428571431E-2</v>
-      </c>
-      <c r="K82" s="131">
-        <f t="shared" si="42"/>
         <v>31.818181818181817</v>
       </c>
       <c r="L82" s="115">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>15.018181818181816</v>
       </c>
     </row>
@@ -23140,22 +23028,22 @@
         <v>1050000</v>
       </c>
       <c r="H83" s="130">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>33000</v>
       </c>
       <c r="I83" s="153">
         <v>3300</v>
       </c>
       <c r="J83" s="131">
+        <f t="shared" si="40"/>
+        <v>3.1428571428571431E-2</v>
+      </c>
+      <c r="K83" s="131">
         <f t="shared" si="41"/>
-        <v>3.1428571428571431E-2</v>
-      </c>
-      <c r="K83" s="131">
-        <f t="shared" si="42"/>
         <v>31.818181818181817</v>
       </c>
       <c r="L83" s="115">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>15.018181818181816</v>
       </c>
     </row>
@@ -23183,22 +23071,22 @@
         <v>1050000</v>
       </c>
       <c r="H84" s="130">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>33000</v>
       </c>
       <c r="I84" s="153">
         <v>3300</v>
       </c>
       <c r="J84" s="131">
+        <f t="shared" si="40"/>
+        <v>3.1428571428571431E-2</v>
+      </c>
+      <c r="K84" s="131">
         <f t="shared" si="41"/>
-        <v>3.1428571428571431E-2</v>
-      </c>
-      <c r="K84" s="131">
-        <f t="shared" si="42"/>
         <v>31.818181818181817</v>
       </c>
       <c r="L84" s="115">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>15.018181818181816</v>
       </c>
     </row>
@@ -23226,22 +23114,22 @@
         <v>1050000</v>
       </c>
       <c r="H85" s="130">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>33000</v>
       </c>
       <c r="I85" s="153">
         <v>3300</v>
       </c>
       <c r="J85" s="131">
+        <f t="shared" si="40"/>
+        <v>3.1428571428571431E-2</v>
+      </c>
+      <c r="K85" s="131">
         <f t="shared" si="41"/>
-        <v>3.1428571428571431E-2</v>
-      </c>
-      <c r="K85" s="131">
-        <f t="shared" si="42"/>
         <v>31.818181818181817</v>
       </c>
       <c r="L85" s="115">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>15.018181818181816</v>
       </c>
     </row>
@@ -23269,22 +23157,22 @@
         <v>1054000</v>
       </c>
       <c r="H86" s="130">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>33000</v>
       </c>
       <c r="I86" s="153">
         <v>3300</v>
       </c>
       <c r="J86" s="131">
+        <f t="shared" si="40"/>
+        <v>3.1309297912713474E-2</v>
+      </c>
+      <c r="K86" s="131">
         <f t="shared" si="41"/>
-        <v>3.1309297912713474E-2</v>
-      </c>
-      <c r="K86" s="131">
-        <f t="shared" si="42"/>
         <v>31.939393939393938</v>
       </c>
       <c r="L86" s="115">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>15.075393939393937</v>
       </c>
     </row>
@@ -23312,22 +23200,22 @@
         <v>490000</v>
       </c>
       <c r="H87" s="130">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>33000</v>
       </c>
       <c r="I87" s="153">
         <v>3300</v>
       </c>
       <c r="J87" s="131">
+        <f t="shared" si="40"/>
+        <v>6.7346938775510207E-2</v>
+      </c>
+      <c r="K87" s="131">
         <f t="shared" si="41"/>
-        <v>6.7346938775510207E-2</v>
-      </c>
-      <c r="K87" s="131">
-        <f t="shared" si="42"/>
         <v>14.848484848484848</v>
       </c>
       <c r="L87" s="115">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>7.0084848484848479</v>
       </c>
     </row>
@@ -23348,30 +23236,30 @@
         <v>0</v>
       </c>
       <c r="F88" s="128">
-        <v>900</v>
+        <v>960</v>
       </c>
       <c r="G88" s="129">
-        <f>E88+(F88*1200)</f>
-        <v>1080000</v>
+        <f>E88+(F88*1500)</f>
+        <v>1440000</v>
       </c>
       <c r="H88" s="130">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>33000</v>
       </c>
       <c r="I88" s="153">
         <v>3300</v>
       </c>
       <c r="J88" s="131">
+        <f t="shared" si="40"/>
+        <v>2.2916666666666665E-2</v>
+      </c>
+      <c r="K88" s="131">
         <f t="shared" si="41"/>
-        <v>3.0555555555555555E-2</v>
-      </c>
-      <c r="K88" s="131">
-        <f t="shared" si="42"/>
-        <v>32.727272727272727</v>
+        <v>43.636363636363633</v>
       </c>
       <c r="L88" s="115">
-        <f t="shared" si="40"/>
-        <v>15.447272727272725</v>
+        <f t="shared" si="39"/>
+        <v>20.596363636363634</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -23437,26 +23325,26 @@
         <v>0</v>
       </c>
       <c r="G90" s="181">
-        <f t="shared" ref="G90:G91" si="43">E90+(F90*150)</f>
+        <f t="shared" ref="G90:G91" si="42">E90+(F90*150)</f>
         <v>0</v>
       </c>
       <c r="H90" s="182">
-        <f t="shared" ref="H90:H91" si="44">I90*10</f>
+        <f t="shared" ref="H90:H91" si="43">I90*10</f>
         <v>33000</v>
       </c>
       <c r="I90" s="183">
         <v>3300</v>
       </c>
       <c r="J90" s="184" t="e">
-        <f t="shared" ref="J90:J91" si="45">H90/G90</f>
+        <f t="shared" ref="J90:J91" si="44">H90/G90</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K90" s="184">
-        <f t="shared" ref="K90:K91" si="46">G90/H90</f>
+        <f t="shared" ref="K90:K91" si="45">G90/H90</f>
         <v>0</v>
       </c>
       <c r="L90" s="143">
-        <f t="shared" ref="L90:L91" si="47">K90/K$2</f>
+        <f t="shared" ref="L90:L91" si="46">K90/K$2</f>
         <v>0</v>
       </c>
     </row>
@@ -23480,26 +23368,26 @@
         <v>0</v>
       </c>
       <c r="G91" s="181">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="H91" s="182">
         <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H91" s="182">
-        <f t="shared" si="44"/>
         <v>33000</v>
       </c>
       <c r="I91" s="183">
         <v>3300</v>
       </c>
       <c r="J91" s="184" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K91" s="184">
         <f t="shared" si="45"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K91" s="184">
+        <v>0</v>
+      </c>
+      <c r="L91" s="143">
         <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="L91" s="143">
-        <f t="shared" si="47"/>
         <v>0</v>
       </c>
     </row>
